--- a/outputs/market_scan.xlsx
+++ b/outputs/market_scan.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -84,7 +79,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -458,7 +452,7 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -690,11 +684,11 @@
         <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>16.74</v>
+        <v>6.19</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Fertilizer Maker Yara Warns Farmers Are Being Squeezed by Price Surge  (-94) // Pareto Securities Upgrades Yara International ASA (OTCMKTS:YARIY) to S (+93) // Yara increases productivity, plant uptime, and safety with a digital t (+85)</t>
+          <t>Fertilizer Maker Yara Warns Farmers Are Being Squeezed by Price Surge  (-94) // Yara increases productivity, plant uptime, and safety with a digital t (+85) // Yara International (OB:YAR) Valuation Check After Strong Recent Shareh (+66)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n">
@@ -718,7 +712,7 @@
         </is>
       </c>
       <c r="X2" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y2" s="2" t="n">
         <v>26</v>
@@ -727,7 +721,7 @@
         <v>30</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>0</v>
@@ -765,10 +759,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>249.4398</v>
+        <v>249.2685</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37.055706</v>
+        <v>37.035076</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
@@ -778,16 +772,16 @@
         <v>1.02</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>55.7608130355775</v>
+        <v>55.53075948789884</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>5.310841716786539</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>260.7979436803747</v>
+        <v>260.79451779966</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.9564485099928316</v>
+        <v>0.9558042581172647</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0.2374</v>
@@ -807,7 +801,7 @@
         <v>8</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>27.71</v>
+        <v>27.8</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1079,10 +1073,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17.8611</v>
+        <v>17.8426</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21.878626</v>
+        <v>21.855942</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
@@ -1090,16 +1084,16 @@
         <v>1.47</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>65.51724623921065</v>
+        <v>65.19607591060702</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.45634943341452</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.12500003532127</v>
+        <v>17.12462965647379</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.042984637779975</v>
+        <v>1.041925774418288</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>0.2717</v>
@@ -1108,11 +1102,11 @@
         <v>4</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>15.37</v>
+        <v>23.36</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Global fossil power fell in March 2026 despite continued Hormuz blocka (-96) // Global Clean Energy Inc. (GCEI) Accelerates AI Division Growth with Fl (+91) // Renewable Energy &amp; Battery Stocks to Buy As Global Clean Energy Spendi (+63)</t>
+          <t>Global fossil power fell in March 2026 despite continued Hormuz blocka (-96) // Global Clean Energy Inc. (GCEI) Accelerates AI Division Growth with Fl (+91) // Envision Energy Secures $500M Financing Program with BBVA to Accelerat (+69)</t>
         </is>
       </c>
       <c r="R6" s="3" t="n">
@@ -1125,7 +1119,7 @@
         </is>
       </c>
       <c r="U6" s="3" t="n">
-        <v>72.8</v>
+        <v>72.62</v>
       </c>
       <c r="V6" s="3" t="b">
         <v>0</v>
@@ -1136,7 +1130,7 @@
         </is>
       </c>
       <c r="X6" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>10</v>
@@ -1145,7 +1139,7 @@
         <v>23</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB6" s="3" t="n">
         <v>0</v>
@@ -1183,10 +1177,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>75.9258</v>
+        <v>75.8935</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>26.125175</v>
+        <v>26.114056</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1194,16 +1188,16 @@
         <v>0.43</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>86.14896739575988</v>
+        <v>86.11887321482173</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>1.882606082492403</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>67.67703487254954</v>
+        <v>67.67638849329064</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.12188476096221</v>
+        <v>1.121417924586807</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.3171</v>
@@ -1385,7 +1379,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32.6198</v>
+        <v>32.6111</v>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1394,16 +1388,16 @@
         <v>3.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>18.39083425799286</v>
+        <v>18.3543651815606</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.5062305107318531</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.86958305924026</v>
+        <v>33.86940899601689</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.963100589266376</v>
+        <v>0.9628485765791459</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0.169</v>
@@ -1425,7 +1419,7 @@
         </is>
       </c>
       <c r="U9" s="3" t="n">
-        <v>-19.85</v>
+        <v>-19.87</v>
       </c>
       <c r="V9" s="3" t="b">
         <v>1</v>
@@ -1483,10 +1477,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>75.8796</v>
+        <v>75.9907</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>33.863632</v>
+        <v>33.913223</v>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="n">
@@ -1496,16 +1490,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>52.06092712153159</v>
+        <v>52.3172915525573</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>2.775793226938399</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>75.53722212049695</v>
+        <v>75.5394443935818</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.004532926599879</v>
+        <v>1.005974310086759</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.426</v>
@@ -1525,7 +1519,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>17.29</v>
+        <v>17.12</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1527,7 @@
         </is>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-17.39</v>
+        <v>-17.27</v>
       </c>
       <c r="V10" s="3" t="b">
         <v>1</v>
@@ -1591,10 +1585,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>154.2755</v>
+        <v>154.3055</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>92.05386</v>
+        <v>92.07182</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
@@ -1604,16 +1598,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>57.39038947589455</v>
+        <v>57.41033566914608</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>7.814815057017812</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>148.3971761067708</v>
+        <v>148.3977779812283</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.039611805485293</v>
+        <v>1.039810379934875</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.4084</v>
@@ -1633,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>33.5</v>
+        <v>33.48</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1641,7 +1635,7 @@
         </is>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-3.99</v>
+        <v>-3.98</v>
       </c>
       <c r="V11" s="3" t="b">
         <v>1</v>
@@ -1699,7 +1693,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>387.0324</v>
+        <v>386.8657</v>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1710,16 +1704,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>57.25186152695446</v>
+        <v>57.20783722103779</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>19.71699548146081</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>375.1544438114872</v>
+        <v>375.1511106137876</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.031661517731524</v>
+        <v>1.031226436644018</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0.503</v>
@@ -1739,7 +1733,7 @@
         <v>8</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>26.57</v>
+        <v>26.62</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1741,7 @@
         </is>
       </c>
       <c r="U12" s="3" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="V12" s="3" t="b">
         <v>0</v>
@@ -1805,7 +1799,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.7778</v>
+        <v>12.7917</v>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1816,16 +1810,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>53.63636820769428</v>
+        <v>53.76246542174277</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.6345238635148949</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>12.46018522757071</v>
+        <v>12.46046299404568</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.025488603982442</v>
+        <v>1.026580335276889</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0.6405</v>
@@ -1834,18 +1828,18 @@
         <v>2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-3.83</v>
+        <v>7.84</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>A Look At SentinelOne (S) Valuation After Geopolitical Jitters And AI  (-53)</t>
+          <t>SentinelOne: Business Growth Quality Is Better Today, At A Cheaper Val (+92) // A Look At SentinelOne (S) Valuation After Geopolitical Jitters And AI  (-53)</t>
         </is>
       </c>
       <c r="R13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>45.24</v>
+        <v>45.09</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -1862,7 +1856,7 @@
         </is>
       </c>
       <c r="X13" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>0</v>
@@ -1871,7 +1865,7 @@
         <v>30</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB13" s="3" t="n">
         <v>3</v>
@@ -1883,7 +1877,7 @@
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | A Look At SentinelOne (S) Valuation After Geopolitical Jitte</t>
+          <t>High-vol penalty | SentinelOne: Business Growth Quality Is Better Today, At A C</t>
         </is>
       </c>
     </row>
@@ -1909,10 +1903,10 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>623.4537</v>
+        <v>623.6759</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>23.130539</v>
+        <v>23.143766</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="n">
@@ -1922,16 +1916,16 @@
         <v>1.36</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>40.83858590737924</v>
+        <v>40.93505104783984</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>13.9609725387008</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>655.6292837637442</v>
+        <v>655.6337280273436</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9509241502280035</v>
+        <v>0.9512566331572238</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0.2496</v>
@@ -1951,7 +1945,7 @@
         <v>8</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>18.07</v>
+        <v>18.03</v>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
@@ -1959,7 +1953,7 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>29.24</v>
+        <v>29.29</v>
       </c>
       <c r="V14" s="4" t="b">
         <v>1</v>
@@ -2339,10 +2333,10 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>327.7685</v>
+        <v>327.8171</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>41.450817</v>
+        <v>41.45697</v>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
@@ -2350,16 +2344,16 @@
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>53.98592939795257</v>
+        <v>54.03458243438555</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>7.890588265878173</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>328.3750616002965</v>
+        <v>328.3760342068142</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.9981528678789812</v>
+        <v>0.9982980048893989</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.2371</v>
@@ -2379,7 +2373,7 @@
         <v>8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>19.64</v>
+        <v>19.63</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2381,7 @@
         </is>
       </c>
       <c r="U18" s="3" t="n">
-        <v>62.96</v>
+        <v>62.98</v>
       </c>
       <c r="V18" s="3" t="b">
         <v>0</v>
@@ -2553,10 +2547,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.5694</v>
+        <v>35.5926</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>19.801546</v>
+        <v>19.814432</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
@@ -2566,16 +2560,16 @@
         <v>4.24</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.68739574307431</v>
+        <v>39.80213518420565</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.725198604442455</v>
+        <v>1.725859869094122</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>31.86908442885787</v>
+        <v>31.86954734943531</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1.116111301269338</v>
+        <v>1.11682136337771</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0.3331</v>
@@ -2595,7 +2589,7 @@
         <v>8</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-1.84</v>
+        <v>-1.9</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -2767,10 +2761,10 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>273.3056</v>
+        <v>273.9491</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>39.88784</v>
+        <v>39.98243</v>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="n">
@@ -2780,16 +2774,16 @@
         <v>0.58</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>49.98662045856489</v>
+        <v>50.44763493001532</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>11.22036888485863</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>273.9805362842701</v>
+        <v>273.9934062251338</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.9975364370594308</v>
+        <v>0.9998381669328618</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>0.4937</v>
@@ -2809,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>36.59</v>
+        <v>36.26</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
@@ -2904,7 +2898,7 @@
         <v>4</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>25.54</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
@@ -2981,10 +2975,10 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>151.0926</v>
+        <v>151.2593</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>74.8532</v>
+        <v>74.935776</v>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="n">
@@ -2994,16 +2988,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>63.37922351338523</v>
+        <v>63.54063453206661</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>6.260252251196162</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>148.2434412638346</v>
+        <v>148.2467747441044</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>1.019219363249962</v>
+        <v>1.020320746171343</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.474</v>
@@ -3023,7 +3017,7 @@
         <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>55.05</v>
+        <v>54.88</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
@@ -3193,7 +3187,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5.834</v>
+        <v>5.838</v>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr"/>
@@ -3204,16 +3198,16 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.70671198896585</v>
+        <v>31.88853044880595</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.2870304243905203</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>5.832790736798886</v>
+        <v>5.832870359773988</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.000204176442631</v>
+        <v>1.000873059733742</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>0.6311</v>
@@ -3233,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
@@ -3509,10 +3503,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>104.9583</v>
+        <v>105.0741</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.739437</v>
+        <v>17.758999</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
@@ -3522,16 +3516,16 @@
         <v>0.92</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>68.53396650584757</v>
+        <v>68.6378010593737</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>4.258597338641133</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>106.6148288868092</v>
+        <v>106.617143701624</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.9844628325862373</v>
+        <v>0.9855270319040205</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>0.3699</v>
@@ -3551,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.49</v>
+        <v>33.35</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
@@ -3615,10 +3609,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>198.0833</v>
+        <v>198.3333</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.17288</v>
+        <v>24.203388</v>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="n">
@@ -3628,16 +3622,16 @@
         <v>0.84</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>77.83406991277013</v>
+        <v>78.28025962624062</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>7.117065550788998</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>197.7498943187572</v>
+        <v>197.7548943978769</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.001686131029504</v>
+        <v>1.002925015390977</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0.3636</v>
@@ -3657,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28.41</v>
+        <v>28.25</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
@@ -3743,7 +3737,7 @@
         <v>23.19327707643862</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.9701086750018467</v>
+        <v>0.9701086750018471</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0.3983</v>
@@ -3827,10 +3821,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>90.3428</v>
+        <v>90.4722</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>20.10365</v>
+        <v>20.132454</v>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
@@ -3838,16 +3832,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>77.96666487690418</v>
+        <v>78.37036178861214</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.470238175972428</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>91.03315155594436</v>
+        <v>91.03574046382195</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.9924162180094513</v>
+        <v>0.993809913705989</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.3575</v>
@@ -3929,10 +3923,10 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43.4444</v>
+        <v>43.3611</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>97.75</v>
+        <v>97.56251</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
@@ -3942,16 +3936,16 @@
         <v>1.78</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>74.2105145599709</v>
+        <v>74.05691041927068</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>1.902949873101774</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46.34790039062499</v>
+        <v>46.34623379177517</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0.9373551419345663</v>
+        <v>0.9355908616295633</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>0.4829</v>
@@ -3971,7 +3965,7 @@
         <v>8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>50.77</v>
+        <v>51.06</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -4035,10 +4029,10 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>481.8333</v>
+        <v>481.3009</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>29.300676</v>
+        <v>29.2683</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="n">
@@ -4048,19 +4042,19 @@
         <v>0.33</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>64.01457594572869</v>
+        <v>63.68901850649745</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>13.18650624108692</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>466.5195787217882</v>
+        <v>466.5089303475838</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1.032825544373991</v>
+        <v>1.031707836301519</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2662</v>
+        <v>0.2663</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>2</v>
@@ -4077,7 +4071,7 @@
         <v>8</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>34.84</v>
+        <v>34.98</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
@@ -4353,10 +4347,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>351.5648</v>
+        <v>351.1389</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>20.282587</v>
+        <v>20.258015</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
@@ -4366,16 +4360,16 @@
         <v>1.59</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>69.04222410573885</v>
+        <v>68.86123377492311</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>8.746029081798724</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>339.2807871500651</v>
+        <v>339.2722687897858</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.036206087672975</v>
+        <v>1.034976717413299</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0.3238</v>
@@ -4395,7 +4389,7 @@
         <v>8</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>14.65</v>
+        <v>14.79</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
@@ -4546,118 +4540,122 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>NEO.TO</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Neo Performance</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HEI.DE</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Heidelberg Materials</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Materials / Mining</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>21.5833</v>
-      </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="n">
-        <v>-0.02507</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>60.23951266913153</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>1.110449796000485</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>21.33362296775535</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>1.011704991292741</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.5242</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>‘More bang for your buck’: 7 easy ways to boost your MacBook Neo’s per (+80)</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>190.65</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>17.052773</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="n">
+        <v>0.11068</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>58.38565348898506</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>6.246426173618862</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>186.7429998779297</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1.020921769603726</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Heidelberg Materials Posts Higher Earnings, Revenue - WSJ (+93) // Is Heidelberg Materials (XTRA:HEI) Offering Value After Recent Share P (+69) // Heidelberg Materials (ETR:HEI) Stock Crosses Above Fifty Day Moving Av (+53)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>NO_ENTRY</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA39" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>‘More bang for your buck’: 7 easy ways to boost your MacBook</t>
+      <c r="S39" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="V39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>Bullish news (+37) | Heidelberg Materials Posts Higher Earnings, Revenue - WSJ (+</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ZNWD.L</t>
+          <t>NEO.TO</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Zinnwald Lithium</t>
+          <t>Neo Performance</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -4667,50 +4665,52 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>5.2778</v>
+        <v>21.5926</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="n">
-        <v>-0.038599998</v>
+        <v>-0.02507</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>22.2221515795007</v>
+        <v>60.28707413492297</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1988096842690122</v>
+        <v>1.110449796000485</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>6.029629610202931</v>
+        <v>21.33380815717909</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0.8753070988375015</v>
+        <v>1.012130237177381</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.6058</v>
+        <v>0.5242</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>27.44</v>
+        <v>14.24</v>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>Zinnwald Lithium plc receives strong support from German Federal Gover (+90) // Zinnwald Lithium advances flagship German project with strong study re (+86) // Plans for German lithium mining prompt local protests - dw.com (-63)</t>
+          <t>‘More bang for your buck’: 7 easy ways to boost your MacBook Neo’s per (+80)</t>
         </is>
       </c>
       <c r="R40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="n">
+        <v>29.8</v>
+      </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -4726,19 +4726,19 @@
         </is>
       </c>
       <c r="X40" s="3" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
@@ -4747,19 +4747,19 @@
       </c>
       <c r="AD40" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | Zinnwald Lithium plc receives strong support from German Fed</t>
+          <t>‘More bang for your buck’: 7 easy ways to boost your MacBook</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>ZNWD.L</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Albemarle</t>
+          <t>Zinnwald Lithium</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4769,52 +4769,50 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>195.4722</v>
+        <v>5.2778</v>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="n">
-        <v>-0.04656</v>
+        <v>-0.038599998</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>75.00342338057426</v>
+        <v>22.2221515795007</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>9.242724867724871</v>
+        <v>0.1988096842690122</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>159.7532083016854</v>
+        <v>6.029629610202931</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.223588714526619</v>
+        <v>0.8753070988375015</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0.5425</v>
+        <v>0.6058</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-12.94</v>
+        <v>27.44</v>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (+83) // ACPS: AHS student in critical condition, incident under investigation  (-62) // Honduran woman now charged in Albemarle County sexual exploitation cas (-59)</t>
+          <t>Zinnwald Lithium plc receives strong support from German Federal Gover (+90) // Zinnwald Lithium advances flagship German project with strong study re (+86) // Plans for German lithium mining prompt local protests - dw.com (-63)</t>
         </is>
       </c>
       <c r="R41" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>-2.63</v>
-      </c>
+      <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -4830,240 +4828,240 @@
         </is>
       </c>
       <c r="X41" s="3" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>21</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD41" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=75 | Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (</t>
+          <t>High-vol penalty | Zinnwald Lithium plc receives strong support from German Fed</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Quantum Computing</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Albemarle</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Materials / Mining</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>232.3287</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>22.524237</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="n">
-        <v>0.35158002</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>58.44986036838648</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>5.97156040252201</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>232.5782996283637</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>0.9989268038264852</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>0.2506</v>
-      </c>
-      <c r="O42" s="2" t="n">
+      <c r="E42" s="3" t="n">
+        <v>194.4352</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="n">
+        <v>-0.04656</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>74.61507477316596</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>9.242724867724871</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>159.7324676513672</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>1.217255283977853</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="O42" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P42" s="2" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>Justice Department settles with IBM over alleged DEI practices - The W (-85) // University of Illinois and IBM renew quantum technology partnership at (+38) // IBM unveils security services for thwarting agentic attacks, automatin (+35)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n">
+      <c r="P42" s="3" t="n">
+        <v>-12.94</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (+83) // ACPS: AHS student in critical condition, incident under investigation  (-62) // Honduran woman now charged in Albemarle County sexual exploitation cas (-59)</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S42" s="2" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>BUSINESS COLLATERAL (10yr)</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="V42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y42" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA42" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AD42" s="2" t="inlineStr">
-        <is>
-          <t>Justice Department settles with IBM over alleged DEI practic</t>
+      <c r="S42" s="3" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr"/>
+      <c r="V42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>NO_ENTRY</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>Weak structure | Overbought RSI=75 | Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>IONQ</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>IonQ</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Quantum Computing</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>41.205</v>
-      </c>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="n">
-        <v>-0.24400999</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>77.47494841563955</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>2.713624384037401</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>30.73428524865044</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>1.340685155388734</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>0.9896</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ (IONQ) Soars 21% on Nvidia Quantum Computing Support - Yahoo Fina (+88) // State invests $500K for Bothell quantum computing expansion, adds up t (+67)</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="n">
+      <c r="E43" s="2" t="n">
+        <v>232.2594</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>22.517065</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n">
+        <v>0.35158002</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>58.39290103456753</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>5.97156040252201</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>232.57691277398</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>0.9986346107951281</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>-11.01</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Justice Department settles with IBM over alleged DEI practices - The W (-85) // NJ residents charged with breaking into abandoned Somers IBM building  (-71) // University of Illinois and IBM renew quantum technology partnership at (+38)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S43" s="3" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>NO_ENTRY</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3" t="n">
+      <c r="S43" s="2" t="n">
+        <v>30.62</v>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y43" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA43" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="AB43" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC43" s="3" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>Weak structure | Overbought RSI=77 | Bullish news (+33) | High-vol penalty | Quantum computing stocks are back on the rise. Here’s why IO</t>
+      <c r="AB43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>Justice Department settles with IBM over alleged DEI practic</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5087,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>18.2269</v>
+        <v>18.1667</v>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
@@ -5100,16 +5098,16 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>75.03559871839184</v>
+        <v>74.88061763851279</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>1.204365018814328</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>14.85629627439711</v>
+        <v>14.85509259612472</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.226877212240689</v>
+        <v>1.222925224207206</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>1.2711</v>
@@ -5118,18 +5116,18 @@
         <v>2</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>25.55</v>
+        <v>41.15</v>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88) // Exclusive: Chad Rigetti’s Sygaldry raises $139 million to bring quantu (+71) // Quantum stocks on pace for a massive week after Nvidia debuts AI model (+69)</t>
+          <t>IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88) // Quantum Computing Stocks Are Surging. New Models From Nvidia Are Helpi (+83) // Exclusive: Chad Rigetti’s Sygaldry raises $139 million to bring quantu (+71)</t>
         </is>
       </c>
       <c r="R44" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>73.03</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -5146,7 +5144,7 @@
         </is>
       </c>
       <c r="X44" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>0</v>
@@ -5155,7 +5153,7 @@
         <v>5</v>
       </c>
       <c r="AA44" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB44" s="3" t="n">
         <v>3</v>
@@ -5167,19 +5165,19 @@
       </c>
       <c r="AD44" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=75 | High-vol penalty | IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quant</t>
+          <t>Weak structure | Overbought RSI=75 | Bullish news (+41) | High-vol penalty | IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quant</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>QBTS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>D-Wave Quantum</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5193,62 +5191,60 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>20.5231</v>
+        <v>41.2872</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="n">
-        <v>-0.77620006</v>
+        <v>-0.24400999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>75.26050532230342</v>
+        <v>77.54966551461843</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1.396428655695032</v>
+        <v>2.713624384037401</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.19398132960001</v>
+        <v>30.73592966574209</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1.267331891901444</v>
+        <v>1.34328849974398</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.3077</v>
+        <v>0.9896</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>26.75</v>
+        <v>32.6</v>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has Inched Low (-95) // Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88)</t>
+          <t>Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ (IONQ) Soars 21% on Nvidia Quantum Computing Support - Yahoo Fina (+88) // State invests $500K for Bothell quantum computing expansion, adds up t (+67)</t>
         </is>
       </c>
       <c r="R45" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>79.09</v>
+        <v>58.14</v>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U45" s="3" t="n">
-        <v>220.3</v>
-      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>NO_ENTRY</t>
         </is>
       </c>
       <c r="X45" s="3" t="n">
@@ -5273,73 +5269,73 @@
       </c>
       <c r="AD45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weak structure | Overbought RSI=75 | High-vol penalty | Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has </t>
+          <t>Weak structure | Overbought RSI=78 | Bullish news (+33) | High-vol penalty | Quantum computing stocks are back on the rise. Here’s why IO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>QBTS</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>D-Wave Quantum</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Quantum Computing</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>195370.3704</v>
+        <v>20.537</v>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>0.10783</v>
+        <v>-0.77620006</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.11741682974559</v>
+        <v>75.28542656394569</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>10403.43915343915</v>
+        <v>1.396428655695032</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>173125</v>
+        <v>16.19425909607498</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>1.128493114052681</v>
+        <v>1.268167762277237</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.3185</v>
+        <v>1.3077</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.52</v>
+        <v>26.75</v>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>Samsung asks court to block illegal strike activities by unions - Reut (-73) // Samsung hikes Galaxy Book 6 prices by up to $600 as base model goes on (+65)</t>
+          <t>Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has Inched Low (-95) // Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88)</t>
         </is>
       </c>
       <c r="R46" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>39.73</v>
+        <v>78.97</v>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -5347,10 +5343,10 @@
         </is>
       </c>
       <c r="U46" s="3" t="n">
-        <v>264.42</v>
+        <v>220.52</v>
       </c>
       <c r="V46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
@@ -5358,125 +5354,125 @@
         </is>
       </c>
       <c r="X46" s="3" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AA46" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AD46" s="3" t="inlineStr">
         <is>
-          <t>Samsung asks court to block illegal strike activities by uni</t>
+          <t xml:space="preserve">Weak structure | Overbought RSI=75 | High-vol penalty | Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>005930.KS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Uranium / Nuclear</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>185.7778</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>51.44615</v>
-      </c>
+        <v>195370.3704</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="n">
-        <v>0.16794</v>
+        <v>0.10783</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>53.78030018658377</v>
+        <v>65.11741682974559</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>12.48115055144778</v>
+        <v>10403.43915343915</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>187.9455557929145</v>
+        <v>173125</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>0.988465922638439</v>
+        <v>1.128493114052681</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>0.8539</v>
+        <v>0.3185</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>28.26</v>
+        <v>1.52</v>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>Centrus Energy Earns Technical Rating Upgrade - Investor's Business Da (+81) // Centrus Energy Stock Surges on Massive Government Deal - TipRanks (+73) // Oklo, Nano Nuclear, Centrus, NuScale Surge as White House Space Nuclea (+51)</t>
+          <t>Samsung asks court to block illegal strike activities by unions - Reut (-73) // Samsung hikes Galaxy Book 6 prices by up to $600 as base model goes on (+65)</t>
         </is>
       </c>
       <c r="R47" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S47" s="3" t="n">
-        <v>50.01</v>
+        <v>39.73</v>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="n">
+        <v>264.42</v>
+      </c>
       <c r="V47" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>NO_ENTRY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="X47" s="3" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="Y47" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA47" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Z47" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA47" s="3" t="n">
-        <v>21</v>
-      </c>
       <c r="AB47" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
@@ -5485,19 +5481,19 @@
       </c>
       <c r="AD47" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | Centrus Energy Earns Technical Rating Upgrade - Investor's B</t>
+          <t>Samsung asks court to block illegal strike activities by uni</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5511,80 +5507,78 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>215.0926</v>
+        <v>186.4074</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>64.88827000000001</v>
+        <v>51.620514</v>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>0.28517</v>
+        <v>0.16794</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>68.39757881389944</v>
+        <v>54.10222747363354</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>8.733465810301441</v>
+        <v>12.48115055144778</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>192.0487360071253</v>
+        <v>187.9581485324435</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.119989643724154</v>
+        <v>0.9917495764059175</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.323</v>
+        <v>0.8539</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>19.76</v>
+        <v>28.26</v>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nuclear Deal (+80) // BWX Technologies stock hits all-time high at 239.88 USD - Investing.co (+68)</t>
+          <t>Centrus Energy Earns Technical Rating Upgrade - Investor's Business Da (+81) // Centrus Energy Stock Surges on Massive Government Deal - TipRanks (+73) // Oklo, Nano Nuclear, Centrus, NuScale Surge as White House Space Nuclea (+51)</t>
         </is>
       </c>
       <c r="R48" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>7.99</v>
+        <v>49.51</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U48" s="3" t="n">
-        <v>124.65</v>
-      </c>
+      <c r="U48" s="3" t="inlineStr"/>
       <c r="V48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>NO_ENTRY</t>
         </is>
       </c>
       <c r="X48" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA48" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
@@ -5593,19 +5587,19 @@
       </c>
       <c r="AD48" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nu</t>
+          <t>High-vol penalty | Centrus Energy Earns Technical Rating Upgrade - Investor's B</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>URNM</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>URNM ETF</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5615,75 +5609,81 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>64.2778</v>
+        <v>215.1204</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>14.236692</v>
+        <v>64.89664999999999</v>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="n">
+        <v>0.28517</v>
+      </c>
       <c r="I49" s="3" t="n">
-        <v>2.81</v>
+        <v>0.43</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>78.5634208823345</v>
+        <v>68.42533645417541</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2.608201112696733</v>
+        <v>8.733465810301441</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>61.84537011605722</v>
+        <v>192.0492915400752</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>1.039330445621636</v>
+        <v>1.120131036884881</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>0.4787</v>
+        <v>0.323</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>16.08</v>
+        <v>19.76</v>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-Demand Asse (+84)</t>
+          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nuclear Deal (+80) // BWX Technologies stock hits all-time high at 239.88 USD - Investing.co (+68)</t>
         </is>
       </c>
       <c r="R49" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="n">
+        <v>7.97</v>
+      </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="n">
+        <v>124.68</v>
+      </c>
       <c r="V49" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>NO_ENTRY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="X49" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA49" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AB49" s="3" t="n">
         <v>0</v>
@@ -5695,19 +5695,19 @@
       </c>
       <c r="AD49" s="3" t="inlineStr">
         <is>
-          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-D</t>
+          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nu</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>URNM</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Cameco</t>
+          <t>URNM ETF</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5717,54 +5717,50 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>111.3796</v>
+        <v>64.3796</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>122.744896</v>
+        <v>14.259252</v>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="n">
-        <v>0.088870004</v>
-      </c>
+      <c r="H50" s="3" t="inlineStr"/>
       <c r="I50" s="3" t="n">
-        <v>0.15</v>
+        <v>2.81</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>80.08475211373326</v>
+        <v>78.69493444907802</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>4.714286138140964</v>
+        <v>2.608201112696733</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>105.5470367714211</v>
+        <v>61.84740716439706</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>1.055260610665465</v>
+        <v>1.040943047591647</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.4961</v>
+        <v>0.4788</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>31.95</v>
+        <v>16.08</v>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBeat (+92) // Cameco gains as uranium market sentiment improves amid higher term-pri (+90) // Cameco Surges 200% in a Year: Buy, Sell or Hold the Stock? - Yahoo Fin (+65)</t>
+          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-Demand Asse (+84)</t>
         </is>
       </c>
       <c r="R50" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S50" s="3" t="n">
-        <v>17.52</v>
-      </c>
+      <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -5780,40 +5776,40 @@
         </is>
       </c>
       <c r="X50" s="3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z50" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA50" s="3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AB50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD50" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=80 | Bullish news (+32) | Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBea</t>
+          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-D</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NXE</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NexGen Energy</t>
+          <t>Cameco</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5827,47 +5823,49 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>11.7176</v>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
+        <v>111.6667</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>123.06122</v>
+      </c>
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="n">
-        <v>-0.20569</v>
+        <v>0.088870004</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>75.28090541231049</v>
+        <v>80.31976083137471</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.5350529832184003</v>
+        <v>4.714286138140964</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>11.05064815945095</v>
+        <v>105.5527774669506</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.060353399752606</v>
+        <v>1.057922566639988</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.4961</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>35.51</v>
+        <v>31.95</v>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interest - Market (-94) // NexGen Energy (NXE) price target increased by 15.94% to 15.35 - MSN (+93) // NexGen Energy Up 123% This Past Year as Investor Adds $7.3 Million Bef (+92)</t>
+          <t>Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBeat (+92) // Cameco gains as uranium market sentiment improves amid higher term-pri (+90) // Cameco Surges 200% in a Year: Buy, Sell or Hold the Stock? - Yahoo Fin (+65)</t>
         </is>
       </c>
       <c r="R51" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>66.66</v>
+        <v>17.21</v>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
@@ -5884,16 +5882,16 @@
         </is>
       </c>
       <c r="X51" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA51" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB51" s="3" t="n">
         <v>0</v>
@@ -5905,19 +5903,19 @@
       </c>
       <c r="AD51" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=75 | Bullish news (+36) | NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interes</t>
+          <t>Overbought RSI=80 | Bullish news (+32) | Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBea</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>NXE</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>URA ETF</t>
+          <t>NexGen Energy</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -5927,50 +5925,52 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>51.0741</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>42.49409</v>
-      </c>
+        <v>11.7454</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="n">
+        <v>-0.20569</v>
+      </c>
       <c r="I52" s="3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>78.50404707604926</v>
+        <v>75.51670507139522</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>2.018518044204307</v>
+        <v>0.5350529832184003</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>47.39425941749855</v>
+        <v>11.05120372772217</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1.077642620868379</v>
+        <v>1.062813703220478</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>0.4303</v>
+        <v>0.5833</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>25.13</v>
+        <v>25.36</v>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Quadrupling (+93) // Uranium ETF (URA) Hits New 52-Week High - Zacks Investment Research (+78) // Disruptive Theme of the Week: Hot Themes in the New Year - ETF Trends (-29)</t>
+          <t>Why NexGen Energy (TSX:NXE) Is Down 5.7% After Rook I Licence Win And  (-96) // NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interest - Market (-94) // NexGen Energy (NXE) price target increased by 15.94% to 15.35 - MSN (+93)</t>
         </is>
       </c>
       <c r="R52" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S52" s="3" t="inlineStr"/>
+      <c r="S52" s="3" t="n">
+        <v>66.27</v>
+      </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -5986,16 +5986,16 @@
         </is>
       </c>
       <c r="X52" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y52" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA52" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AB52" s="3" t="n">
         <v>0</v>
@@ -6007,217 +6007,319 @@
       </c>
       <c r="AD52" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=79 | Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Q</t>
+          <t>Overbought RSI=76 | Why NexGen Energy (TSX:NXE) Is Down 5.7% After Rook I Licenc</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>VIE.PA</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Veolia</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Water / Environment</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>35.24</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>20.729412</v>
-      </c>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="n">
-        <v>0.1216</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>77.67180171122854</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>0.6292854036603656</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>33.3906001663208</v>
-      </c>
-      <c r="M53" s="4" t="n">
-        <v>1.055386890410295</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>0.2411</v>
-      </c>
-      <c r="O53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P53" s="4" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>Veolia unveils a next-generation integrated offering to revolutionize  (+69) // French group Veolia aims $1.2 billion in revenue from data centres, ch (+37) // Veolia Sees €1 Billion Sales to AI Industries by 2030 - Bloomberg.com (+23)</t>
-        </is>
-      </c>
-      <c r="R53" s="4" t="n">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>URA</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>URA ETF</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Uranium / Nuclear</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>51.213</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>42.60965</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>78.71915222603778</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>2.018518044204307</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>47.39703722353335</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>1.080509821594939</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Quadrupling (+93) // Uranium ETF (URA) Hits New 52-Week High - Zacks Investment Research (+78) // Disruptive Theme of the Week: Hot Themes in the New Year - ETF Trends (-29)</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S53" s="4" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>RETIREMENT (20yr+)</t>
-        </is>
-      </c>
-      <c r="U53" s="4" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="V53" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="W53" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="X53" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y53" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z53" s="4" t="n">
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>NO_ENTRY</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z53" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="AA53" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD53" s="4" t="inlineStr">
-        <is>
-          <t>Veolia unveils a next-generation integrated offering to revo</t>
+      <c r="AA53" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>Overbought RSI=79 | Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Q</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>VIE.PA</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Veolia</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Water / Environment</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>20.729412</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>77.67180171122854</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>0.6292854036603656</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>33.3906001663208</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>1.055386890410295</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>0.2411</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>Veolia unveils a next-generation integrated offering to revolutionize  (+69) // French group Veolia aims $1.2 billion in revenue from data centres, ch (+37) // Veolia Sees €1 Billion Sales to AI Industries by 2030 - Bloomberg.com (+23)</t>
+        </is>
+      </c>
+      <c r="R54" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S54" s="4" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>RETIREMENT (20yr+)</t>
+        </is>
+      </c>
+      <c r="U54" s="4" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="V54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W54" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y54" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA54" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="AD54" s="4" t="inlineStr">
+        <is>
+          <t>Veolia unveils a next-generation integrated offering to revo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>GLUG.L</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>L&amp;G Clean Water ETF</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Water / Environment</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>19.7269</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>22.824575</v>
       </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="n">
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="n">
         <v>62.01274123674997</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="K55" s="3" t="n">
         <v>0.4167793919800454</v>
       </c>
-      <c r="L54" s="3" t="n">
+      <c r="L55" s="3" t="n">
         <v>19.87497234344482</v>
       </c>
-      <c r="M54" s="3" t="n">
+      <c r="M55" s="3" t="n">
         <v>0.9925474004963003</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="N55" s="3" t="n">
         <v>0.1747</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="O55" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P54" s="3" t="n">
+      <c r="P55" s="3" t="n">
         <v>19.58</v>
       </c>
-      <c r="Q54" s="3" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>Five thematic ETFs to outperform in 2024 - ETF Stream (+76) // Water ETF demand set to soar over next two years, survey finds - ETF S (+57)</t>
         </is>
       </c>
-      <c r="R54" s="3" t="n">
+      <c r="R55" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S54" s="3" t="inlineStr"/>
-      <c r="T54" s="3" t="inlineStr">
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U54" s="3" t="n">
+      <c r="U55" s="3" t="n">
         <v>22.21</v>
       </c>
-      <c r="V54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W54" s="3" t="inlineStr">
+      <c r="V55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="X54" s="3" t="n">
+      <c r="X55" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="Y54" s="3" t="n">
+      <c r="Y55" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Z54" s="3" t="n">
+      <c r="Z55" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="AA54" s="3" t="n">
+      <c r="AA55" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="AB54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="3" t="inlineStr">
+      <c r="AB55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AD54" s="3" t="inlineStr">
+      <c r="AD55" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Five thematic ETFs to outperform in 2024 - ETF Stream (+76) </t>
         </is>
@@ -6247,7 +6349,7 @@
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -6326,10 +6428,10 @@
         <v>185.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>249.4398</v>
+        <v>249.2685</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.13</v>
+        <v>6.05</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -6340,7 +6442,7 @@
         <v>45.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.8</v>
+        <v>55.5</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>62</v>
@@ -6362,42 +6464,50 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>HEI.DE</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="4" t="n">
         <v>175.79</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>171.13</v>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>NOT SCANNED</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Symbol not in scanned universe</t>
+      <c r="D3" s="4" t="n">
+        <v>190.65</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>BUY MORE (DCA OK)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Score=76.0 | PnL=+8.5% | BUSINESS COLLATERAL (10yr)</t>
         </is>
       </c>
     </row>

--- a/outputs/market_scan.xlsx
+++ b/outputs/market_scan.xlsx
@@ -452,7 +452,7 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -684,7 +684,7 @@
         <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>6.19</v>
+        <v>5.41</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>249.2685</v>
+        <v>248.5833</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37.035076</v>
+        <v>36.928474</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
@@ -772,19 +772,19 @@
         <v>1.02</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>55.53075948789884</v>
+        <v>54.62921984751939</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>5.310841716786539</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>260.79451779966</v>
+        <v>260.7808142768012</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.9558042581172647</v>
+        <v>0.9532270813441038</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2374</v>
+        <v>0.2375</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>2</v>
@@ -801,7 +801,7 @@
         <v>8</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>27.8</v>
+        <v>28.15</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17.8426</v>
+        <v>17.8518</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21.855942</v>
+        <v>21.86717</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
@@ -1084,16 +1084,16 @@
         <v>1.47</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>65.19607591060702</v>
+        <v>65.35464324794214</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.45634943341452</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.12462965647379</v>
+        <v>17.12481297387017</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.041925774418288</v>
+        <v>1.042449859949167</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>0.2717</v>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="U6" s="3" t="n">
-        <v>72.62</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="V6" s="3" t="b">
         <v>0</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>75.8935</v>
+        <v>75.8796</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>26.114056</v>
+        <v>26.109278</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1188,16 +1188,16 @@
         <v>0.43</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>86.11887321482173</v>
+        <v>86.10590072947461</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.882606082492403</v>
+        <v>1.88293002900623</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>67.67638849329064</v>
+        <v>67.67611072681568</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.121417924586807</v>
+        <v>1.121217309756864</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.3171</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32.6111</v>
+        <v>32.6667</v>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1388,16 +1388,16 @@
         <v>3.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>18.3543651815606</v>
+        <v>18.58966834904855</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0.5062305107318531</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.86940899601689</v>
+        <v>33.87052006191677</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.9628485765791459</v>
+        <v>0.9644571585163121</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0.169</v>
@@ -1406,9 +1406,13 @@
         <v>4</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
+        <v>4.97</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>3 Best Inverse ETFs to Profit in a Market Crash - 24/7 Wall St. (+32)</t>
+        </is>
+      </c>
       <c r="R9" s="3" t="n">
         <v>8</v>
       </c>
@@ -1419,7 +1423,7 @@
         </is>
       </c>
       <c r="U9" s="3" t="n">
-        <v>-19.87</v>
+        <v>-19.73</v>
       </c>
       <c r="V9" s="3" t="b">
         <v>1</v>
@@ -1451,7 +1455,7 @@
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>Neutral backdrop</t>
+          <t xml:space="preserve">3 Best Inverse ETFs to Profit in a Market Crash - 24/7 Wall </t>
         </is>
       </c>
     </row>
@@ -1477,10 +1481,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>75.9907</v>
+        <v>75.81480000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>33.913223</v>
+        <v>33.83471</v>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="n">
@@ -1490,16 +1494,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>52.3172915525573</v>
+        <v>51.91010827564429</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>2.775793226938399</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>75.5394443935818</v>
+        <v>75.53592582985206</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.005974310086759</v>
+        <v>1.003692103310674</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.426</v>
@@ -1519,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>17.12</v>
+        <v>17.39</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
@@ -1527,7 +1531,7 @@
         </is>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-17.27</v>
+        <v>-17.46</v>
       </c>
       <c r="V10" s="3" t="b">
         <v>1</v>
@@ -1585,10 +1589,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>154.3055</v>
+        <v>153.8519</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>92.07182</v>
+        <v>91.80110999999999</v>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
@@ -1598,16 +1602,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>57.41033566914608</v>
+        <v>57.10763021150927</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>7.814815057017812</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>148.3977779812283</v>
+        <v>148.3887040879991</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.039810379934875</v>
+        <v>1.036816489423986</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0.4084</v>
@@ -1616,18 +1620,18 @@
         <v>2</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>28.28</v>
+        <v>16.87</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Nations Financial Group Inc. IA ADV Boosts Palo Alto Networks Stake -  (+91) // Can Platform Wins Accelerate Palo Alto Networks' Long-Term Growth? - Y (+50) // Exclusive | Palo Alto Networks Founder Agrees to Buy California Bank f (+45)</t>
+          <t>Can Platform Wins Accelerate Palo Alto Networks' Long-Term Growth? - Y (+50) // Exclusive | Palo Alto Networks Founder Agrees to Buy California Bank f (+45) // Palo Alto Networks founder Nir Zuk moves into U.S. banking with Libert (+21)</t>
         </is>
       </c>
       <c r="R11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>33.48</v>
+        <v>33.87</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1635,7 +1639,7 @@
         </is>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-3.98</v>
+        <v>-4.26</v>
       </c>
       <c r="V11" s="3" t="b">
         <v>1</v>
@@ -1646,7 +1650,7 @@
         </is>
       </c>
       <c r="X11" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>10</v>
@@ -1655,7 +1659,7 @@
         <v>30</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB11" s="3" t="n">
         <v>0</v>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>Nations Financial Group Inc. IA ADV Boosts Palo Alto Network</t>
+          <t>Can Platform Wins Accelerate Palo Alto Networks' Long-Term G</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1697,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>386.8657</v>
+        <v>384.3426</v>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1704,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>57.20783722103779</v>
+        <v>56.53007580878639</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>19.71699548146081</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>375.1511106137876</v>
+        <v>375.1006475377965</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.031226436644018</v>
+        <v>1.024638564941487</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0.503</v>
@@ -1733,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>26.62</v>
+        <v>27.45</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
@@ -1741,7 +1745,7 @@
         </is>
       </c>
       <c r="U12" s="3" t="n">
-        <v>6.37</v>
+        <v>5.67</v>
       </c>
       <c r="V12" s="3" t="b">
         <v>0</v>
@@ -1799,7 +1803,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.7917</v>
+        <v>12.7407</v>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1810,16 +1814,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>53.76246542174277</v>
+        <v>53.29670828714884</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.6345238635148949</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>12.46046299404568</v>
+        <v>12.45944448753639</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.026580335276889</v>
+        <v>1.022576966847387</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0.6405</v>
@@ -1828,18 +1832,18 @@
         <v>2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>7.84</v>
+        <v>-3.83</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>SentinelOne: Business Growth Quality Is Better Today, At A Cheaper Val (+92) // A Look At SentinelOne (S) Valuation After Geopolitical Jitters And AI  (-53)</t>
+          <t>A Look At SentinelOne (S) Valuation After Geopolitical Jitters And AI  (-53)</t>
         </is>
       </c>
       <c r="R13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>45.09</v>
+        <v>45.67</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -1856,7 +1860,7 @@
         </is>
       </c>
       <c r="X13" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>0</v>
@@ -1865,7 +1869,7 @@
         <v>30</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB13" s="3" t="n">
         <v>3</v>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | SentinelOne: Business Growth Quality Is Better Today, At A C</t>
+          <t>High-vol penalty | A Look At SentinelOne (S) Valuation After Geopolitical Jitte</t>
         </is>
       </c>
     </row>
@@ -1903,10 +1907,10 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>623.6759</v>
+        <v>623.9305000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>23.143766</v>
+        <v>23.14823</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="n">
@@ -1916,16 +1920,16 @@
         <v>1.36</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>40.93505104783984</v>
+        <v>41.04613549704533</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>13.9609725387008</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>655.6337280273436</v>
+        <v>655.6388199417679</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.9512566331572238</v>
+        <v>0.9516375624070509</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0.2496</v>
@@ -1945,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>18.03</v>
+        <v>17.98</v>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
@@ -1953,7 +1957,7 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>29.29</v>
+        <v>29.34</v>
       </c>
       <c r="V14" s="4" t="b">
         <v>1</v>
@@ -2138,7 +2142,7 @@
         <v>60.59192475818448</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1996.87962962963</v>
+        <v>1996.879629629629</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>1.027760904744903</v>
@@ -2333,10 +2337,10 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>327.8171</v>
+        <v>328.3056</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>41.45697</v>
+        <v>41.518738</v>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
@@ -2344,36 +2348,36 @@
         <v>1.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>54.03458243438555</v>
+        <v>54.52814086151916</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>7.890588265878173</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>328.3760342068142</v>
+        <v>328.3858026575159</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.9982980048893989</v>
+        <v>0.9997556522857353</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.2371</v>
+        <v>0.237</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>32.64</v>
+        <v>33.67</v>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>Airbus and Lakota Connector Partners Successfully Execute Fourth Auton (+91) // Australia Expands Missile Production Plans With NIOA-L3Harris Deal - T (+80) // Xoople and L3Harris team up to build satellites for ‘Earth AI’ - Space (+54)</t>
+          <t>Airbus and Lakota Connector Partners Successfully Execute Fourth Auton (+91) // Australia Expands Missile Production Plans With NIOA-L3Harris Deal - T (+80) // L3Harris investing upfront in bid for Golden Dome work - SpaceNews (+62)</t>
         </is>
       </c>
       <c r="R18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>19.63</v>
+        <v>19.45</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -2381,7 +2385,7 @@
         </is>
       </c>
       <c r="U18" s="3" t="n">
-        <v>62.98</v>
+        <v>63.22</v>
       </c>
       <c r="V18" s="3" t="b">
         <v>0</v>
@@ -2392,7 +2396,7 @@
         </is>
       </c>
       <c r="X18" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>4</v>
@@ -2401,7 +2405,7 @@
         <v>30</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB18" s="3" t="n">
         <v>0</v>
@@ -2413,7 +2417,7 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>Bullish news (+33) | Airbus and Lakota Connector Partners Successfully Execute Fo</t>
+          <t>Bullish news (+34) | Airbus and Lakota Connector Partners Successfully Execute Fo</t>
         </is>
       </c>
     </row>
@@ -2547,10 +2551,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.5926</v>
+        <v>35.4769</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>19.814432</v>
+        <v>19.749998</v>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="n">
@@ -2560,16 +2564,16 @@
         <v>4.24</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.80213518420565</v>
+        <v>39.2239769787614</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.725859869094122</v>
+        <v>1.730820237013397</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>31.86954734943531</v>
+        <v>31.86723253462049</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1.11682136337771</v>
+        <v>1.113270521428057</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0.3331</v>
@@ -2578,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>-17.01</v>
+        <v>-15.42</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
@@ -2589,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-1.9</v>
+        <v>-1.58</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -2761,10 +2765,10 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>273.9491</v>
+        <v>275.4306</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>39.98243</v>
+        <v>40.19797</v>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="n">
@@ -2774,16 +2778,16 @@
         <v>0.58</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>50.44763493001532</v>
+        <v>51.47736654711176</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>11.22036888485863</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>273.9934062251338</v>
+        <v>274.0230359677915</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.9998381669328618</v>
+        <v>1.005136488587359</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>0.4937</v>
@@ -2803,7 +2807,7 @@
         <v>8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>36.26</v>
+        <v>35.53</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
@@ -2975,10 +2979,10 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>151.2593</v>
+        <v>151.6696</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>74.935776</v>
+        <v>75.139084</v>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="n">
@@ -2988,16 +2992,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>63.54063453206661</v>
+        <v>63.93205344001822</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>6.260252251196162</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>148.2467747441044</v>
+        <v>148.2549822771991</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>1.020320746171343</v>
+        <v>1.023032306567255</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0.474</v>
@@ -3017,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>54.88</v>
+        <v>54.46</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
@@ -3187,7 +3191,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5.838</v>
+        <v>5.8194</v>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr"/>
@@ -3198,19 +3202,19 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.88853044880595</v>
+        <v>31.03446832618074</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.2870304243905203</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>5.832870359773988</v>
+        <v>5.832499989756831</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>1.000873059733742</v>
+        <v>0.9977615625168624</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.6311</v>
+        <v>0.631</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>3</v>
@@ -3227,7 +3231,7 @@
         <v>8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
@@ -3503,10 +3507,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>105.0741</v>
+        <v>105.213</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.758999</v>
+        <v>17.782473</v>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
@@ -3516,16 +3520,16 @@
         <v>0.92</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>68.6378010593737</v>
+        <v>68.76149650057005</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>4.258597338641133</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>106.617143701624</v>
+        <v>106.6199213663737</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.9855270319040205</v>
+        <v>0.9868039581298549</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>0.3699</v>
@@ -3545,7 +3549,7 @@
         <v>8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.35</v>
+        <v>33.17</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
@@ -3609,10 +3613,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>198.3333</v>
+        <v>198.75</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.203388</v>
+        <v>24.254236</v>
       </c>
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="n">
@@ -3622,16 +3626,16 @@
         <v>0.84</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>78.28025962624062</v>
+        <v>78.72746537079672</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>7.117065550788998</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>197.7548943978769</v>
+        <v>197.7632276746961</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.002925015390977</v>
+        <v>1.004989636776781</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0.3636</v>
@@ -3640,18 +3644,18 @@
         <v>2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>24.07</v>
+        <v>18.11</v>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>Agnico-Eagle Mines Ltd. stock falls Monday, underperforms market - Mar (-95) // Agnico Eagle's Fair Value Estimate Raised as We Increase our Assumed N (+92) // Agnico Eagle Mines Limited (TSE:AEM) Given Consensus Rating of "Modera (+84)</t>
+          <t>Agnico-Eagle Mines Ltd. stock falls Monday, underperforms market - Mar (-95) // Agnico Eagle's Fair Value Estimate Raised as We Increase our Assumed N (+92) // AGNICO EAGLE ANNOUNCES FINANCING AND STRATEGIC ALLIANCE WITH CASCADIA  (+50)</t>
         </is>
       </c>
       <c r="R30" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28.25</v>
+        <v>27.98</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
@@ -3668,7 +3672,7 @@
         </is>
       </c>
       <c r="X30" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>16</v>
@@ -3677,7 +3681,7 @@
         <v>17</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB30" s="3" t="n">
         <v>0</v>
@@ -3821,10 +3825,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>90.4722</v>
+        <v>90.61109999999999</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>20.132454</v>
+        <v>20.16336</v>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
@@ -3832,16 +3836,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>78.37036178861214</v>
+        <v>78.61633959735559</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.470238175972428</v>
+        <v>3.473545256115141</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>91.03574046382195</v>
+        <v>91.03851826985675</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.993809913705989</v>
+        <v>0.9953052114453533</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.3575</v>
@@ -3897,7 +3901,7 @@
       </c>
       <c r="AD32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overbought RSI=78 | Gold miners' bull run squeezed as prices plummet and energy </t>
+          <t xml:space="preserve">Overbought RSI=79 | Gold miners' bull run squeezed as prices plummet and energy </t>
         </is>
       </c>
     </row>
@@ -3923,10 +3927,10 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43.3611</v>
+        <v>43.3556</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>97.56251</v>
+        <v>97.55</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
@@ -3936,16 +3940,16 @@
         <v>1.78</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>74.05691041927068</v>
+        <v>74.04660374842399</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>1.902949873101774</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46.34623379177517</v>
+        <v>46.34612267105668</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0.9355908616295633</v>
+        <v>0.9354732234738371</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>0.4829</v>
@@ -3954,7 +3958,7 @@
         <v>2</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>15.87</v>
+        <v>25.74</v>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3969,7 @@
         <v>8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>51.06</v>
+        <v>51.08</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -3982,7 +3986,7 @@
         </is>
       </c>
       <c r="X33" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>7</v>
@@ -3991,7 +3995,7 @@
         <v>10</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB33" s="3" t="n">
         <v>0</v>
@@ -4029,10 +4033,10 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>481.3009</v>
+        <v>481.2037</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>29.2683</v>
+        <v>29.262388</v>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="n">
@@ -4042,16 +4046,16 @@
         <v>0.33</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63.68901850649745</v>
+        <v>63.62993834193329</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.18650624108692</v>
+        <v>13.21362490376466</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>466.5089303475838</v>
+        <v>466.5069862648293</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1.031707836301519</v>
+        <v>1.031503769877817</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0.2663</v>
@@ -4071,7 +4075,7 @@
         <v>8</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>34.98</v>
+        <v>35.01</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
@@ -4347,10 +4351,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>351.1389</v>
+        <v>351.1945</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>20.258015</v>
+        <v>20.261219</v>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="n">
@@ -4360,16 +4364,16 @@
         <v>1.59</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>68.86123377492311</v>
+        <v>68.88496060889463</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>8.746029081798724</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>339.2722687897858</v>
+        <v>339.2733798556857</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.034976717413299</v>
+        <v>1.035137070010604</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0.3238</v>
@@ -4389,7 +4393,7 @@
         <v>8</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>14.79</v>
+        <v>14.77</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4673,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.5926</v>
+        <v>21.5741</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
@@ -4680,19 +4684,19 @@
         <v>1.74</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>60.28707413492297</v>
+        <v>60.19183714448482</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>1.110449796000485</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>21.33380815717909</v>
+        <v>21.33343777833161</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>1.012130237177381</v>
+        <v>1.011279738025226</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0.5242</v>
+        <v>0.5241</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>2</v>
@@ -4709,7 +4713,7 @@
         <v>8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
@@ -4875,7 +4879,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>194.4352</v>
+        <v>194.0278</v>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr"/>
@@ -4886,25 +4890,25 @@
         <v>0.87</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>74.61507477316596</v>
+        <v>74.45918597477285</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>9.242724867724871</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>159.7324676513672</v>
+        <v>159.7243194580078</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.217255283977853</v>
+        <v>1.214766675869232</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.5422</v>
+        <v>0.5421</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-12.94</v>
+        <v>-11.87</v>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
@@ -4915,7 +4919,7 @@
         <v>8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>-2.11</v>
+        <v>-1.91</v>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
@@ -4953,7 +4957,7 @@
       </c>
       <c r="AD42" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=75 | Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (</t>
+          <t>Weak structure | Overbought RSI=74 | Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (</t>
         </is>
       </c>
     </row>
@@ -4979,10 +4983,10 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>232.2594</v>
+        <v>231.9907</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>22.517065</v>
+        <v>22.489227</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
@@ -4992,16 +4996,16 @@
         <v>2.75</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>58.39290103456753</v>
+        <v>58.17077704656935</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>5.97156040252201</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>232.57691277398</v>
+        <v>232.5715405499494</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.9986346107951281</v>
+        <v>0.9975027168752738</v>
       </c>
       <c r="N43" s="2" t="n">
         <v>0.2506</v>
@@ -5021,7 +5025,7 @@
         <v>8</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>30.62</v>
+        <v>30.77</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
@@ -5029,7 +5033,7 @@
         </is>
       </c>
       <c r="U43" s="2" t="n">
-        <v>6.8</v>
+        <v>6.68</v>
       </c>
       <c r="V43" s="2" t="b">
         <v>0</v>
@@ -5087,7 +5091,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>18.1667</v>
+        <v>18.3194</v>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
@@ -5098,19 +5102,19 @@
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>74.88061763851279</v>
+        <v>75.27033779176521</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>1.204365018814328</v>
+        <v>1.215939042429444</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>14.85509259612472</v>
+        <v>14.85814813331321</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.222925224207206</v>
+        <v>1.232956095119662</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.2711</v>
+        <v>1.2712</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>2</v>
@@ -5127,7 +5131,7 @@
         <v>8</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -5191,7 +5195,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>41.2872</v>
+        <v>41.4748</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
@@ -5202,16 +5206,16 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>77.54966551461843</v>
+        <v>77.71829805493245</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.713624384037401</v>
+        <v>2.739285791992511</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>30.73592966574209</v>
+        <v>30.73968156178792</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1.34328849974398</v>
+        <v>1.349227238019905</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0.9896</v>
@@ -5231,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>58.14</v>
+        <v>57.42</v>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -5295,7 +5299,7 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>20.537</v>
+        <v>20.4444</v>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr"/>
@@ -5306,16 +5310,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>75.28542656394569</v>
+        <v>75.11832266817295</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>1.396428655695032</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>16.19425909607498</v>
+        <v>16.19240723715888</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>1.268167762277237</v>
+        <v>1.262594503359902</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>1.3077</v>
@@ -5335,7 +5339,7 @@
         <v>8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>78.97</v>
+        <v>79.78</v>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -5343,7 +5347,7 @@
         </is>
       </c>
       <c r="U46" s="3" t="n">
-        <v>220.52</v>
+        <v>219.08</v>
       </c>
       <c r="V46" s="3" t="b">
         <v>0</v>
@@ -5430,11 +5434,11 @@
         <v>7</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>1.52</v>
+        <v>-1.09</v>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>Samsung asks court to block illegal strike activities by unions - Reut (-73) // Samsung hikes Galaxy Book 6 prices by up to $600 as base model goes on (+65)</t>
+          <t>Two Samsung washers at Lowe’s are marked down by up to $300 during thi (-94) // Samsung hikes Galaxy Book 6 prices by up to $600 as base model goes on (+65)</t>
         </is>
       </c>
       <c r="R47" s="3" t="n">
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AD47" s="3" t="inlineStr">
         <is>
-          <t>Samsung asks court to block illegal strike activities by uni</t>
+          <t xml:space="preserve">Two Samsung washers at Lowe’s are marked down by up to $300 </t>
         </is>
       </c>
     </row>
@@ -5507,10 +5511,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>186.4074</v>
+        <v>186.5556</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>51.620514</v>
+        <v>51.661537</v>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="n">
@@ -5520,16 +5524,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>54.10222747363354</v>
+        <v>54.17731809482795</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>12.48115055144778</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>187.9581485324435</v>
+        <v>187.9611112806532</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.9917495764059175</v>
+        <v>0.9925220718716581</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.8539</v>
@@ -5549,7 +5553,7 @@
         <v>8</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>49.51</v>
+        <v>49.39</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
@@ -5613,10 +5617,10 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>215.1204</v>
+        <v>215.1852</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>64.89664999999999</v>
+        <v>64.9162</v>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="n">
@@ -5626,16 +5630,16 @@
         <v>0.43</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>68.42533645417541</v>
+        <v>68.49018726269837</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>8.733465810301441</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>192.0492915400752</v>
+        <v>192.050587689435</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>1.120131036884881</v>
+        <v>1.120460927106132</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>0.323</v>
@@ -5655,7 +5659,7 @@
         <v>8</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>7.97</v>
+        <v>7.94</v>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
@@ -5663,7 +5667,7 @@
         </is>
       </c>
       <c r="U49" s="3" t="n">
-        <v>124.68</v>
+        <v>124.75</v>
       </c>
       <c r="V49" s="3" t="b">
         <v>0</v>
@@ -5721,10 +5725,10 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>64.3796</v>
+        <v>64.3056</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>14.259252</v>
+        <v>14.242845</v>
       </c>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
@@ -5732,19 +5736,19 @@
         <v>2.81</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>78.69493444907802</v>
+        <v>78.59944730659737</v>
       </c>
       <c r="K50" s="3" t="n">
         <v>2.608201112696733</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>61.84740716439706</v>
+        <v>61.84592564900715</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>1.040943047591647</v>
+        <v>1.039770236358104</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.4788</v>
+        <v>0.4787</v>
       </c>
       <c r="O50" s="3" t="n">
         <v>4</v>
@@ -5823,10 +5827,10 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>111.6667</v>
+        <v>111.5648</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>123.06122</v>
+        <v>122.948975</v>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="n">
@@ -5836,16 +5840,16 @@
         <v>0.15</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>80.31976083137471</v>
+        <v>80.23700706039912</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>4.714286138140964</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>105.5527774669506</v>
+        <v>105.5507404186107</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.057922566639988</v>
+        <v>1.056978022080767</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>0.4961</v>
@@ -5865,7 +5869,7 @@
         <v>8</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>17.21</v>
+        <v>17.34</v>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
@@ -5929,7 +5933,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>11.7454</v>
+        <v>11.7685</v>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr"/>
@@ -5940,16 +5944,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>75.51670507139522</v>
+        <v>75.70978810072852</v>
       </c>
       <c r="K52" s="3" t="n">
         <v>0.5350529832184003</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>11.05120372772217</v>
+        <v>11.05166668362088</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1.062813703220478</v>
+        <v>1.064863688956646</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>0.5833</v>
@@ -5958,18 +5962,18 @@
         <v>2</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>25.36</v>
+        <v>35.51</v>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>Why NexGen Energy (TSX:NXE) Is Down 5.7% After Rook I Licence Win And  (-96) // NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interest - Market (-94) // NexGen Energy (NXE) price target increased by 15.94% to 15.35 - MSN (+93)</t>
+          <t>NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interest - Market (-94) // NexGen Energy (NXE) price target increased by 15.94% to 15.35 - MSN (+93) // NexGen Energy Up 123% This Past Year as Investor Adds $7.3 Million Bef (+92)</t>
         </is>
       </c>
       <c r="R52" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>66.27</v>
+        <v>65.98</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
@@ -5986,7 +5990,7 @@
         </is>
       </c>
       <c r="X52" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y52" s="3" t="n">
         <v>0</v>
@@ -5995,7 +5999,7 @@
         <v>17</v>
       </c>
       <c r="AA52" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB52" s="3" t="n">
         <v>0</v>
@@ -6007,7 +6011,7 @@
       </c>
       <c r="AD52" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=76 | Why NexGen Energy (TSX:NXE) Is Down 5.7% After Rook I Licenc</t>
+          <t>Overbought RSI=76 | Bullish news (+36) | NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interes</t>
         </is>
       </c>
     </row>
@@ -6033,10 +6037,10 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>51.213</v>
+        <v>51.1759</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>42.60965</v>
+        <v>42.578835</v>
       </c>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
@@ -6044,16 +6048,16 @@
         <v>4.4</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>78.71915222603778</v>
+        <v>78.66221218804957</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>2.018518044204307</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>47.39703722353335</v>
+        <v>47.39629646583839</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>1.080509821594939</v>
+        <v>1.079745257874041</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>0.4303</v>
@@ -6428,10 +6432,10 @@
         <v>185.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>249.2685</v>
+        <v>248.5833</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.05</v>
+        <v>5.76</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -6442,7 +6446,7 @@
         <v>45.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.5</v>
+        <v>54.6</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>62</v>
@@ -6459,7 +6463,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Score=62.0 | PnL=+6.1% | BUSINESS COLLATERAL (10yr)</t>
+          <t>Score=62.0 | PnL=+5.8% | BUSINESS COLLATERAL (10yr)</t>
         </is>
       </c>
     </row>

--- a/outputs/market_scan.xlsx
+++ b/outputs/market_scan.xlsx
@@ -451,9 +451,9 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -653,49 +653,51 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>515.7406999999999</v>
+        <v>508.3333</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10.975369</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+        <v>10.819865</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2.5338</v>
+      </c>
       <c r="H2" s="2" t="n">
         <v>0.17412001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>58.57663390111972</v>
+        <v>54.76190010415657</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>20.80688072890832</v>
+        <v>20.07936750139509</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>468.6722225613063</v>
+        <v>470.5907411928529</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1.100429502568348</v>
+        <v>1.080202581216984</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2833</v>
+        <v>0.2834</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>5.41</v>
+        <v>-4.02</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Fertilizer Maker Yara Warns Farmers Are Being Squeezed by Price Surge  (-94) // Yara increases productivity, plant uptime, and safety with a digital t (+85) // Yara International (OB:YAR) Valuation Check After Strong Recent Shareh (+66)</t>
+          <t>Fertilizer Maker Yara Warns Farmers Are Being Squeezed by Price Surge  (-94) // Yara increases productivity, plant uptime, and safety with a digital t (+85) // Yara International ASA (OTCMKTS:YARIY) Shares Gap Down - Here's What H (-81)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>-2.6</v>
+        <v>0.12</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
@@ -712,10 +714,10 @@
         </is>
       </c>
       <c r="X2" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>30</v>
@@ -759,29 +761,31 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>248.5833</v>
+        <v>249.287</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>36.928474</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>37.033012</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2.4853</v>
+      </c>
       <c r="H3" s="2" t="n">
         <v>0.22516</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54.62921984751939</v>
+        <v>55.5555631210155</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5.310841716786539</v>
+        <v>5.348540613890955</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>260.7808142768012</v>
+        <v>260.7948885317202</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.9532270813441038</v>
+        <v>0.9558739767219117</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0.2375</v>
@@ -790,18 +794,18 @@
         <v>2</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45.54</v>
+        <v>26.3</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Ecolab's Earnings Beat Last Year's by 19% - AOL.com (+92) // Lbp Am Sa Boosts Stake in Ecolab Inc. $ECL - MarketBeat (+92) // Ecolab (ECL) Valuation Check As Shares Move Without A Clear News Catal (-86)</t>
+          <t>Lbp Am Sa Boosts Stake in Ecolab Inc. $ECL - MarketBeat (+92) // Ecolab (ECL) Valuation Check As Shares Move Without A Clear News Catal (-86) // Global Green Floor Care Chemical Systems for Commercial Facilities Mar (+80)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>28.15</v>
+        <v>27.79</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
@@ -818,16 +822,16 @@
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="2" t="n">
         <v>23</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>0</v>
@@ -839,7 +843,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>Bullish news (+46) | Ecolab's Earnings Beat Last Year's by 19% - AOL.com (+92) //</t>
+          <t>Lbp Am Sa Boosts Stake in Ecolab Inc. $ECL - MarketBeat (+92</t>
         </is>
       </c>
     </row>
@@ -865,10 +869,12 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>40.69</v>
+        <v>40.32</v>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="n">
+        <v>4.6465</v>
+      </c>
       <c r="H4" s="3" t="n">
         <v>-0.123739995</v>
       </c>
@@ -876,36 +882,32 @@
         <v>0.27</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>73.40030545424113</v>
+        <v>67.95430675083327</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.026071003505162</v>
+        <v>1.007856641496931</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>41.24719985961914</v>
+        <v>41.15059982299805</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.986491174314704</v>
+        <v>0.9798156009451501</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.3198</v>
+        <v>0.3197</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Bayer Aktiengesellschaft (ETR:BAYN) Stock Price Down 0.4% - What's Nex (-95) // Bayer wins MHRA approval for Kerendia in heart failure - PharmaTimes (+91) // Bayer CEO says AI is powerful tool in drug development - Semafor (+68)</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>14.34</v>
+        <v>18</v>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
@@ -922,40 +924,40 @@
         </is>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overbought RSI=73 | Bayer Aktiengesellschaft (ETR:BAYN) Stock Price Down 0.4% - </t>
+          <t>Neutral backdrop</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>EIMI.L</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>EM IMI (EIMI)</t>
+          <t>Global Clean Energy</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -969,40 +971,40 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>47.3889</v>
+        <v>17.9167</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>17.642792</v>
+        <v>21.946678</v>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>69.8058135926041</v>
+        <v>66.49999618530268</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.164199435521684</v>
+        <v>0.45634943341452</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>44.95999986154061</v>
+        <v>17.12611113654242</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.054023338910109</v>
+        <v>1.046160852106706</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.1804</v>
+        <v>0.2716</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-14.36</v>
+        <v>35.14</v>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Trump tariffs blow headwinds at emerging market ETFs - ETF Stream (-90) // Emerging markets ETFs battered by China woes to start 2024 - ETF Strea (-66)</t>
+          <t>Global fossil power fell in March 2026 despite continued Hormuz blocka (-96) // Global Clean Energy Inc. (GCEI) Accelerates AI Division Growth with Fl (+91) // India steadily positioning itself as global player in clean energy: Un (+86)</t>
         </is>
       </c>
       <c r="R5" s="3" t="n">
@@ -1015,7 +1017,7 @@
         </is>
       </c>
       <c r="U5" s="3" t="n">
-        <v>51.51</v>
+        <v>73.33</v>
       </c>
       <c r="V5" s="3" t="b">
         <v>0</v>
@@ -1026,16 +1028,16 @@
         </is>
       </c>
       <c r="X5" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>23</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="3" t="n">
         <v>0</v>
@@ -1047,19 +1049,19 @@
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>Trump tariffs blow headwinds at emerging market ETFs - ETF S</t>
+          <t>Bullish news (+35) | Global fossil power fell in March 2026 despite continued Hor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>EIMI.L</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Global Clean Energy</t>
+          <t>EM IMI (EIMI)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1073,40 +1075,40 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17.8518</v>
+        <v>47.4259</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21.86717</v>
+        <v>17.65658</v>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>65.35464324794214</v>
+        <v>79.97784609152308</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.45634943341452</v>
+        <v>1.098061869384118</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.12481297387017</v>
+        <v>45.00777767322681</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.042449859949167</v>
+        <v>1.053727366868376</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.2717</v>
+        <v>0.1804</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>23.36</v>
+        <v>-15.17</v>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Global fossil power fell in March 2026 despite continued Hormuz blocka (-96) // Global Clean Energy Inc. (GCEI) Accelerates AI Division Growth with Fl (+91) // Envision Energy Secures $500M Financing Program with BBVA to Accelerat (+69)</t>
+          <t>Trump tariffs blow headwinds at emerging market ETFs - ETF Stream (-90) // Emerging markets ETFs battered by China woes to start 2024 - ETF Strea (-66)</t>
         </is>
       </c>
       <c r="R6" s="3" t="n">
@@ -1119,7 +1121,7 @@
         </is>
       </c>
       <c r="U6" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>50.87</v>
       </c>
       <c r="V6" s="3" t="b">
         <v>0</v>
@@ -1130,28 +1132,28 @@
         </is>
       </c>
       <c r="X6" s="3" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AB6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>Global fossil power fell in March 2026 despite continued Hor</t>
+          <t>Overbought RSI=80 | Trump tariffs blow headwinds at emerging market ETFs - ETF S</t>
         </is>
       </c>
     </row>
@@ -1177,10 +1179,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>75.8796</v>
+        <v>76.21299999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>26.109278</v>
+        <v>26.223972</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1188,29 +1190,29 @@
         <v>0.43</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>86.10590072947461</v>
+        <v>86.41070774357806</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.88293002900623</v>
+        <v>1.905423623544198</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>67.67611072681568</v>
+        <v>67.68277740478516</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.121217309756864</v>
+        <v>1.126031815251916</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.3171</v>
+        <v>0.317</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>25.6</v>
+        <v>26.43</v>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Lithium ETF (LIT) Hits New 52-Week High - September 26, 2025 - Zacks I (+79) // Lithium &amp; battery ETF (LIT) hits new 52-week high - MSN (+78) // Best Lithium &amp; Battery Tech ETFs to Buy in 2026 - The Motley Fool (+23)</t>
+          <t>Lithium &amp; battery ETF (LIT) hits new 52-week high - MSN (+85) // Lithium ETF (LIT) Hits New 52-Week High - September 26, 2025 - Zacks I (+79) // Best Lithium &amp; Battery Tech ETFs to Buy in 2026 - The Motley Fool (+23)</t>
         </is>
       </c>
       <c r="R7" s="3" t="n">
@@ -1253,7 +1255,7 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=86 | Lithium ETF (LIT) Hits New 52-Week High - September 26, 2025</t>
+          <t>Overbought RSI=86 | Lithium &amp; battery ETF (LIT) hits new 52-week high - MSN (+85</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1281,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>115.315</v>
+        <v>115.35</v>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1288,16 +1290,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>71.19408582861701</v>
+        <v>78.75226950393748</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.372856685093471</v>
+        <v>1.297499520438058</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>112.0801000976563</v>
+        <v>112.1283000183105</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.028862414834849</v>
+        <v>1.028732250959699</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>0.1417</v>
@@ -1306,7 +1308,7 @@
         <v>4</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.01</v>
+        <v>10.44</v>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1348,12 +1350,12 @@
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best Irish Domiciled World ETFs – VWRA/VWRD vs IWDA/IWDD vs </t>
+          <t xml:space="preserve">Weak structure | Overbought RSI=79 | Best Irish Domiciled World ETFs – VWRA/VWRD vs IWDA/IWDD vs </t>
         </is>
       </c>
     </row>
@@ -1379,7 +1381,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32.6667</v>
+        <v>32.5926</v>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1388,16 +1390,16 @@
         <v>3.92</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>18.58966834904855</v>
+        <v>18.27724408420232</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.5062305107318531</v>
+        <v>0.50595273416509</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.87052006191677</v>
+        <v>33.86903861716942</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.9644571585163121</v>
+        <v>0.9623123250535864</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0.169</v>
@@ -1423,7 +1425,7 @@
         </is>
       </c>
       <c r="U9" s="3" t="n">
-        <v>-19.73</v>
+        <v>-19.92</v>
       </c>
       <c r="V9" s="3" t="b">
         <v>1</v>
@@ -1481,12 +1483,14 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>75.81480000000001</v>
+        <v>76.2963</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>33.83471</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
+        <v>34.049587</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2.0003</v>
+      </c>
       <c r="H10" s="3" t="n">
         <v>1.3571601</v>
       </c>
@@ -1494,19 +1498,19 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>51.91010827564429</v>
+        <v>53.00834877137329</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>2.775793226938399</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>75.53592582985206</v>
+        <v>75.54555553860133</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.003692103310674</v>
+        <v>1.009937608707665</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.426</v>
+        <v>0.4263</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>2</v>
@@ -1523,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>17.39</v>
+        <v>16.65</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1535,7 @@
         </is>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-17.46</v>
+        <v>-16.94</v>
       </c>
       <c r="V10" s="3" t="b">
         <v>1</v>
@@ -1542,10 +1546,10 @@
         </is>
       </c>
       <c r="X10" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>30</v>
@@ -1589,12 +1593,14 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>153.8519</v>
+        <v>154.6019</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>91.80110999999999</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+        <v>92.761116</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2.8003</v>
+      </c>
       <c r="H11" s="3" t="n">
         <v>0.16259001</v>
       </c>
@@ -1602,36 +1608,36 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>57.10763021150927</v>
+        <v>57.60573354069241</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>7.814815057017812</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>148.3887040879991</v>
+        <v>148.4037040427879</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.036816489423986</v>
+        <v>1.041765459826781</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.4084</v>
+        <v>0.4086</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>16.87</v>
+        <v>24.59</v>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Can Platform Wins Accelerate Palo Alto Networks' Long-Term Growth? - Y (+50) // Exclusive | Palo Alto Networks Founder Agrees to Buy California Bank f (+45) // Palo Alto Networks founder Nir Zuk moves into U.S. banking with Libert (+21)</t>
+          <t>Palo Alto Networks completes $400 million acquisition of Koi - CTech (+69) // CrowdStrike, Palo Alto Networks shares pop as cybersecurity bulls fina (+62) // Exclusive | Palo Alto Networks Founder Agrees to Buy California Bank f (+45)</t>
         </is>
       </c>
       <c r="R11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>33.87</v>
+        <v>33.22</v>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
@@ -1639,7 +1645,7 @@
         </is>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-4.26</v>
+        <v>-3.79</v>
       </c>
       <c r="V11" s="3" t="b">
         <v>1</v>
@@ -1650,28 +1656,28 @@
         </is>
       </c>
       <c r="X11" s="3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>30</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>Can Platform Wins Accelerate Palo Alto Networks' Long-Term G</t>
+          <t>Palo Alto Networks completes $400 million acquisition of Koi</t>
         </is>
       </c>
     </row>
@@ -1697,10 +1703,12 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>384.3426</v>
+        <v>387.2222</v>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="n">
+        <v>3.4491</v>
+      </c>
       <c r="H12" s="3" t="n">
         <v>-0.04137</v>
       </c>
@@ -1708,36 +1716,36 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>56.53007580878639</v>
+        <v>57.30189631904128</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>19.71699548146081</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>375.1006475377965</v>
+        <v>375.1582404242621</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.024638564941487</v>
+        <v>1.032157078802598</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.503</v>
+        <v>0.5032</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-4.49</v>
+        <v>15.16</v>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>Palo Alto (PANW), CrowdStrike (CRWD), and Akamai (AKAM) Slide after An (-90) // Why CrowdStrike (CRWD) Stock Is Up Today - TradingView — Track All Mar (+40) // CrowdStrike among favorites; 'turbulent' week ahead for markets: Wedbu (+28)</t>
+          <t>CrowdStrike Holdings (CRWD) Surpasses Market Returns: Some Facts Worth (+64) // CrowdStrike, Palo Alto Networks shares pop as cybersecurity bulls fina (+62) // Is the Software Selloff Nearing an End? What the Oracle, CrowdStrike a (-21)</t>
         </is>
       </c>
       <c r="R12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>27.45</v>
+        <v>26.51</v>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
@@ -1745,7 +1753,7 @@
         </is>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.67</v>
+        <v>6.47</v>
       </c>
       <c r="V12" s="3" t="b">
         <v>0</v>
@@ -1756,16 +1764,16 @@
         </is>
       </c>
       <c r="X12" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>30</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB12" s="3" t="n">
         <v>0</v>
@@ -1777,7 +1785,7 @@
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>Palo Alto (PANW), CrowdStrike (CRWD), and Akamai (AKAM) Slid</t>
+          <t>CrowdStrike Holdings (CRWD) Surpasses Market Returns: Some F</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1811,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.7407</v>
+        <v>12.8981</v>
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1814,25 +1822,25 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>53.29670828714884</v>
+        <v>54.70693238094658</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.6345238635148949</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>12.45944448753639</v>
+        <v>12.46259263709739</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.022576966847387</v>
+        <v>1.034949051638293</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.6405</v>
+        <v>0.6407</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-3.83</v>
+        <v>-2.37</v>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
@@ -1843,7 +1851,7 @@
         <v>8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>45.67</v>
+        <v>43.89</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -1886,110 +1894,112 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>NOC</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Northrop Grumman</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>RHM.DE</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Rheinmetall</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>623.9305000000001</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>23.14823</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>0.26167</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>41.04613549704533</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>13.9609725387008</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>655.6388199417679</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.9516375624070509</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.2496</v>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1509.6</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>67.66473000000001</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.7514</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.23336</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>56.46067229113085</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>68.28571428571429</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>1576.459997558594</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0.9575885071132791</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="O14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P14" s="4" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>DAF increases B-21 Raider production capacity to deliver combat capabi (+93) // Navy MQ-4C Triton suffers Class A mishap - Breaking Defense (-81) // Missile Defense Agency awards Northrop Grumman contract modification t (+71)</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="n">
+      <c r="P14" s="3" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>Rheinmetall wins €300mn drone order from German armed forces - Financi (+88) // German defense giant Rheinmetall aims to build “defense ecosystem” in  (+79) // Rheinmetall to Establish Joint Venture with Cruise Missile Manufacture (+72)</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S14" s="4" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>RETIREMENT (20yr+)</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>29.34</v>
-      </c>
-      <c r="V14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
+      <c r="S14" s="3" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="X14" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="Y14" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z14" s="4" t="n">
+      <c r="X14" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="AA14" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AA14" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>DAF increases B-21 Raider production capacity to deliver com</t>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>Bullish news (+51) | Rheinmetall wins €300mn drone order from German armed forces</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2025,14 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>57.98</v>
+        <v>58.82</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>27.349058</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+        <v>27.745285</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1.4625</v>
+      </c>
       <c r="H15" s="3" t="n">
         <v>0.12741</v>
       </c>
@@ -2028,25 +2040,25 @@
         <v>1.09</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>47.76439991156985</v>
+        <v>50.50718069317866</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.789999553135463</v>
+        <v>2.748570850917271</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>58.32359992980957</v>
+        <v>58.42599990844727</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.9941087246331374</v>
+        <v>1.006743569421051</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.3534</v>
+        <v>0.3533</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>6.17</v>
+        <v>8.69</v>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
@@ -2057,7 +2069,7 @@
         <v>8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>18.68</v>
+        <v>16.99</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2077,7 @@
         </is>
       </c>
       <c r="U15" s="3" t="n">
-        <v>26.08</v>
+        <v>31.24</v>
       </c>
       <c r="V15" s="3" t="b">
         <v>0</v>
@@ -2076,16 +2088,16 @@
         </is>
       </c>
       <c r="X15" s="3" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB15" s="3" t="n">
         <v>0</v>
@@ -2102,216 +2114,220 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>BA.L</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>BAE Systems</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>NOC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Northrop Grumman</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>2052.3148</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>32.59559</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="n">
-        <v>0.18141001</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>55.4156171284635</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>60.59192475818448</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>1996.879629629629</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>1.027760904744903</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0.2557</v>
-      </c>
-      <c r="O16" s="2" t="n">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>622.9352</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>23.151068</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>5.1031</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.26167</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>40.61525091761327</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>13.97221479466351</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>655.618913438585</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.9501483110096842</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="P16" s="2" t="n">
-        <v>43.68</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>BAE Systems awarded $180m contract for Tridon Mk2 from Sweden - BAE Sy (+92) // Norwegian Armed Forces upgrade enterprise simulation capabilities with (+75) // BAE Systems Adds Highly Maneuverable Ascent Spacecraft to Elevation Pr (+68)</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="n">
+      <c r="P16" s="4" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Navy MQ-4C Triton suffers Class A mishap - Breaking Defense (-81) // US Awards Northrop $475M for Hypersonic Glide Phase Interceptor Design (+80) // Missile Defense Agency awards Northrop Grumman contract modification t (+71)</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="S16" s="2" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>BUSINESS COLLATERAL (10yr)</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr"/>
-      <c r="V16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>NO_ENTRY</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA16" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="S16" s="4" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>RETIREMENT (20yr+)</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="V16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>Bullish news (+44) | BAE Systems awarded $180m contract for Tridon Mk2 from Swede</t>
+      <c r="X16" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navy MQ-4C Triton suffers Class A mishap - Breaking Defense </t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>RHM.DE</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Rheinmetall</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BA.L</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BAE Systems</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>1497.2</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>67.229454</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="n">
-        <v>0.23336</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>50.88036465621244</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>70.17142159598214</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>1579.857998046875</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0.9476800782240002</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.4179</v>
-      </c>
-      <c r="O17" s="3" t="n">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2087.037</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>33.14706</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>3.5332</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.18141001</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>64.02439024390245</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>59.26917343543315</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2003.907407407407</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1.041483767823974</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="O17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>Rheinmetall wins €300mn drone order from German armed forces - Financi (+88) // Rheinmetall to Establish Joint Venture with Cruise Missile Manufacture (+72) // Ukraine's Ruta Developer Partners with Rheinmetall to Co-Produce HIMAR (+66)</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n">
+      <c r="P17" s="2" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>BAE Systems awarded $180m contract for Tridon Mk2 from Sweden - BAE Sy (+92) // Norwegian Armed Forces upgrade enterprise simulation capabilities with (+75) // BAE Systems Adds Highly Maneuverable Ascent Spacecraft to Elevation Pr (+68)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>36.54</v>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z17" s="3" t="n">
+      <c r="S17" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>NO_ENTRY</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z17" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="AA17" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="3" t="inlineStr">
+      <c r="AA17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>Bullish news (+52) | Rheinmetall wins €300mn drone order from German armed forces</t>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>Bullish news (+44) | BAE Systems awarded $180m contract for Tridon Mk2 from Swede</t>
         </is>
       </c>
     </row>
@@ -2337,47 +2353,49 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>328.3056</v>
+        <v>327.2315</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>41.518738</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+        <v>41.480045</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>2.2402</v>
+      </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>54.52814086151916</v>
+        <v>53.45442263280644</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>7.890588265878173</v>
+        <v>7.891534875940384</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>328.3858026575159</v>
+        <v>328.3643211082176</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.9997556522857353</v>
+        <v>0.9965500629542491</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.237</v>
+        <v>0.2371</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>33.67</v>
+        <v>30.6</v>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>Airbus and Lakota Connector Partners Successfully Execute Fourth Auton (+91) // Australia Expands Missile Production Plans With NIOA-L3Harris Deal - T (+80) // L3Harris investing upfront in bid for Golden Dome work - SpaceNews (+62)</t>
+          <t>Australia Expands Missile Production Plans With NIOA-L3Harris Deal - T (+80) // L3Harris investing upfront in bid for Golden Dome work - SpaceNews (+62) // Joby and L3Harris to demonstrate autonomous S-4T rotorcraft for US Arm (+53)</t>
         </is>
       </c>
       <c r="R18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>19.45</v>
+        <v>19.84</v>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
@@ -2385,7 +2403,7 @@
         </is>
       </c>
       <c r="U18" s="3" t="n">
-        <v>63.22</v>
+        <v>62.69</v>
       </c>
       <c r="V18" s="3" t="b">
         <v>0</v>
@@ -2396,16 +2414,16 @@
         </is>
       </c>
       <c r="X18" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>30</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB18" s="3" t="n">
         <v>0</v>
@@ -2417,7 +2435,7 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>Bullish news (+34) | Airbus and Lakota Connector Partners Successfully Execute Fo</t>
+          <t>Bullish news (+31) | Australia Expands Missile Production Plans With NIOA-L3Harri</t>
         </is>
       </c>
     </row>
@@ -2443,49 +2461,51 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>58.1</v>
+        <v>57.22</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>13.511627</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+        <v>13.306976</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>6.8527</v>
+      </c>
       <c r="H19" s="2" t="n">
         <v>0.089940004</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>55.87044393727681</v>
+        <v>56.21181903572842</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.368570872715541</v>
+        <v>1.372856412615095</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>55.10700004577637</v>
+        <v>55.17580009460449</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.05431249071549</v>
+        <v>1.037048871472523</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2576</v>
+        <v>0.2577</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>16.16</v>
+        <v>38.09</v>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>RWE withdraws 99.9 MW solar-plus-storage project in UK on grid constra (-91) // Wind power fuels semiconductor innovation: RWE deepens cooperation wit (+79) // RWE to provide 65% of Network Rail's non-traction electricity from win (+63)</t>
+          <t>RWE and Indiana Michigan Power Company partner to support Indiana’s gr (+84) // Wind power fuels semiconductor innovation: RWE deepens cooperation wit (+79) // RWE to provide 65% of Network Rail's non-traction electricity from win (+63)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>3.48</v>
+        <v>5.07</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
@@ -2493,7 +2513,7 @@
         </is>
       </c>
       <c r="U19" s="2" t="n">
-        <v>76.15000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="V19" s="2" t="b">
         <v>0</v>
@@ -2504,28 +2524,28 @@
         </is>
       </c>
       <c r="X19" s="2" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>RWE withdraws 99.9 MW solar-plus-storage project in UK on gr</t>
+          <t>Bullish news (+38) | RWE and Indiana Michigan Power Company partner to support In</t>
         </is>
       </c>
     </row>
@@ -2551,49 +2571,51 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>35.4769</v>
+        <v>35.4352</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>19.749998</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+        <v>19.726803</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>3.4021</v>
+      </c>
       <c r="H20" s="2" t="n">
         <v>0.12206</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.24</v>
+        <v>4.08</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>39.2239769787614</v>
+        <v>39.01312054964545</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1.730820237013397</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>31.86723253462049</v>
+        <v>31.86639923519558</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1.113270521428057</v>
+        <v>1.111992144060733</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3331</v>
+        <v>0.3332</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>-15.42</v>
+        <v>7.07</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Equinor Cuts Scatec Stake as Capital Discipline Trumps Renewables Expa (-89) // Equinor Signals Trading Windfall as War-Driven Volatility Lifts Result (-88) // Equinor Trading Profits to Beat Forecast as War Spurs Volatility - Blo (+85)</t>
+          <t>Equinor Trading Unit Set to Beat Guidance as Mideast Turmoil Fuels Bre (+91) // Equinor Signals Trading Windfall as War-Driven Volatility Lifts Result (-88) // Equinor Trading Profits to Beat Forecast as War Spurs Volatility - Blo (+85)</t>
         </is>
       </c>
       <c r="R20" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>-1.58</v>
+        <v>1.26</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
@@ -2610,16 +2632,16 @@
         </is>
       </c>
       <c r="X20" s="2" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>0</v>
@@ -2631,7 +2653,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>Equinor Cuts Scatec Stake as Capital Discipline Trumps Renew</t>
+          <t>Equinor Trading Unit Set to Beat Guidance as Mideast Turmoil</t>
         </is>
       </c>
     </row>
@@ -2657,77 +2679,77 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>166.94</v>
+        <v>165.72</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>77.64651000000001</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
+        <v>77.07906</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1.0029</v>
+      </c>
       <c r="H21" s="3" t="n">
         <v>0.20254</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>56.82327118308493</v>
+        <v>63.95683301210301</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.905713762555804</v>
+        <v>7.474285670689174</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>156.3077221679688</v>
+        <v>156.6667254638672</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1.06802146513281</v>
+        <v>1.057786844845519</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.5094</v>
+        <v>0.5093</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>19.31</v>
+        <v>50.88</v>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>Siemens Energy Expands Operations in Charlotte, Creating More Jobs - C (+90) // Siemens Energy is investing $1 billion and creating highly skilled job (+66) // First US state passes data centre ban over power fears – but the reali (-46)</t>
+          <t>Siemens Energy Expands Operations in Charlotte, Creating More Jobs - C (+90) // Siemens Energy Commits $1 Billion to Expanding U.S. Turbine and Grid P (+81) // Siemens Energy's Growing Role in the Reconstruction of Syria - Energy  (+70)</t>
         </is>
       </c>
       <c r="R21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1.34</v>
+        <v>2.09</v>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>190.46</v>
-      </c>
+      <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>NO_ENTRY</t>
         </is>
       </c>
       <c r="X21" s="3" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AB21" s="3" t="n">
         <v>0</v>
@@ -2739,19 +2761,19 @@
       </c>
       <c r="AD21" s="3" t="inlineStr">
         <is>
-          <t>Siemens Energy Expands Operations in Charlotte, Creating Mor</t>
+          <t>Bullish news (+51) | Siemens Energy Expands Operations in Charlotte, Creating Mor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>TE.PA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Technip Energies</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2761,199 +2783,201 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>275.4306</v>
+        <v>39.98</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>40.19797</v>
+        <v>19.59804</v>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>0.16364</v>
+        <v>0.16753</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.58</v>
+        <v>2.52</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>51.47736654711176</v>
+        <v>69.9822206803842</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>11.22036888485863</v>
+        <v>1.374285561697824</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>274.0230359677915</v>
+        <v>34.98959972381592</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>1.005136488587359</v>
+        <v>1.142625233149599</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.4937</v>
+        <v>0.3534</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-2.32</v>
+        <v>25.54</v>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>Constellation Energy Is Down 28% From Its 52-Week High. Here's What Is (-96) // Constellation Energy Is Down 28% From Its 52-Week High. Here's What Is (-96) // TMI’s owner proposes workaround to ‘27 restart barrier; federal approv (+68)</t>
+          <t>Technip Energies awarded two FEED contracts by SOGARA for refinery com (+92) // Assessing Technip Energies (ENXTPA:TE) Valuation After New LNG And Ste (+39) // Technip Energies Secures FEED Contracts for Gabon Refinery Revamp &amp; Ex (+36)</t>
         </is>
       </c>
       <c r="R22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>35.53</v>
+        <v>5.21</v>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="n">
+        <v>39.55</v>
+      </c>
       <c r="V22" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>NO_ENTRY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="X22" s="3" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AB22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AD22" s="3" t="inlineStr">
         <is>
-          <t>Constellation Energy Is Down 28% From Its 52-Week High. Here</t>
+          <t>Technip Energies awarded two FEED contracts by SOGARA for re</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>TE.PA</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Technip Energies</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ENI.MI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Eni</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>39.62</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>19.421568</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="n">
-        <v>0.16753</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>72.47555318500551</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>1.455714362008231</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>34.84079975128174</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>1.137172487851035</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>0.3533</v>
-      </c>
-      <c r="O23" s="3" t="n">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>30.012821</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0.9647</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0.050869998</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>48.41379709504379</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.8564285550798688</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>21.18299022674561</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1.105131976025495</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="O23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>Technip Energies awarded two FEED contracts by SOGARA for refinery com (+92) // Assessing Technip Energies (ENXTPA:TE) Valuation After New LNG And Ste (+39) // Technip Energies Secures FEED Contracts for Gabon Refinery Revamp &amp; Ex (+36)</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="n">
+      <c r="P23" s="2" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Eni CEO Calls for Suspending EU Ban on Russian LNG - Crude Oil Prices  (-57) // Kazakhstan hires Chinese firm to replace Shell and Eni as Ukrainian st (+28) // EU should reconsider its plans to ban imports of Russian gas, Eni CEO  (-26)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="V23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="Y23" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3" t="inlineStr">
+      <c r="S23" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>NO_ENTRY</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>Technip Energies awarded two FEED contracts by SOGARA for re</t>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>Eni CEO Calls for Suspending EU Ban on Russian LNG - Crude O</t>
         </is>
       </c>
     </row>
@@ -2979,49 +3003,51 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>151.6696</v>
+        <v>153.2685</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>75.139084</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
+        <v>75.93119</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>1.4226</v>
+      </c>
       <c r="H24" s="3" t="n">
         <v>0.17656</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>63.93205344001822</v>
+        <v>65.38013023711244</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>6.260252251196162</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>148.2549822771991</v>
+        <v>148.2869598953812</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>1.023032306567255</v>
+        <v>1.033594036160504</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.474</v>
+        <v>0.4743</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>25.76</v>
+        <v>18.27</v>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>Amazon and Meta agreements boost Vistra nuclear plants - World Nuclear (+92) // Vistra CEO wants to help United Way connect more people with high-payi (+68) // Vistra and Meta Announce Agreements to Support Nuclear Plants in PJM a (+47)</t>
+          <t>Amazon and Meta agreements boost Vistra nuclear plants - World Nuclear (+92) // Vistra Names Chief AI And Digital Officer As Valuation Gap Persists -  (-89) // Vistra Corp. stock outperforms competitors on strong trading day - Mar (+84)</t>
         </is>
       </c>
       <c r="R24" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>54.46</v>
+        <v>52.84</v>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
@@ -3038,16 +3064,16 @@
         </is>
       </c>
       <c r="X24" s="3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>23</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB24" s="3" t="n">
         <v>0</v>
@@ -3064,108 +3090,108 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ENI.MI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Eni</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CEG</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Constellation Energy</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>23.405</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>30.006413</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="n">
-        <v>0.050869998</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>51.46009261714099</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>0.8685714176722935</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>21.06228260040283</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>1.111228119510554</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0.2313</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>Is Eni Positioned to Gain From the Ongoing Strength in Crude Prices? - (+86) // Eni CEO Calls for Suspending EU Ban on Russian LNG - Crude Oil Prices  (-57) // Kazakhstan hires Chinese firm to replace Shell and Eni as Ukrainian st (+28)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>276.9815</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>40.479027</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>0.16364</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>52.51049709526055</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>11.22036888485863</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>274.0540548253942</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>1.010681981046843</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>-11.55</v>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>Constellation Energy Is Down 28% From Its 52-Week High. Here's What Is (-96) // Constellation Energy Is Down 28% From Its 52-Week High. Here's What Is (-96) // Constellation to ask regulators for help speeding up Three Mile Island (+52)</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S25" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>BUSINESS COLLATERAL (10yr)</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="S25" s="3" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
         <is>
           <t>NO_ENTRY</t>
         </is>
       </c>
-      <c r="X25" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y25" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z25" s="2" t="n">
+      <c r="X25" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AA25" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AA25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AD25" s="2" t="inlineStr">
-        <is>
-          <t>Is Eni Positioned to Gain From the Ongoing Strength in Crude</t>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>Constellation Energy Is Down 28% From Its 52-Week High. Here</t>
         </is>
       </c>
     </row>
@@ -3191,10 +3217,12 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>5.8194</v>
+        <v>5.8796</v>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="n">
+        <v>1.1687</v>
+      </c>
       <c r="H26" s="3" t="n">
         <v>-0.31697</v>
       </c>
@@ -3202,36 +3230,36 @@
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.03446832618074</v>
+        <v>33.73493006862438</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.2870304243905203</v>
+        <v>0.2870370155919796</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>5.832499989756831</v>
+        <v>5.833703694520173</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.9977615625168624</v>
+        <v>1.007872502480614</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0.631</v>
+        <v>0.6314</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>49.31</v>
+        <v>44.99</v>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>Transocean Adds Major Ultra-Deepwater Contract, Boosting Backlog - Tip (+93) // Transocean wins five-well contract for Deepwater Asgard in Eastern Med (+91) // Transocean wins $158 million drillship contract for Eastern Mediterran (+89)</t>
+          <t>Transocean Adds Major Ultra-Deepwater Contract, Boosting Backlog - Tip (+93) // Transocean wins $158 million drillship contract for Eastern Mediterran (+89) // Transocean Ltd. Announces $425 Million Additional Backlog for Ultra-De (+68)</t>
         </is>
       </c>
       <c r="R26" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.62</v>
+        <v>0.58</v>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
@@ -3248,16 +3276,16 @@
         </is>
       </c>
       <c r="X26" s="3" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>30</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB26" s="3" t="n">
         <v>3</v>
@@ -3269,7 +3297,7 @@
       </c>
       <c r="AD26" s="3" t="inlineStr">
         <is>
-          <t>Bullish news (+49) | High-vol penalty | Transocean Adds Major Ultra-Deepwater Contract, Boosting Bac</t>
+          <t>Bullish news (+45) | High-vol penalty | Transocean Adds Major Ultra-Deepwater Contract, Boosting Bac</t>
         </is>
       </c>
     </row>
@@ -3295,29 +3323,31 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>23.24</v>
+        <v>23.48</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>7.1950464</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+        <v>7.2693496</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>14.7462</v>
+      </c>
       <c r="H27" s="2" t="n">
         <v>0.13647</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>67.51593001524665</v>
+        <v>78.44038262491611</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.6042857851300921</v>
+        <v>0.567857197352818</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>24.57879985809326</v>
+        <v>24.55359985351562</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.9455302905469463</v>
+        <v>0.9562752379413084</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0.3443</v>
@@ -3326,18 +3356,18 @@
         <v>2</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>3.14</v>
+        <v>14.16</v>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Vonovia shares hit 2-year low in 2025 results as cash flow misses esti (-96) // Vonovia (ETR:VNA) Is Posting Solid Earnings, But It Is Not All Good Ne (+90) // Vonovia Swings to Net Profit on Rental Business Strength - WSJ (+24)</t>
+          <t>Vonovia (ETR:VNA) Is Posting Solid Earnings, But It Is Not All Good Ne (+90) // Vonovia Swings to Net Profit on Rental Business Strength - WSJ (+24)</t>
         </is>
       </c>
       <c r="R27" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>45.61</v>
+        <v>44.12</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
@@ -3354,16 +3384,16 @@
         </is>
       </c>
       <c r="X27" s="2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>0</v>
@@ -3375,7 +3405,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>Vonovia shares hit 2-year low in 2025 results as cash flow m</t>
+          <t>Vonovia (ETR:VNA) Is Posting Solid Earnings, But It Is Not A</t>
         </is>
       </c>
     </row>
@@ -3401,29 +3431,31 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>45.2</v>
+        <v>45.24</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11.832461</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
+        <v>11.842933</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>2.8379</v>
+      </c>
       <c r="H28" s="3" t="n">
         <v>0.07574</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>75.23291039836036</v>
+        <v>78.97997443689377</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1.799494753932079</v>
+        <v>1.754023127798506</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>38.95906784057618</v>
+        <v>39.01941413879395</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1.160192049458209</v>
+        <v>1.159422884145465</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0.3874</v>
@@ -3432,18 +3464,18 @@
         <v>9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>34.76</v>
+        <v>32.96</v>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>Raiffeisen Takeover Target Addiko Gets Higher Offer From Slovenia’s NL (+93) // Raiffeisen Bank International (OTCMKTS:RAIFY) Sets New 52-Week High -  (+71) // NLB Joins Raiffeisen in Bidding Battle for Balkans Lender Addiko - Blo (+53)</t>
+          <t>Garanti BBVA Reaches Agreement to Sell Its Romanian Unit - BBVA (+76) // Raiffeisen Bank International (OTCMKTS:RAIFY) Sets New 52-Week High -  (+71) // Austria’s Raiffeisen offers to buy smaller peer Addiko for $524 millio (+51)</t>
         </is>
       </c>
       <c r="R28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
@@ -3460,16 +3492,16 @@
         </is>
       </c>
       <c r="X28" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB28" s="3" t="n">
         <v>0</v>
@@ -3481,7 +3513,7 @@
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=75 | Bullish news (+35) | Raiffeisen Takeover Target Addiko Gets Higher Offer From Slo</t>
+          <t>Weak structure | Overbought RSI=79 | Bullish news (+33) | Garanti BBVA Reaches Agreement to Sell Its Romanian Unit - B</t>
         </is>
       </c>
     </row>
@@ -3507,12 +3539,14 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>105.213</v>
+        <v>105.0093</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>17.782473</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
+        <v>17.775862</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>2.7807</v>
+      </c>
       <c r="H29" s="3" t="n">
         <v>0.22343999</v>
       </c>
@@ -3520,36 +3554,36 @@
         <v>0.92</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>68.76149650057005</v>
+        <v>68.5797385465292</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>4.258597338641133</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>106.6199213663737</v>
+        <v>106.6158474109791</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.9868039581298549</v>
+        <v>0.9849310885774345</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.3699</v>
+        <v>0.37</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-49.77</v>
+        <v>-50.03</v>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>Why Newmont Corporation Stock Dropped Today - The Motley Fool (-94) // Newmont suspends operations at Cadia gold mine after earthquake (NEM:N (-87) // Why Newmont Shares Are Sinking Hard Today - TipRanks (-86)</t>
+          <t>Why Newmont Corporation CHESS Shares Are Sliding - TipRanks (-94) // National Bank cuts Newmont stock rating on cost pressures - Investing. (-93) // Newmont suspends operations at Cadia gold mine after earthquake (NEM:N (-87)</t>
         </is>
       </c>
       <c r="R29" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>33.17</v>
+        <v>33.43</v>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
@@ -3566,10 +3600,10 @@
         </is>
       </c>
       <c r="X29" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>23</v>
@@ -3582,12 +3616,12 @@
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD29" s="3" t="inlineStr">
         <is>
-          <t>Bearish news (-50) | Why Newmont Corporation Stock Dropped Today - The Motley Foo</t>
+          <t xml:space="preserve">Bearish news (-50) | Why Newmont Corporation CHESS Shares Are Sliding - TipRanks </t>
         </is>
       </c>
     </row>
@@ -3613,12 +3647,14 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>198.75</v>
+        <v>199.0093</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>24.254236</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
+        <v>24.258465</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>28.1515</v>
+      </c>
       <c r="H30" s="3" t="n">
         <v>0.19578</v>
       </c>
@@ -3626,36 +3662,36 @@
         <v>0.84</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>78.72746537079672</v>
+        <v>78.85304590312873</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>7.117065550788998</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>197.7632276746961</v>
+        <v>197.7684128372757</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.004989636776781</v>
+        <v>1.006274205382436</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.3636</v>
+        <v>0.3637</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>18.11</v>
+        <v>37.95</v>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>Agnico-Eagle Mines Ltd. stock falls Monday, underperforms market - Mar (-95) // Agnico Eagle's Fair Value Estimate Raised as We Increase our Assumed N (+92) // AGNICO EAGLE ANNOUNCES FINANCING AND STRATEGIC ALLIANCE WITH CASCADIA  (+50)</t>
+          <t>Agnico-Eagle Mines Ltd. stock falls Monday, underperforms market - Mar (-95) // Agnico Eagle's Fair Value Estimate Raised as We Increase our Assumed N (+92) // Agnico Eagle Mines Limited (NYSE:AEM) Short Interest Up 24.7% in March (+92)</t>
         </is>
       </c>
       <c r="R30" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>27.98</v>
+        <v>27.81</v>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
@@ -3672,16 +3708,16 @@
         </is>
       </c>
       <c r="X30" s="3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB30" s="3" t="n">
         <v>0</v>
@@ -3693,7 +3729,7 @@
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>Agnico-Eagle Mines Ltd. stock falls Monday, underperforms ma</t>
+          <t>Bullish news (+38) | Agnico-Eagle Mines Ltd. stock falls Monday, underperforms ma</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3755,14 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>20.59322</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
+        <v>20.135593</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.2326</v>
+      </c>
       <c r="H31" s="3" t="n">
         <v>0.12798001</v>
       </c>
@@ -3732,16 +3770,16 @@
         <v>2.06</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>83.61856497503426</v>
+        <v>78.80182964747908</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.9738756866051401</v>
+        <v>0.9923942505367214</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>23.19327707643862</v>
+        <v>23.10887739393446</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.9701086750018471</v>
+        <v>0.9520150995176473</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0.3983</v>
@@ -3750,18 +3788,18 @@
         <v>4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-20.76</v>
+        <v>8.73</v>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>Investigation reveals inaccurate reporting, writer terminated - northe (-92) // NIU students involved in car accident on Lucinda, Annie Glidden Road - (-56) // Opinion: Beef between Gen Z and other generations is getting old - nor (-39)</t>
+          <t>Comic book TV heats up with a wave of sring releases - northernstar.in (+60) // An evening of culture with ‘Healing Through Heritage: Honoring Arab Am (+22)</t>
         </is>
       </c>
       <c r="R31" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>23.59</v>
+        <v>26.4</v>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
@@ -3778,28 +3816,28 @@
         </is>
       </c>
       <c r="X31" s="3" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AB31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD31" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=84 | Investigation reveals inaccurate reporting, writer terminate</t>
+          <t>Strong fundamentals | Comic book TV heats up with a wave of sring releases - north</t>
         </is>
       </c>
     </row>
@@ -3825,10 +3863,10 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>90.61109999999999</v>
+        <v>90.4259</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>20.16336</v>
+        <v>20.122152</v>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
@@ -3836,29 +3874,29 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>78.61633959735559</v>
+        <v>78.22551303089159</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.473545256115141</v>
+        <v>3.483465991953693</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>91.03851826985675</v>
+        <v>91.03481462266707</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.9953052114453533</v>
+        <v>0.9933115115527733</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>0.3575</v>
+        <v>0.3576</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-3.42</v>
+        <v>26.18</v>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>Gold miners' bull run squeezed as prices plummet and energy costs soar (-87) // Gold Soared 50% This Year. Here’s Which ETF to Buy Before Rates Fall - (+33) // VanEck Gold Miners ETF Appears To Have Peaked (NYSEARCA:GDX) - Seeking (+25)</t>
+          <t>VanEck trims Endeavour Mining holding to 7.995% from 8.013% - Stock Ti (+85) // Gold Miners Surge as ETFs Sell — And Why It’s Still Bullish - Investin (+68) // Gold Soared 50% This Year. Here’s Which ETF to Buy Before Rates Fall - (+33)</t>
         </is>
       </c>
       <c r="R32" s="3" t="n">
@@ -3880,7 +3918,7 @@
         </is>
       </c>
       <c r="X32" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>10</v>
@@ -3889,7 +3927,7 @@
         <v>17</v>
       </c>
       <c r="AA32" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AB32" s="3" t="n">
         <v>0</v>
@@ -3901,7 +3939,7 @@
       </c>
       <c r="AD32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overbought RSI=79 | Gold miners' bull run squeezed as prices plummet and energy </t>
+          <t xml:space="preserve">Overbought RSI=78 | VanEck trims Endeavour Mining holding to 7.995% from 8.013% </t>
         </is>
       </c>
     </row>
@@ -3927,49 +3965,49 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43.3556</v>
+        <v>43.1852</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>97.55</v>
+        <v>97.166664</v>
       </c>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="n">
         <v>0.020380002</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>74.04660374842399</v>
+        <v>73.72653175287616</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1.902949873101774</v>
+        <v>1.902976364055008</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46.34612267105668</v>
+        <v>46.34271522804543</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0.9354732234738371</v>
+        <v>0.9318656536963176</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.4829</v>
+        <v>0.4828</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>25.74</v>
+        <v>25.35</v>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>Barrick's Fair Value Increased as We Raise Our Assumed Near-Term Gold  (+93) // Why Barrick Mining Stock Keeps Going Down - The Motley Fool (-87) // Barrick Gold (TSX:ABX) Rally Sparks Buzz In S&amp;PTSX Composite Index - K (+56)</t>
+          <t>Barrick's Fair Value Increased as We Raise Our Assumed Near-Term Gold  (+93) // Why Barrick Mining Stock Keeps Going Down - The Motley Fool (-87) // Barrick Gold's Dividend Surge and Institutional Bet Signal a High-Stak (+70)</t>
         </is>
       </c>
       <c r="R33" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>51.08</v>
+        <v>51.67</v>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
@@ -4033,49 +4071,51 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>481.2037</v>
+        <v>477.7778</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>29.262388</v>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+        <v>29.070423</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1.9108</v>
+      </c>
       <c r="H34" s="2" t="n">
         <v>0.13024001</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63.62993834193329</v>
+        <v>61.61546502151531</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.21362490376466</v>
+        <v>13.54365071291645</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>466.5069862648293</v>
+        <v>466.4384675202546</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1.031503769877817</v>
+        <v>1.024310409726296</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2663</v>
+        <v>0.2665</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>21.42</v>
+        <v>32.08</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (TMO) Earnings Expected to Grow: Should You B (+66) // Thermo Fisher Introduces PowerFlex Thermal Cycler To Simplify Complex  (+32) // Thermo Fisher Scientific Launches Applied Biosystems™ PowerFlex™ Therm (+30)</t>
+          <t>Assetmark Inc. Raises Position in Thermo Fisher Scientific Inc. $TMO - (+89) // Thermo Fisher Scientific Inc. stock rises Monday, outperforms market - (+88) // Thermo Fisher Scientific (TMO) Earnings Expected to Grow: Should You B (+66)</t>
         </is>
       </c>
       <c r="R34" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>35.01</v>
+        <v>35.69</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
@@ -4092,10 +4132,10 @@
         </is>
       </c>
       <c r="X34" s="2" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Z34" s="2" t="n">
         <v>23</v>
@@ -4113,7 +4153,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific (TMO) Earnings Expected to Grow: Sh</t>
+          <t>Bullish news (+32) | Assetmark Inc. Raises Position in Thermo Fisher Scientific I</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4179,14 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>228</v>
+        <v>228.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>101.78571</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
+        <v>102.421524</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.9666</v>
+      </c>
       <c r="H35" s="3" t="n">
         <v>0.05934</v>
       </c>
@@ -4152,16 +4194,16 @@
         <v>0.32</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>63.44049681044316</v>
+        <v>62.14388320714121</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>8.605301087922831</v>
+        <v>8.29999760219029</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>222.403537902832</v>
+        <v>222.1162673950195</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.025163547981027</v>
+        <v>1.028290257958863</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0.4467</v>
@@ -4181,29 +4223,27 @@
         <v>8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>15.44</v>
+        <v>15.24</v>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U35" s="3" t="n">
-        <v>6.91</v>
-      </c>
+      <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>NO_ENTRY</t>
         </is>
       </c>
       <c r="X35" s="3" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>23</v>
@@ -4216,7 +4256,7 @@
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AD35" s="3" t="inlineStr">
@@ -4247,29 +4287,31 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>14388.8889</v>
+        <v>14398.1481</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>13.773665</v>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
+        <v>13.801979</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.3708</v>
+      </c>
       <c r="H36" s="3" t="n">
         <v>0.05085</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>41.03312713665908</v>
+        <v>41.78082191780819</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>419.1082685177172</v>
+        <v>402.1164021164021</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>14442.11568648727</v>
+        <v>14447.25130208333</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.9963144736717363</v>
+        <v>0.996601211337128</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0.386</v>
@@ -4278,11 +4320,11 @@
         <v>2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>32.81</v>
+        <v>30.89</v>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>AP Moller Maersk : Maersk Expands Brazil Footprint with Additional Dep (+92) // Maersk Expands Brazil Footprint with Additional Depots in Rio Grande a (+92) // Maersk gets sustainability rating upgrade weeks after defeating activi (+91)</t>
+          <t>A.P. Moller-Maersk (OTCMKTS:AMKBY) Short Interest Down 31.2% in March  (-96) // AP Moller Maersk : Maersk Expands Brazil Footprint with Additional Dep (+92) // Maersk Expands Brazil Footprint with Additional Depots in Rio Grande a (+92)</t>
         </is>
       </c>
       <c r="R36" s="3" t="n">
@@ -4304,10 +4346,10 @@
         </is>
       </c>
       <c r="X36" s="3" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>30</v>
@@ -4325,221 +4367,225 @@
       </c>
       <c r="AD36" s="3" t="inlineStr">
         <is>
-          <t>Bullish news (+33) | AP Moller Maersk : Maersk Expands Brazil Footprint with Addi</t>
+          <t>Bullish news (+31) | Strong fundamentals | A.P. Moller-Maersk (OTCMKTS:AMKBY) Short Interest Down 31.2%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>FDX</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>FedEx</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>HLAG.DE</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Hapag-Lloyd</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Logistics / Shipping</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>351.1945</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>20.261219</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="n">
-        <v>0.15869</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>68.88496060889463</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>8.746029081798724</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>339.2733798556857</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>1.035137070010604</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>0.3238</v>
-      </c>
-      <c r="O37" s="2" t="n">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>22.928709</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.6312</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>37.62575069716091</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>5.750000544956753</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>128.1860002136231</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0.9283385065583253</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0.5246</v>
+      </c>
+      <c r="O37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P37" s="2" t="n">
-        <v>-16.37</v>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>On This Day: 8 killed at FedEx facility in Indiana's deadliest shootin (-81) // Commentary: FedEx and UPS need to move up the e-commerce food chain -  (+78) // FedEx CFO John Dietrich resigns - FreightWaves (-74)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n">
+      <c r="P37" s="3" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>Zim strike halts operations as takeover tensions escalate - CTech (-91) // Hapag-Zim deal could ignite another merger wave in container shipping  (-23)</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S37" s="2" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>BUSINESS COLLATERAL (10yr)</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr"/>
-      <c r="V37" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>NO_ENTRY</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y37" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z37" s="2" t="n">
+      <c r="S37" s="3" t="n">
+        <v>-15.97</v>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="V37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z37" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="AA37" s="2" t="n">
+      <c r="AA37" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="AB37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AB37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="AD37" s="2" t="inlineStr">
-        <is>
-          <t>On This Day: 8 killed at FedEx facility in Indiana's deadlie</t>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zim strike halts operations as takeover tensions escalate - </t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>HLAG.DE</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Hapag-Lloyd</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FedEx</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Logistics / Shipping</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>118.4</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>22.857143</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="n">
-        <v>0.04758</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>32.55395498355222</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>6.700000217982701</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>128.1900001525879</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>0.9236289990244505</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>0.5246</v>
-      </c>
-      <c r="O38" s="3" t="n">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>352.6667</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>20.32444</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1.3464</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>69.50083046759963</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>8.817458783507968</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>339.3028242323133</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1.039386194281501</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="O38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="P38" s="3" t="n">
-        <v>-33.37</v>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>Zim CEO Eli Glickman to step down months after $4.2 billion sale - CTe (-89) // Zim chief executive Glickman to step down amid Hapag-Lloyd takeover -  (-77) // ZIM CEO Eli Glickman steps down amid ZIM’s strategic shift and Hapag-L (-70)</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n">
+      <c r="P38" s="2" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>On This Day: 8 killed at FedEx facility in Indiana's deadliest shootin (-81) // Commentary: FedEx and UPS need to move up the e-commerce food chain -  (+78) // Thief intercepts $25K silver bar delivery from FedEx in Rockville - WJ (-65)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>-15.54</v>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>-9.56</v>
-      </c>
-      <c r="V38" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
+      <c r="S38" s="2" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>BUSINESS COLLATERAL (10yr)</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>NO_ENTRY</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="X38" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA38" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bearish news (-33) | Zim CEO Eli Glickman to step down months after $4.2 billion </t>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>On This Day: 8 killed at FedEx facility in Indiana's deadlie</t>
         </is>
       </c>
     </row>
@@ -4565,49 +4611,51 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>190.65</v>
+        <v>189.1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>17.052773</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+        <v>16.929276</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>2.0098</v>
+      </c>
       <c r="H39" s="2" t="n">
         <v>0.11068</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>58.38565348898506</v>
+        <v>58.38566946917938</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6.246426173618862</v>
+        <v>6.203569684709821</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>186.7429998779297</v>
+        <v>186.255</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1.020921769603726</v>
+        <v>1.015274790494299</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.3043</v>
+        <v>0.3042</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>36.71</v>
+        <v>10.02</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials Posts Higher Earnings, Revenue - WSJ (+93) // Is Heidelberg Materials (XTRA:HEI) Offering Value After Recent Share P (+69) // Heidelberg Materials (ETR:HEI) Stock Crosses Above Fifty Day Moving Av (+53)</t>
+          <t>Heidelberg Materials (ETR:HEI) Stock Crosses Above Fifty Day Moving Av (+53) // Heidelberg Materials to Close Paderborn Cement Plant - WSJ (-33) // Could a Donald Trump executive order benefit a historic Lehigh Valley  (+28)</t>
         </is>
       </c>
       <c r="R39" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>18.4</v>
+        <v>19.37</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
@@ -4615,7 +4663,7 @@
         </is>
       </c>
       <c r="U39" s="2" t="n">
-        <v>17.51</v>
+        <v>19.16</v>
       </c>
       <c r="V39" s="2" t="b">
         <v>0</v>
@@ -4626,16 +4674,16 @@
         </is>
       </c>
       <c r="X39" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y39" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="AA39" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>0</v>
@@ -4647,7 +4695,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>Bullish news (+37) | Heidelberg Materials Posts Higher Earnings, Revenue - WSJ (+</t>
+          <t>Heidelberg Materials (ETR:HEI) Stock Crosses Above Fifty Day</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4721,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.5741</v>
+        <v>21.4907</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
@@ -4681,19 +4729,19 @@
         <v>-0.02507</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>60.19183714448482</v>
+        <v>59.75756564109902</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>1.110449796000485</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>21.33343777833161</v>
+        <v>21.33177110883924</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>1.011279738025226</v>
+        <v>1.00745220747869</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0.5241</v>
@@ -4702,7 +4750,7 @@
         <v>2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>14.24</v>
+        <v>13.76</v>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
@@ -4713,7 +4761,7 @@
         <v>8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>29.9</v>
+        <v>30.13</v>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
@@ -4730,13 +4778,13 @@
         </is>
       </c>
       <c r="X40" s="3" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>23</v>
@@ -4777,7 +4825,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>5.2778</v>
+        <v>5.463</v>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr"/>
@@ -4788,29 +4836,29 @@
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>22.2221515795007</v>
+        <v>46.15386308299844</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.1988096842690122</v>
+        <v>0.238492217644182</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6.029629610202931</v>
+        <v>6.00833331214057</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.8753070988375015</v>
+        <v>0.9092310242222343</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0.6058</v>
+        <v>0.606</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>27.44</v>
+        <v>10.69</v>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>Zinnwald Lithium plc receives strong support from German Federal Gover (+90) // Zinnwald Lithium advances flagship German project with strong study re (+86) // Plans for German lithium mining prompt local protests - dw.com (-63)</t>
+          <t>ZNWLF Stock Crashes 99.375% on Apr 17, 2026 – Lithium Miner Hits Botto (-93) // Zinnwald Lithium plc receives strong support from German Federal Gover (+90) // Zinnwald Lithium advances flagship German project with strong study re (+86)</t>
         </is>
       </c>
       <c r="R41" s="3" t="n">
@@ -4832,16 +4880,16 @@
         </is>
       </c>
       <c r="X41" s="3" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AA41" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB41" s="3" t="n">
         <v>3</v>
@@ -4853,7 +4901,7 @@
       </c>
       <c r="AD41" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | Zinnwald Lithium plc receives strong support from German Fed</t>
+          <t xml:space="preserve">High-vol penalty | ZNWLF Stock Crashes 99.375% on Apr 17, 2026 – Lithium Miner </t>
         </is>
       </c>
     </row>
@@ -4879,47 +4927,49 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>194.0278</v>
+        <v>199.6481</v>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="n">
+        <v>1.6803</v>
+      </c>
       <c r="H42" s="3" t="n">
         <v>-0.04656</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>74.45918597477285</v>
+        <v>76.45394404113829</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>9.242724867724871</v>
+        <v>9.542989983129756</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>159.7243194580078</v>
+        <v>159.8367267184787</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>1.214766675869232</v>
+        <v>1.249075526794707</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.5421</v>
+        <v>0.5438</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-11.87</v>
+        <v>-0.76</v>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (+83) // ACPS: AHS student in critical condition, incident under investigation  (-62) // Honduran woman now charged in Albemarle County sexual exploitation cas (-59)</t>
+          <t>Albemarle Stock Is Surging. Demand for EVs, Specialty Chemicals Fuels  (+90) // Albemarle soars to nearly three-year high as lithium rebound sparks mo (+89) // Albemarle student critically injured in overnight shooting - WVIR (-80)</t>
         </is>
       </c>
       <c r="R42" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>-1.91</v>
+        <v>-4.67</v>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
@@ -4936,16 +4986,16 @@
         </is>
       </c>
       <c r="X42" s="3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AA42" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB42" s="3" t="n">
         <v>0</v>
@@ -4957,7 +5007,7 @@
       </c>
       <c r="AD42" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=74 | Why Albemarle Stock Is Suddenly Climbing Higher - TipRanks (</t>
+          <t>Weak structure | Overbought RSI=76 | Albemarle Stock Is Surging. Demand for EVs, Specialty Chemic</t>
         </is>
       </c>
     </row>
@@ -4983,49 +5033,49 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>231.9907</v>
+        <v>232.4074</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>22.489227</v>
+        <v>22.531418</v>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="n">
         <v>0.35158002</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>58.17077704656935</v>
+        <v>58.51432540390937</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>5.97156040252201</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>232.5715405499494</v>
+        <v>232.5798738267686</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.9975027168752738</v>
+        <v>0.9992584636988422</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2506</v>
+        <v>0.2507</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>-11.01</v>
+        <v>-8.25</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Justice Department settles with IBM over alleged DEI practices - The W (-85) // NJ residents charged with breaking into abandoned Somers IBM building  (-71) // University of Illinois and IBM renew quantum technology partnership at (+38)</t>
+          <t>IBM doubles down on quantum tech with U of I - Crain's Chicago Busines (-95) // Justice Department settles with IBM over alleged DEI practices - The W (-83) // IBM adds cybersecurity measures to help businesses against agentic att (+73)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n">
         <v>8</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>30.77</v>
+        <v>30.54</v>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
@@ -5033,7 +5083,7 @@
         </is>
       </c>
       <c r="U43" s="2" t="n">
-        <v>6.68</v>
+        <v>6.87</v>
       </c>
       <c r="V43" s="2" t="b">
         <v>0</v>
@@ -5065,19 +5115,19 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>Justice Department settles with IBM over alleged DEI practic</t>
+          <t>IBM doubles down on quantum tech with U of I - Crain's Chica</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Rigetti Computing</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5091,47 +5141,47 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>18.3194</v>
+        <v>41.3704</v>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="n">
-        <v>-0.64273</v>
+        <v>-0.24400999</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>75.27033779176521</v>
+        <v>77.62472435400451</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>1.215939042429444</v>
+        <v>2.747354684052644</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>14.85814813331321</v>
+        <v>30.73759266182228</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.232956095119662</v>
+        <v>1.345920973971547</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.2712</v>
+        <v>0.99</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>41.15</v>
+        <v>68.56</v>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88) // Quantum Computing Stocks Are Surging. New Models From Nvidia Are Helpi (+83) // Exclusive: Chad Rigetti’s Sygaldry raises $139 million to bring quantu (+71)</t>
+          <t>Why IonQ (IONQ) Is Up 59.1% After DARPA-Backed Quantum Networking Brea (+91) // IonQ surges after getting DARPA contract - Seeking Alpha (+90) // Quantum computing company lands state cash as presence in Bothell grow (+78)</t>
         </is>
       </c>
       <c r="R44" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>72.15000000000001</v>
+        <v>57.82</v>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
@@ -5148,7 +5198,7 @@
         </is>
       </c>
       <c r="X44" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>0</v>
@@ -5157,7 +5207,7 @@
         <v>5</v>
       </c>
       <c r="AA44" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB44" s="3" t="n">
         <v>3</v>
@@ -5169,19 +5219,19 @@
       </c>
       <c r="AD44" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=75 | Bullish news (+41) | High-vol penalty | IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quant</t>
+          <t>Weak structure | Overbought RSI=78 | Bullish news (+69) | High-vol penalty | Why IonQ (IONQ) Is Up 59.1% After DARPA-Backed Quantum Netwo</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Rigetti Computing</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5195,47 +5245,47 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>41.4748</v>
+        <v>18.0093</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="n">
-        <v>-0.24400999</v>
+        <v>-0.64273</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>77.71829805493245</v>
+        <v>74.46602567402559</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.739285791992511</v>
+        <v>1.225529019794766</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>30.73968156178792</v>
+        <v>14.85194444656372</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1.349227238019905</v>
+        <v>1.212586003838135</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>0.9896</v>
+        <v>1.2711</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>32.6</v>
+        <v>39.12</v>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ (IONQ) Soars 21% on Nvidia Quantum Computing Support - Yahoo Fina (+88) // State invests $500K for Bothell quantum computing expansion, adds up t (+67)</t>
+          <t>IonQ Rises 4%, D-Wave Surges 5%, Rigetti Gains 3%: The Quantum Rally I (+89) // Quantum Computing Stocks Are Surging. New Models From Nvidia Are Helpi (+83) // Exclusive: Chad Rigetti’s Sygaldry raises $139 million to bring quantu (+71)</t>
         </is>
       </c>
       <c r="R45" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>57.42</v>
+        <v>75.12</v>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
@@ -5252,7 +5302,7 @@
         </is>
       </c>
       <c r="X45" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>0</v>
@@ -5261,7 +5311,7 @@
         <v>5</v>
       </c>
       <c r="AA45" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB45" s="3" t="n">
         <v>3</v>
@@ -5273,7 +5323,7 @@
       </c>
       <c r="AD45" s="3" t="inlineStr">
         <is>
-          <t>Weak structure | Overbought RSI=78 | Bullish news (+33) | High-vol penalty | Quantum computing stocks are back on the rise. Here’s why IO</t>
+          <t>Weak structure | Overbought RSI=74 | Bullish news (+39) | High-vol penalty | IonQ Rises 4%, D-Wave Surges 5%, Rigetti Gains 3%: The Quant</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5349,7 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>20.4444</v>
+        <v>19.9259</v>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr"/>
@@ -5310,36 +5360,36 @@
         <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>75.11832266817295</v>
+        <v>74.13914314616522</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.396428655695032</v>
+        <v>1.400396874342015</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>16.19240723715888</v>
+        <v>16.18203687667846</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>1.262594503359902</v>
+        <v>1.231360829395859</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>1.3077</v>
+        <v>1.308</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.75</v>
+        <v>33.72</v>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has Inched Low (-95) // Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ Surges 10%, D-Wave Jumps 9%, Rigetti Climbs 7% as Quantum Computi (+88)</t>
+          <t>Quantum computing stocks are back on the rise. Here’s why IONQ, QBTS,  (+89) // IonQ Soars 18%, D-Wave Climbs 15%, Rigetti Gains 12%: Is the Quantum S (+86) // Quantum stocks on pace for a massive week after Nvidia debuts AI model (+69)</t>
         </is>
       </c>
       <c r="R46" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>79.78</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
@@ -5347,7 +5397,7 @@
         </is>
       </c>
       <c r="U46" s="3" t="n">
-        <v>219.08</v>
+        <v>210.98</v>
       </c>
       <c r="V46" s="3" t="b">
         <v>0</v>
@@ -5358,7 +5408,7 @@
         </is>
       </c>
       <c r="X46" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>0</v>
@@ -5367,7 +5417,7 @@
         <v>5</v>
       </c>
       <c r="AA46" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB46" s="3" t="n">
         <v>3</v>
@@ -5379,7 +5429,7 @@
       </c>
       <c r="AD46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weak structure | Overbought RSI=75 | High-vol penalty | Why D-Wave Quantum Stock Plummeted 23.2% Last Month and Has </t>
+          <t>Weak structure | Overbought RSI=74 | Bullish news (+34) | High-vol penalty | Quantum computing stocks are back on the rise. Here’s why IO</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5455,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>195370.3704</v>
+        <v>200000</v>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr"/>
@@ -5413,39 +5463,39 @@
         <v>0.10783</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>65.11741682974559</v>
+        <v>68.65601503759399</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>10403.43915343915</v>
+        <v>9828.042328042326</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>173125</v>
+        <v>175395.3703703703</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>1.128493114052681</v>
+        <v>1.140280952556922</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>0.3185</v>
+        <v>0.3186</v>
       </c>
       <c r="O47" s="3" t="n">
         <v>7</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.82</v>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>Two Samsung washers at Lowe’s are marked down by up to $300 during thi (-94) // Samsung hikes Galaxy Book 6 prices by up to $600 as base model goes on (+65)</t>
+          <t>Samsung's The Frame TV is at its lowest price in months — save up to $ (-94) // Samsung Union Strike Threat: 30 Trillion Loss Over Bonus Demand - 조선일보 (-92) // Samsung improves Now Brief with SmartThings integration - SamMobile (+89)</t>
         </is>
       </c>
       <c r="R47" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S47" s="3" t="n">
-        <v>39.73</v>
+        <v>36.49</v>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
@@ -5453,10 +5503,10 @@
         </is>
       </c>
       <c r="U47" s="3" t="n">
-        <v>264.42</v>
+        <v>291.01</v>
       </c>
       <c r="V47" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
@@ -5485,19 +5535,19 @@
       </c>
       <c r="AD47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two Samsung washers at Lowe’s are marked down by up to $300 </t>
+          <t>Samsung's The Frame TV is at its lowest price in months — sa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centrus Energy</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5511,78 +5561,80 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>186.5556</v>
+        <v>213.7037</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>51.661537</v>
+        <v>64.46928</v>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>0.16794</v>
+        <v>0.28517</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>54.17731809482795</v>
+        <v>67.03778538953614</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.48115055144778</v>
+        <v>8.781084938654823</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>187.9611112806532</v>
+        <v>192.0209582293475</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.9925220718716581</v>
+        <v>1.11291865481767</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.8539</v>
+        <v>0.3233</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>28.26</v>
+        <v>7.56</v>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>Centrus Energy Earns Technical Rating Upgrade - Investor's Business Da (+81) // Centrus Energy Stock Surges on Massive Government Deal - TipRanks (+73) // Oklo, Nano Nuclear, Centrus, NuScale Surge as White House Space Nuclea (+51)</t>
+          <t>BWX Technologies Inc (BWXT) Shares Fall 3.2% -- GF Value Says St - Gur (-96) // BWX Technologies (BWXT) Hits an All-Time High on Canadian Nuclear Deal (+80) // BWX Technologies stock hits all-time high at 239.88 USD - Investing.co (+68)</t>
         </is>
       </c>
       <c r="R48" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>49.39</v>
+        <v>8.69</v>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>123.2</v>
+      </c>
       <c r="V48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>NO_ENTRY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="X48" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA48" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
@@ -5591,19 +5643,19 @@
       </c>
       <c r="AD48" s="3" t="inlineStr">
         <is>
-          <t>High-vol penalty | Centrus Energy Earns Technical Rating Upgrade - Investor's B</t>
+          <t>BWX Technologies Inc (BWXT) Shares Fall 3.2% -- GF Value Say</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Centrus Energy</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -5617,80 +5669,78 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>215.1852</v>
+        <v>187.0556</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>64.9162</v>
+        <v>51.8</v>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="n">
-        <v>0.28517</v>
+        <v>0.16794</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>68.49018726269837</v>
+        <v>54.42896702515691</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>8.733465810301441</v>
+        <v>12.48081954067976</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>192.050587689435</v>
+        <v>187.9711114388925</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>1.120460927106132</v>
+        <v>0.9951292944945308</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>0.323</v>
+        <v>0.8541</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>19.76</v>
+        <v>5.41</v>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nuclear Deal (+80) // BWX Technologies stock hits all-time high at 239.88 USD - Investing.co (+68)</t>
+          <t>Centrus Energy (LEU) share price target cut by analysts - MSN (-92) // Centrus Energy Earns Technical Rating Upgrade - Investor's Business Da (+81) // Oklo, Nano Nuclear, Centrus, NuScale Surge as White House Space Nuclea (+51)</t>
         </is>
       </c>
       <c r="R49" s="3" t="n">
         <v>8</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>7.94</v>
+        <v>48.99</v>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
         </is>
       </c>
-      <c r="U49" s="3" t="n">
-        <v>124.75</v>
-      </c>
+      <c r="U49" s="3" t="inlineStr"/>
       <c r="V49" s="3" t="b">
         <v>0</v>
       </c>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>NO_ENTRY</t>
         </is>
       </c>
       <c r="X49" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AA49" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AB49" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
@@ -5699,19 +5749,19 @@
       </c>
       <c r="AD49" s="3" t="inlineStr">
         <is>
-          <t>BWX Technologies (BWXT) Hits an All-Time High on Canadian Nu</t>
+          <t>High-vol penalty | Centrus Energy (LEU) share price target cut by analysts - MS</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>URNM</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>URNM ETF</t>
+          <t>Cameco</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -5721,50 +5771,56 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>64.3056</v>
+        <v>111.3611</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>14.242845</v>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr"/>
+        <v>121.48484</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1.9161</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.088870004</v>
+      </c>
       <c r="I50" s="3" t="n">
-        <v>2.81</v>
+        <v>0.14</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>78.59944730659737</v>
+        <v>80.06939397477714</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>2.608201112696733</v>
+        <v>4.714947655087423</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>61.84592564900715</v>
+        <v>105.546666321931</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>1.039770236358104</v>
+        <v>1.05508882358419</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>0.4787</v>
+        <v>0.4962</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>16.08</v>
+        <v>27.27</v>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-Demand Asse (+84)</t>
+          <t>Assessing Cameco’s Valuation As U.S. Space Nuclear Reactor Initiative  (+91) // Cameco gains as uranium market sentiment improves amid higher term-pri (+90)</t>
         </is>
       </c>
       <c r="R50" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -5780,16 +5836,16 @@
         </is>
       </c>
       <c r="X50" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z50" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA50" s="3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AB50" s="3" t="n">
         <v>0</v>
@@ -5801,19 +5857,19 @@
       </c>
       <c r="AD50" s="3" t="inlineStr">
         <is>
-          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-D</t>
+          <t>Assessing Cameco’s Valuation As U.S. Space Nuclear Reactor I</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>URNM</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Cameco</t>
+          <t>URNM ETF</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5823,54 +5879,50 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>111.5648</v>
+        <v>64.3704</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>122.948975</v>
+        <v>14.2572</v>
       </c>
       <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="n">
-        <v>0.088870004</v>
-      </c>
+      <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="3" t="n">
-        <v>0.15</v>
+        <v>2.81</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>80.23700706039912</v>
+        <v>78.6830429130344</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>4.714286138140964</v>
+        <v>2.608201112696733</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>105.5507404186107</v>
+        <v>61.84722193965205</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.056978022080767</v>
+        <v>1.040796421299383</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.4961</v>
+        <v>0.4788</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>31.95</v>
+        <v>15.77</v>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBeat (+92) // Cameco gains as uranium market sentiment improves amid higher term-pri (+90) // Cameco Surges 200% in a Year: Buy, Sell or Hold the Stock? - Yahoo Fin (+65)</t>
+          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-Demand Asse (+84)</t>
         </is>
       </c>
       <c r="R51" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S51" s="3" t="n">
-        <v>17.34</v>
-      </c>
+      <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr">
         <is>
           <t>SPECULATIVE (short-term)</t>
@@ -5886,28 +5938,28 @@
         </is>
       </c>
       <c r="X51" s="3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AA51" s="3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AB51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AD51" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=80 | Bullish news (+32) | Cameco (NYSE:CCJ) Trading Up 2.7% - What's Next? - MarketBea</t>
+          <t>Sprott Uranium Miners ETF Opens Clearest Path To Highly In-D</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5985,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>11.7685</v>
+        <v>11.713</v>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr"/>
@@ -5944,16 +5996,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>75.70978810072852</v>
+        <v>75.24116317650343</v>
       </c>
       <c r="K52" s="3" t="n">
         <v>0.5350529832184003</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>11.05166668362088</v>
+        <v>11.05055556473909</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1.064863688956646</v>
+        <v>1.059943325123383</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>0.5833</v>
@@ -5962,7 +6014,7 @@
         <v>2</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>35.51</v>
+        <v>41.24</v>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
@@ -5973,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>65.98</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
@@ -6011,7 +6063,7 @@
       </c>
       <c r="AD52" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=76 | Bullish news (+36) | NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interes</t>
+          <t>Overbought RSI=75 | Bullish news (+41) | NexGen Energy (NYSE:NXE) Sees Large Decline in Short Interes</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6103,7 @@
         <v>78.66221218804957</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>2.018518044204307</v>
+        <v>2.019179561150767</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>47.39629646583839</v>
@@ -6060,17 +6112,17 @@
         <v>1.079745257874041</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0.4303</v>
+        <v>0.4304</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>25.13</v>
+        <v>11.44</v>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Quadrupling (+93) // Uranium ETF (URA) Hits New 52-Week High - Zacks Investment Research (+78) // Disruptive Theme of the Week: Hot Themes in the New Year - ETF Trends (-29)</t>
+          <t>Uranium ETF (URA) Hits New 52-Week High - Zacks Investment Research (+78) // Disruptive Theme of the Week: Hot Themes in the New Year - ETF Trends (-29)</t>
         </is>
       </c>
       <c r="R53" s="3" t="n">
@@ -6092,7 +6144,7 @@
         </is>
       </c>
       <c r="X53" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y53" s="3" t="n">
         <v>4</v>
@@ -6101,7 +6153,7 @@
         <v>17</v>
       </c>
       <c r="AA53" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB53" s="3" t="n">
         <v>0</v>
@@ -6113,7 +6165,7 @@
       </c>
       <c r="AD53" s="3" t="inlineStr">
         <is>
-          <t>Overbought RSI=79 | Global X Uranium ETF (URA) Is Up 17.6% After US Commits to Q</t>
+          <t>Weak structure | Overbought RSI=79 | Uranium ETF (URA) Hits New 52-Week High - Zacks Investment R</t>
         </is>
       </c>
     </row>
@@ -6139,29 +6191,31 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>35.24</v>
+        <v>35.03</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>20.729412</v>
-      </c>
-      <c r="G54" s="4" t="inlineStr"/>
+        <v>20.60588</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>1.2036</v>
+      </c>
       <c r="H54" s="4" t="n">
         <v>0.1216</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>77.67180171122854</v>
+        <v>77.82028895443658</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.6292854036603656</v>
+        <v>0.6257140295846122</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>33.3906001663208</v>
+        <v>33.44920017242432</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.055386890410295</v>
+        <v>1.047259683302555</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>0.2411</v>
@@ -6170,18 +6224,18 @@
         <v>2</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>18.38</v>
+        <v>26.6</v>
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>Veolia unveils a next-generation integrated offering to revolutionize  (+69) // French group Veolia aims $1.2 billion in revenue from data centres, ch (+37) // Veolia Sees €1 Billion Sales to AI Industries by 2030 - Bloomberg.com (+23)</t>
+          <t>Veolia unveils a next-generation integrated offering to revolutionize  (+69) // Veolia launches Data Center Resource 360 solution to take on digital s (+56) // French group Veolia aims $1.2 billion in revenue from data centres, ch (+37)</t>
         </is>
       </c>
       <c r="R54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>6.81</v>
+        <v>8.44</v>
       </c>
       <c r="T54" s="4" t="inlineStr">
         <is>
@@ -6189,7 +6243,7 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>18.14</v>
+        <v>17.21</v>
       </c>
       <c r="V54" s="4" t="b">
         <v>0</v>
@@ -6200,23 +6254,23 @@
         </is>
       </c>
       <c r="X54" s="4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="Y54" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z54" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB54" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AC54" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AD54" s="4" t="inlineStr">
@@ -6247,10 +6301,10 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>19.7269</v>
+        <v>19.6759</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>22.824575</v>
+        <v>22.765652</v>
       </c>
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr"/>
@@ -6258,16 +6312,16 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>62.01274123674997</v>
+        <v>63.68267301745596</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.4167793919800454</v>
+        <v>0.4263693693453676</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>19.87497234344482</v>
+        <v>19.86117603160717</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>0.9925474004963003</v>
+        <v>0.990672752439914</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>0.1747</v>
@@ -6276,7 +6330,7 @@
         <v>4</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>19.58</v>
+        <v>19.87</v>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
@@ -6293,7 +6347,7 @@
         </is>
       </c>
       <c r="U55" s="3" t="n">
-        <v>22.21</v>
+        <v>22.08</v>
       </c>
       <c r="V55" s="3" t="b">
         <v>0</v>
@@ -6432,10 +6486,10 @@
         <v>185.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>248.5833</v>
+        <v>249.287</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.76</v>
+        <v>6.06</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -6443,13 +6497,13 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45.5</v>
+        <v>26.3</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>54.6</v>
+        <v>55.6</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -6463,7 +6517,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Score=62.0 | PnL=+5.8% | BUSINESS COLLATERAL (10yr)</t>
+          <t>Score=64.0 | PnL=+6.1% | BUSINESS COLLATERAL (10yr)</t>
         </is>
       </c>
     </row>
@@ -6480,10 +6534,10 @@
         <v>171.13</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>190.65</v>
+        <v>189.1</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8.449999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -6491,13 +6545,13 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>36.7</v>
+        <v>10</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>58.4</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -6511,7 +6565,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Score=76.0 | PnL=+8.5% | BUSINESS COLLATERAL (10yr)</t>
+          <t>Score=77.0 | PnL=+7.6% | BUSINESS COLLATERAL (10yr)</t>
         </is>
       </c>
     </row>

--- a/outputs/market_scan.xlsx
+++ b/outputs/market_scan.xlsx
@@ -579,7 +579,7 @@
         <v>113.1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.57694043408705</v>
+        <v>14.57694043405731</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>5</v>
@@ -592,7 +592,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cameco (CCJ) Stock Falls Amid Market Uptick: What Investors Need to Know - Yahoo Finance, Cameco (NYSE:CCJ) Trading Down 1.3% - Here's What Happened - MarketBeat, Nuclear Stock Face-Off: Is Oklo or Cameco the Better Buy Right Now? - The Motley Fool</t>
+          <t>Cameco (CCJ) Stock Falls Amid Market Uptick: What Investors Need to Know - Yahoo Finance, Nuclear Stock Face-Off: Is Oklo or Cameco the Better Buy Right Now? - The Motley Fool, Cameco (NYSE:CCJ) Trading Down 1.3% - Here's What Happened - MarketBeat</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -652,7 +652,7 @@
         <v>11.48</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>39.14877841435597</v>
+        <v>39.17921915836911</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>190.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37.11488751415039</v>
+        <v>35.29009252507336</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
@@ -734,11 +734,11 @@
         <v>23</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Centrus Energy (NYSE: LEU) sets 2026 virtual meeting, governance and pay votes - Stock Titan, Centrus Energy Selects Geiger Brothers as Construction Contractor for Major Uranium Enrichment Plant Expansion - PR Newswire, Centrus Energy Corp (LEU) Stock Down 6.3% but Still Overvalued -- GF Score: 66/100 - GuruFocus</t>
+          <t>Centrus Energy Selects Geiger Brothers as Construction Contractor for Major Uranium Enrichment Plant Expansion - PR Newswire, Centrus Energy (NYSE: LEU) sets 2026 virtual meeting, governance and pay votes - Stock Titan, Centrus Energy Corp (LEU) Stock Down 6.3% but Still Overvalued -- GF Score: 66/100 - GuruFocus</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
         <v>206.62</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35.75879651307212</v>
+        <v>36.47110982983384</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>5</v>
@@ -807,11 +807,11 @@
         <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>11</v>
+        <v>13.9</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>After years of development, BWX Technologies hopes to prove the value of tiny nuclear fuel particles - Cardinal News, West Michigan Advisors LLC Buys New Stake in BWX Technologies, Inc. $BWXT - MarketBeat, $100 Invested In BWX Technologies 10 Years Ago Would Be Worth This Much Today - Sahm</t>
+          <t>After years of development, BWX Technologies hopes to prove the value of tiny nuclear fuel particles - Cardinal News, BWX Technologies to buy Precision Components, bolstering nuclear manufacturing - MSN, West Michigan Advisors LLC Buys New Stake in BWX Technologies, Inc. $BWXT - MarketBeat</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
         <v>13.01</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43.28359962161595</v>
+        <v>43.71264554280029</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>15</v>
@@ -880,11 +880,11 @@
         <v>23</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Eagle Nuclear Energy to Commence Summer Drilling Program at America's Largest Uranium Deposit - Crux Investor, TerraPower begins construction on Natrium power plant in Kemmerer - American Nuclear Society -- ANS, State-Level Policy Shifts Spark Nuclear Energy Investment Opportunities - ETF Database</t>
+          <t>Eagle Nuclear Energy (NASDAQ:NUCL) - Fully Funded to Drill America's Largest Uranium Deposit - Crux Investor, State-Level Policy Shifts Spark Nuclear Energy Investment Opportunities - ETF Database, TerraPower begins construction on Natrium power plant in Kemmerer - American Nuclear Society -- ANS</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>3.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>35.68410067072915</v>
+        <v>37.05617901123188</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>5</v>
@@ -953,11 +953,11 @@
         <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.7</v>
+        <v>16.2</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Denison Mine (NYSEAMERICAN:DNN) Share Price Passes Above 200 Day Moving Average - Here's Why - MarketBeat, Denison Mines vs. NexGen Energy: Which Uranium Stock to Buy Now? - Yahoo Finance, Can Denison Mines' Phoenix Project Power Its Next Growth Phase? - qz.com</t>
+          <t>Denison Mine (NYSEAMERICAN:DNN) Share Price Passes Above 200 Day Moving Average - Here's Why - MarketBeat, Denison Mines vs. NexGen Energy: Which Uranium Stock to Buy Now? - Yahoo Finance, Skyharbour, Denison Mines launch 2026 Russell Lake uranium exploration - MSN</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
         <v>11.68</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>26.11609930359095</v>
+        <v>24.94730176590527</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>5</v>
@@ -1026,11 +1026,11 @@
         <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Citi Sticks to Its Buy Rating for Paladin Energy Ltd (PALAF) - The Globe and Mail, A Quick Look at Today's Ratings for PALADIN ENERGY LIMITED(PALAF.US), With a Forecast Between $6.95 to $10.91 - Moomoo, Paladin Energy Q3 Earnings Call Highlights - Yahoo Finance</t>
+          <t>Citi Sticks to Its Buy Rating for Paladin Energy Ltd (PALAF) - The Globe and Mail, Paladin Energy Q3 Earnings Call Highlights - MarketBeat, Earnings call transcript: Paladin Energy’s Q3 2026 sees uranium production boost - Investing.com</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
         <v>1.49</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>50.95854231157227</v>
+        <v>50.15313906596219</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>15</v>
@@ -1099,7 +1099,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-16.2</v>
+        <v>-19.4</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>556.02</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.31092709302767</v>
+        <v>45.521001312883</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>5</v>
@@ -1172,7 +1172,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>-2.8</v>
+        <v>2.1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>85.05</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>22.84583740867582</v>
+        <v>22.84583740868634</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>5</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Kazatomprom Sets AGM Date, Proposes 75% FCF Dividend and Approves 2025 Integrated Report - TipRanks, Kazatomprom to lower uranium production in 2026 - World Nuclear News, Areva And Kazatomprom Announce Plans To Build Fuel Facility - NucNet</t>
+          <t>Kazatomprom to lower uranium production in 2026 - World Nuclear News, Kazatomprom Sets AGM Date, Proposes 75% FCF Dividend and Approves 2025 Integrated Report - TipRanks, Areva And Kazatomprom Announce Plans To Build Fuel Facility - NucNet</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
         <v>0.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>41.26338698901228</v>
+        <v>41.2633869890104</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>5</v>
@@ -1380,7 +1380,7 @@
         <v>51.21</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.61053869128295</v>
+        <v>18.61053869128495</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>62.05</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33.18818220123467</v>
+        <v>33.18818220123936</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>152.18</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>30.96418117173339</v>
+        <v>30.96418117172872</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
         <v>290.31</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>25.26284451597466</v>
+        <v>25.26284451598165</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>5</v>
@@ -1672,7 +1672,7 @@
         <v>59.94</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>43.26004678570337</v>
+        <v>42.58079104312434</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>5</v>
@@ -1681,11 +1681,11 @@
         <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>41</v>
+        <v>38.3</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>RWE’s Camster II onshore wind farm is completed and powering Scottish homes and businesses - RWE, Germany: RWE Group Moves Into Austrian Energy Market - NucNet, RWE and Polarium sign multi-asset tolling to unlock virtual battery from thousands of sites to support integration of renewables - RWE</t>
+          <t>RWE’s Camster II onshore wind farm is completed and powering Scottish homes and businesses - RWE, RWE and Polarium sign multi-asset tolling to unlock virtual battery from thousands of sites to support integration of renewables - RWE, Germany: RWE Group Moves Into Austrian Energy Market - NucNet</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
         <v>187.62</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>31.24087912030253</v>
+        <v>31.76008898764377</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>5</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>35.13</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>46.11484374384627</v>
+        <v>46.11484374384642</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>5</v>
@@ -1891,7 +1891,7 @@
         <v>40.26</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>47.52921393140551</v>
+        <v>48.86385142802587</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>10</v>
@@ -1900,11 +1900,11 @@
         <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>30.1</v>
+        <v>35.5</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Technip Energies Extends LNG And Cleaner Fuels Reach Across Three Continents - Yahoo Finance, A Look At Technip Energies (ENXTPA:TE) Valuation After New FEED Wins In Gabon Vietnam And The US - simplywall.st, Technip Energies awarded a substantial authorization to advance Commonwealth LNG project ahead of Final Investment Decision - Technip Energies</t>
+          <t>Technip Energies Extends LNG And Cleaner Fuels Reach Across Three Continents - Yahoo Finance, Technip Energies awarded a substantial authorization to advance Commonwealth LNG project ahead of Final Investment Decision - Technip Energies, Is Technip Energies (ENXTPA:TE) Pricing Reflect Its 36.6% One Year Share Gain? - simplywall.st</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
         <v>22.95</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>34.86946452596246</v>
+        <v>35.60689724237838</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>7.5</v>
+        <v>10.4</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>9.82</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.21616257913632</v>
+        <v>30.2161625791357</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Italy's Enel to hire 1,000 workers at power distribution unit, unions say - Reuters, Artificial intelligence and the benefits to energy - Enel Group, Verkkokauppa.com Oyj - Managers' Transactions – Enel Sintonen - marketscreener.com</t>
+          <t>Italy's Enel to hire 1,000 workers at power distribution unit, unions say - Reuters, Artificial intelligence and the benefits to energy - Enel Group, Italy’s Meloni Ousts Leonardo CEO, Renews Heads of Eni, Enel - Bloomberg.com</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
         <v>19.92</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>24.64316534810344</v>
+        <v>24.6713469363814</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>5</v>
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>149.26</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>35.51716505736038</v>
+        <v>36.40468464419757</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>5</v>
@@ -2192,7 +2192,7 @@
         <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10.1</v>
+        <v>13.6</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>176.67</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>47.85569913871845</v>
+        <v>47.85569913871986</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>5</v>
@@ -2329,7 +2329,7 @@
         <v>88.22</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.86619842984532</v>
+        <v>21.41192491353004</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>10</v>
@@ -2338,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>31.5</v>
+        <v>33.6</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>38.16</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38.12024254816139</v>
+        <v>38.77159912603285</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -2411,11 +2411,11 @@
         <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>12.5</v>
+        <v>15.1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Brookfield Renewable Partners (TSE:BEP.UN) Stock Price Expected to Rise, Desjardins Analyst Says - MarketBeat, Brookfield Renewable Updates Restricted Unit Plan to Sharpen Long-Term Incentives - TipRanks, Stocks with rising relative strength: Brookfield Renewable - MSN</t>
+          <t>Brookfield Renewable Partners (TSE:BEP.UN) Stock Price Expected to Rise, Desjardins Analyst Says - MarketBeat, Brookfield Renewable Updates Restricted Unit Plan to Sharpen Long-Term Incentives - TipRanks, Stocks With Rising Relative Strength: Brookfield Renewable - Investor's Business Daily</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
         <v>13.42</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>42.07050305326018</v>
+        <v>41.21855887118615</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>18.51</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6.254210276530782</v>
+        <v>6.254210276532855</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>The Iran War just made the clean energy transition non-negotiable - Fortune, Renewable Energy Is Booming Again. The Iran War Has Scrambled Markets. - Barron's, How the Iran war set Beijing up for global clean energy dominance - politico.eu</t>
+          <t>The Iran War just made the clean energy transition non-negotiable - Fortune, How the Iran war set Beijing up for global clean energy dominance - E&amp;E News by POLITICO, How the Iran war set Beijing up for global clean energy dominance - politico.eu</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
         <v>82.53</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>50.46108039094746</v>
+        <v>50.46108034438129</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>77</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>58.13493046164935</v>
+        <v>58.1349304616468</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
         <v>529.4400000000001</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.70530114789507</v>
+        <v>24.60835605580893</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
@@ -2774,11 +2774,11 @@
         <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>-33.2</v>
+        <v>-33.6</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>BP shareholders reject two board proposals as chair gets lower-than-typical support - Reuters, Back NIPSCO, BP workers in fights against boss lockouts - The Militant, Update: BP refinery incident being inspected by state labor and air agencies - Cascadia Daily News</t>
+          <t>BP shareholders reject two board proposals as chair gets lower-than-typical support - Reuters, Back NIPSCO, BP workers in fights against boss lockouts - The Militant, What impact will soaring oil prices have on BP’s earnings? - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
         <v>137.88</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.1600048774785</v>
+        <v>28.41808309312296</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>10</v>
@@ -2849,11 +2849,11 @@
         <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>16.6</v>
+        <v>13.7</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>ExxonMobil's 2025 Giving Campaign delivers record results to United Way of Greater Houston and Houston community - Exxon Mobil Corporation | ExxonMobil, ExxonMobil | XOM Stock Price, Company Overview &amp; News - Forbes, ExxonMobil (NYSE:XOM) Shares Down 1.1% - Should You Sell? - MarketBeat</t>
+          <t>ExxonMobil's 2025 Giving Campaign delivers record results to United Way of Greater Houston and Houston community - Exxon Mobil Corporation | ExxonMobil, How ExxonMobil shows up in our hometown, delivering record giving results - Exxon Mobil Corporation | ExxonMobil, ExxonMobil | XOM Stock Price, Company Overview &amp; News - Forbes</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
         <v>171.49</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>29.61613614858379</v>
+        <v>29.61613614858381</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>112.74</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>61.13047338090849</v>
+        <v>61.1304733809066</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>10</v>
@@ -3059,10 +3059,10 @@
         <v>51.99</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>4.909264640871395</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         <v>37.37</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>18.45628590136512</v>
+        <v>18.45628590137505</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>10</v>
@@ -3203,7 +3203,7 @@
         <v>5.66</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>31.47831889801054</v>
+        <v>31.47831889800926</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>5</v>
@@ -3276,7 +3276,7 @@
         <v>41.67</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>47.29992191493536</v>
+        <v>47.29992191493645</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>321.76</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>21.1148742213873</v>
+        <v>23.20062626153676</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>0</v>
@@ -3358,11 +3358,11 @@
         <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>24.5</v>
+        <v>32.8</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>A Look At Aker BP (OB:AKRBP) Valuation After First Quarter 2026 Volume Update - simplywall.st, Aker BP's earnings slide masks a massive growth push - MSN, Aker BP publishes Annual Report for 2025 - Yahoo Finance</t>
+          <t>A Look At Aker BP (OB:AKRBP) Valuation After First Quarter 2026 Volume Update - simplywall.st, Aker BP's Earnings Slide Masks a Massive Growth Push - Crude Oil Prices Today | OilPrice.com, Aker BP publishes Annual Report for 2025 - Yahoo Finance</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
         <v>33.29</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>42.33117528445283</v>
+        <v>42.33117528445073</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
         <v>81.06999999999999</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>43.16724241897962</v>
+        <v>43.16724241898171</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
         <v>44.39</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>43.18490739166821</v>
+        <v>48.59147545136435</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>5</v>
@@ -3577,7 +3577,7 @@
         <v>23</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.7</v>
+        <v>22.4</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>52.66</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32.77058086358164</v>
+        <v>32.26295934990324</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>1319.2</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>40.33636777849423</v>
+        <v>40.33636777849236</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
         <v>1870.83</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>39.98813160882237</v>
+        <v>39.26194777899274</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>10</v>
@@ -3796,11 +3796,11 @@
         <v>8</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Meet Lars – Associate Systems Engineer, Naval Systems, UK - BAE Systems, BAE Systems honors TTTECH with a Partner 2 Win Gold Tier Award - TTTech, BAE Systems introduces Ascent™ spacecraft to support space superiority and exploration - BAE Systems</t>
+          <t>Meet Lars – Associate Systems Engineer, Naval Systems, UK - BAE Systems, Bae Systems PLC (OTCMKTS:BAESY) Short Interest Update - MarketBeat, BAE Systems honors TTTECH with a Partner 2 Win Gold Tier Award - TTTech</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
         <v>52.7</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>10.42214784491781</v>
+        <v>10.42214784491576</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>What Leonardo DiCaprio sent Nikki Glaser after Golden Globes roast - USA Today, Leonardo DiCaprio Urges Fans to Call U.S. Representatives and Fight Against Bill to Dismantle the Endangered Species Act: ‘Reject This Existential Threat’ - Yahoo News Canada, Nikki Glaser Would ‘Absolutely’ Do a Leonardo DiCaprio Roast but Says He Shouldn’t Sign Up for One: ‘Maybe If He Was Donating To Climate Change’ - Variety</t>
+          <t>What Leonardo DiCaprio sent Nikki Glaser after Golden Globes roast - USA Today, In Cuba: To Be, or Not to Be - Time Magazine, Leonardo DRS Targets Maritime Power And Drone Defense Growth Opportunities - simplywall.st</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
         <v>232.8</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>36.2160192774563</v>
+        <v>35.5661453185536</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>10</v>
@@ -3942,7 +3942,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>32.9</v>
+        <v>30.3</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>165.92</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>27.1333102863214</v>
+        <v>27.13331028632088</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>10</v>
@@ -4079,7 +4079,7 @@
         <v>270</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>26.70197056599738</v>
+        <v>26.70197056606812</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>5</v>
@@ -4152,7 +4152,7 @@
         <v>296.4</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>31.47761330194476</v>
+        <v>31.47761330194264</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>10</v>
@@ -4225,7 +4225,7 @@
         <v>532.51</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>23.4743116907711</v>
+        <v>24.07482029123633</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
         <v>8</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>475.42</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>22.71741290758742</v>
+        <v>23.23965837433031</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>10</v>
@@ -4307,7 +4307,7 @@
         <v>8</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>-21.1</v>
+        <v>-19</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>161.35</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>29.09516086801952</v>
+        <v>29.80389385484038</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>16.4</v>
+        <v>19.2</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>293.99</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>23.49870296195419</v>
+        <v>23.08904252015301</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>10</v>
@@ -4453,11 +4453,11 @@
         <v>15</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Pentagon closes $1 billion investment in L3Harris missile unit - SpaceNews, L3Harris Technologies (NYSE: LHX) rings the opening bell® - qz.com, L3Harris closes $1bn DoW investment in missile solutions business - Airforce Technology</t>
+          <t>Pentagon closes $1 billion investment in L3Harris missile unit - SpaceNews, L3Harris Technologies (NYSE: LHX) rings the opening bell® - qz.com, Caprock Group LLC Has $2.71 Million Stake in L3Harris Technologies Inc $LHX - MarketBeat</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
         <v>290.01</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>43.34855749272236</v>
+        <v>43.31178873777827</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>10</v>
@@ -4526,7 +4526,7 @@
         <v>15</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>81.44</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>28.63105924800525</v>
+        <v>29.32752173394184</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>5</v>
@@ -4599,11 +4599,11 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>34.5</v>
+        <v>37.3</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Textron’s Expanding Military and Jet Backlog Might Change The Case For Investing In Textron (TXT) - simplywall.st, Textron Aviation Announces Fleet Order from SD Aviation for 3 Cessna Citation Light Jets - ASDNews, Bell Announces Three New Orders for Corporate-Configured Bell 429s in Europe - Textron Inc. - Investor Relations</t>
+          <t>Textron’s Expanding Military and Jet Backlog Might Change The Case For Investing In Textron (TXT) - simplywall.st, Bell Announces Three New Orders for Corporate-Configured Bell 429s in Europe - Textron Inc. - Investor Relations, Textron To Expand European Parts and Distribution Center in Düsseldorf - Aviation International News</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
         <v>135.24</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>34.88122364225851</v>
+        <v>34.88122364230211</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>5</v>
@@ -4736,7 +4736,7 @@
         <v>244.48</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11.68491033836669</v>
+        <v>11.94402937777555</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>5</v>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>199.81</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2.903947094456925</v>
+        <v>3.523932164535128</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>11.6</v>
+        <v>14.1</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>54.77</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1.700754370541194</v>
+        <v>1.70075437054032</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>414.94</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15.26869755237168</v>
+        <v>15.39948984049277</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>5</v>
@@ -4964,7 +4964,7 @@
         <v>15</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>165.31</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>16.71178737468847</v>
+        <v>15.55709569528907</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>5</v>
@@ -5037,7 +5037,7 @@
         <v>7</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>-1.2</v>
+        <v>-5.8</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>13.19</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>25.12058955802918</v>
+        <v>25.05207057297365</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>5</v>
@@ -5110,11 +5110,11 @@
         <v>23</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Hypersonic Supply Chain Attacks: One Solution That Didn’t Need to Know the Payload - sentinelone.com, How SentinelOne’s AI EDR Autonomously Discovered and Stopped Anthropic’s Claude from Executing a Zero Day Supply Chain Attack, Globally - sentinelone.com, SentinelOne Isn’t A Hypergrowth Story Anymore — And That’s Why It’s A BUY (NYSE:S) - Seeking Alpha</t>
+          <t>Cwm LLC Buys 95,921 Shares of SentinelOne, Inc. $S - MarketBeat, Hypersonic Supply Chain Attacks: One Solution That Didn’t Need to Know the Payload - sentinelone.com, SentinelOne Isn’t A Hypergrowth Story Anymore — And That’s Why It’s A BUY (NYSE:S) - Seeking Alpha</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
         <v>78.09</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>30.47115373611533</v>
+        <v>31.31619588658307</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>5</v>
@@ -5183,7 +5183,7 @@
         <v>23</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>-10.1</v>
+        <v>-6.7</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>125.46</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>21.06218450049615</v>
+        <v>21.06218450049562</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>5</v>
@@ -5320,7 +5320,7 @@
         <v>70.34999999999999</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>44.04797834344964</v>
+        <v>44.6444537118135</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>5</v>
@@ -5329,11 +5329,11 @@
         <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>16.2</v>
+        <v>18.6</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Is Okta (OKTA) A Bargain After Recent 25% Share Price Slide? - simplywall.st, Okta Stock Is Down 23% in 1 Year. Can AI Security Drive a Rebound? - TIKR.com, Do Options Traders Know Something About Okta Stock We Don't? - Yahoo Finance UK</t>
+          <t>Is Okta (OKTA) A Bargain After Recent 25% Share Price Slide? - simplywall.st, Okta Stock Is Down 23% in 1 Year. Can AI Security Drive a Rebound? - TIKR.com, Is Okta (OKTA) a Buy as Wall Street Analysts Look Optimistic? - Yahoo Finance</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -5393,7 +5393,7 @@
         <v>22.71</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>20.45321315713116</v>
+        <v>19.75780492834635</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>5</v>
@@ -5402,7 +5402,7 @@
         <v>23</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>-10.2</v>
+        <v>-13</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>18.54</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>33.93840283621152</v>
+        <v>34.67756795231185</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>5</v>
@@ -5475,11 +5475,11 @@
         <v>15</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>-4.2</v>
+        <v>-1.3</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Vulnerabilities Patched in CrowdStrike, Tenable Products - SecurityWeek, Tenable (NASDAQ:TENB) Rating Lowered to "Buy" at Wall Street Zen - MarketBeat, Tenable rises after director buys 12,000 shares - MSN</t>
+          <t>Vulnerabilities Patched in CrowdStrike, Tenable Products - SecurityWeek, Tenable Holdings (TENB) Launched Advanced OT Asset Discovery Engine - Yahoo! Finance Canada, Tenable (NASDAQ:TENB) Rating Lowered to "Buy" at Wall Street Zen - MarketBeat</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
         <v>78.09</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>34.33760543353807</v>
+        <v>33.58468985184683</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>5</v>
@@ -5548,11 +5548,11 @@
         <v>15</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>-2.6</v>
+        <v>-5.7</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Oracle Critical Patch Update, April 2026 Security Update Review - Qualys, Qualys Inc. (QLYS) Navigating Through Competitive Risks of Large Language Models - Insider Monkey, Leveraging AI-informed Cybersecurity to Measure, Communicate, and Eliminate Cyber Risk - Qualys</t>
+          <t>Qualys Inc. (QLYS) Navigating Through Competitive Risks of Large Language Models - Yahoo Finance, Oracle Critical Patch Update, April 2026 Security Update Review - Qualys, Leveraging AI-informed Cybersecurity to Measure, Communicate, and Eliminate Cyber Risk - Qualys</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
         <v>124.69</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26.37381551040652</v>
+        <v>27.75336883216251</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>5</v>
@@ -5621,7 +5621,7 @@
         <v>8</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>-6.5</v>
+        <v>-1</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>5.51</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>52.68467152212045</v>
+        <v>52.68467152211608</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>5</v>
@@ -5756,7 +5756,7 @@
         <v>108.7</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>28.5116677386722</v>
+        <v>28.51166773867004</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>10</v>
@@ -5829,7 +5829,7 @@
         <v>62.26</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>20.97730650753623</v>
+        <v>21.55519831181466</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>0</v>
@@ -5838,11 +5838,11 @@
         <v>23</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>-8.1</v>
+        <v>-5.8</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>This Cybersecurity ETF Just Suffered a Pullback. Should You Buy the Dip? - Yahoo Finance, First Trust Nasdaq Cybersecurity ETF declares quarterly distribution of $0.1098 - MSN, Best Cybersecurity ETFs to Buy in 2026 and How to Invest - The Motley Fool</t>
+          <t>This Cybersecurity ETF Just Suffered a Pullback. Should You Buy the Dip? - FinancialContent, First Trust Nasdaq Cybersecurity ETF declares quarterly distribution of $0.1098 - MSN, Best Cybersecurity ETFs to Buy in 2026 and How to Invest - The Motley Fool</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
         <v>24.53</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>23.91405934654237</v>
+        <v>23.26231072842974</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>0</v>
@@ -5911,7 +5911,7 @@
         <v>23</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
@@ -5956,75 +5956,75 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>NEM</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Newmont</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Gold / Precious Metals</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n">
+      <c r="D76" s="3" t="n">
         <v>111.76</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>49.49295051396345</v>
-      </c>
-      <c r="F76" s="2" t="n">
+      <c r="E76" s="3" t="n">
+        <v>50.09670519270671</v>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G76" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H76" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="H76" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>Newmont Tops Earnings Expectations for Sixth Consecutive Quarter. What Gold Prices Mean for the Stock. - Barron's, Newmont Beats Q1 Estimates as Record Cash Flow Drives Buyback Expansion - Yahoo Finance, Newmont surges on Q1 earnings topper, record free cash flow, $6B buyback (NEM:NYSE) - Seeking Alpha</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>129.89</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
         <is>
           <t>EXIT_CURRENT</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="2" t="n">
+      <c r="N76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3" t="n">
         <v>17.572771</v>
       </c>
-      <c r="R76" s="2" t="n">
+      <c r="R76" s="3" t="n">
         <v>58.71152915232812</v>
       </c>
-      <c r="S76" s="2" t="n">
+      <c r="S76" s="3" t="n">
         <v>26.4</v>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
         <v>43.53</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>15.63693954608522</v>
+        <v>16.15994581020157</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
         <v>15</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>22.5</v>
+        <v>24.6</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>185.4</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>33.40419416129634</v>
+        <v>33.40419416129916</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>5</v>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>AGNICO EAGLE TO CONSOLIDATE FINLAND'S CENTRAL LAPLAND GREENSTONE BELT IN THREE SEPARATE TRANSACTIONS - PR Newswire, Agnico Eagle in multi-deal push to consolidate Finland gold assets - Reuters, Is Trending Stock Agnico Eagle Mines Limited (AEM) a Buy Now? - Yahoo Finance</t>
+          <t>AGNICO EAGLE TO CONSOLIDATE FINLAND'S CENTRAL LAPLAND GREENSTONE BELT IN THREE SEPARATE TRANSACTIONS - PR Newswire, Agnico Eagle in multi-deal push to consolidate Finland gold assets - Reuters, Agnico Eagle in deals to buy Rupert Resources, Aurion Resources, stake in JV with B2Gold - MSN</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -6175,75 +6175,75 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>KGC</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Kinross Gold</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Gold / Precious Metals</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="2" t="n">
         <v>30.36</v>
       </c>
-      <c r="E79" s="3" t="n">
-        <v>50.34250978381065</v>
-      </c>
-      <c r="F79" s="3" t="n">
+      <c r="E79" s="2" t="n">
+        <v>48.94192952661764</v>
+      </c>
+      <c r="F79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H79" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>Kinross Gold (KGC) Urges Shareholders to Reject TRC Mini-Tender Offer - Yahoo Finance, Kinross Gold (KGC) Urges Shareholders to Reject TRC Mini-Tender Offer - Insider Monkey, Kinross Gold shares slide as gold prices and gold-miner equities weaken - Quiver Quantitative</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>SPECULATIVE (short-term)</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="n">
+      <c r="H79" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corp. stock rises Friday, outperforms market - MarketWatch, Kinross Gold (KGC) Urges Shareholders to Reject TRC Mini-Tender Offer - Yahoo Finance, Kinross Gold (KGC) Urges Shareholders to Reject TRC Mini-Tender Offer - Insider Monkey</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SPECULATIVE (short-term)</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
         <v>129.46</v>
       </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>EXIT_CURRENT</t>
         </is>
       </c>
-      <c r="N79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="3" t="n">
+      <c r="N79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
         <v>17.202562</v>
       </c>
-      <c r="R79" s="3" t="n">
+      <c r="R79" s="2" t="n">
         <v>56.97561643692868</v>
       </c>
-      <c r="S79" s="3" t="n">
+      <c r="S79" s="2" t="n">
         <v>33.4</v>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         <v>42.35</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>40.74528016149064</v>
+        <v>39.87445807083416</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>5</v>
@@ -6276,7 +6276,7 @@
         <v>15</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>91.94</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>59.8984761554844</v>
+        <v>59.89847615547107</v>
       </c>
       <c r="F81" s="3" t="n">
         <v>10</v>
@@ -6413,7 +6413,7 @@
         <v>20.24</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>32.74623683653903</v>
+        <v>32.74623683653777</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>10</v>
@@ -6486,7 +6486,7 @@
         <v>11.81</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>48.4344163071395</v>
+        <v>48.12271777541099</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>10</v>
@@ -6495,7 +6495,7 @@
         <v>15</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>4211.11</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>37.51131870039436</v>
+        <v>35.66052896157958</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>10</v>
@@ -6568,7 +6568,7 @@
         <v>23</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>-2</v>
+        <v>-9.4</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>15.53</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45.71496772579053</v>
+        <v>47.17782701364533</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>5</v>
@@ -6641,11 +6641,11 @@
         <v>15</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Morgan Stanley Upgrades Harmony Gold (HMY) to Overweight - Yahoo Finance, Harmony Gold Mining 1H 2026 earnings preview - MSN, Ninety One builds 5.2017% stake in Harmony Gold (NYSE: HMY) - Stock Titan</t>
+          <t>Morgan Stanley Upgrades Harmony Gold (HMY) to Overweight - Yahoo Finance, Morgan Stanley Upgrades Harmony Gold (HMY) to Overweight - Insider Monkey, Harmony Gold Mining 1H 2026 earnings preview - MSN</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
         <v>11.78</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>36.64416996016327</v>
+        <v>35.91187260298242</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>5</v>
@@ -6714,7 +6714,7 @@
         <v>23</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>87.34999999999999</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>36.0754453968277</v>
+        <v>36.07544539682609</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>0</v>
@@ -6851,7 +6851,7 @@
         <v>114.58</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>35.23277905024571</v>
+        <v>35.23277905024682</v>
       </c>
       <c r="F88" s="2" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>401.16</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15.48458573874115</v>
+        <v>15.48458573874218</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>6282.41</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>3.121567904951727</v>
+        <v>3.121567904951942</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>0</v>
@@ -7066,7 +7066,7 @@
         <v>129.11</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>52.93096091785863</v>
+        <v>52.93096091785333</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>15</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>Wheaton Precious Metals Corp. stock falls Friday, underperforms market - MarketWatch, Spanish Mountain Gold sells 1.5% royalty to Wheaton Precious Metals for $55M - MSN, U S Global Investors Inc. Increases Stock Holdings in Wheaton Precious Metals Corp. $WPM - MarketBeat</t>
+          <t>Wheaton Precious Metals Corp. stock falls Friday, underperforms market - MarketWatch, Spanish Mountain Gold sells 1.5% royalty to Wheaton Precious Metals for $55M - MSN, Have Global Tensions Affected the Price of Wheaton Precious Metal Stock? - The Motley Fool</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -7139,7 +7139,7 @@
         <v>233.67</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>35.74488960951744</v>
+        <v>34.16515865177681</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>5</v>
@@ -7148,7 +7148,7 @@
         <v>22</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>224.38</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>21.12467056141546</v>
+        <v>21.12467056140946</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>5</v>
@@ -7285,7 +7285,7 @@
         <v>51.84</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>40.01848049648363</v>
+        <v>40.26853115484496</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>5</v>
@@ -7294,11 +7294,11 @@
         <v>23</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>28.1</v>
+        <v>29.1</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Pan American Silver: Still Room To Run With Silver Near $80 (NYSE:PAAS) - Seeking Alpha, Pan American Silver vs. SSR Mining: Which Mining Stock Wins Now? - Yahoo Finance, Can Pan American Silver maintain its solid silver production rally? - MSN</t>
+          <t>Pan American Silver: Still Room To Run With Silver Near $80 (NYSE:PAAS) - Seeking Alpha, Pan American Silver vs. SSR Mining: Which Mining Stock Wins Now? - Yahoo Finance, Beach, Gerdeman and Wozniak Secure Silver at Pan American Cup - goduke.com</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
         <v>19.04</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25.25920428149244</v>
+        <v>24.08119628949857</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>5</v>
@@ -7367,11 +7367,11 @@
         <v>22</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>First Majestic Silver launches $300M convertible notes offering - MSN, First Majestic Rises 23.6% YTD: Should You Buy the Stock Now or Wait? - Yahoo Finance, AG Stock Price, Quote &amp; Chart | FIRST MAJESTIC SILVER CORP (NYSE:AG) - ChartMill</t>
+          <t>First Majestic Rises 23.6% YTD: Should You Buy the Stock Now or Wait? - Yahoo Finance, AG Stock Price, Quote &amp; Chart | FIRST MAJESTIC SILVER CORP (NYSE:AG) - ChartMill, A Look at First Majestic Silver Corp (AG) After 6.7% Decline -- GF Value $8.99 vs Price $20.08 - GuruFocus</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
         <v>11.58</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>25.53622191770592</v>
+        <v>25.53622191771034</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>5</v>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Silvercorp Metals Inc (SVM) Stock Up 3.0% but GF Value Says Over - GuruFocus, Silvercorp Secures RMB 1.5 Billion (~US$220 Million) Syndicated Term Loan Facilities with 2x Oversubscription, Bolstering Financial Strength for Global Mining Growth - PR Newswire, Tincorp Provides Supplemental and Amending Disclosure on Proposed Santa Barbara Acquisition - TradingView</t>
+          <t>Silvercorp Metals Inc (SVM) Stock Up 3.0% but GF Value Says Over - GuruFocus, Tincorp Provides Supplemental and Amending Disclosure on Proposed Santa Barbara Acquisition - Investing News Network, Silvercorp Secures RMB 1.5 Billion (~US$220 Million) Syndicated Term Loan Facilities with 2x Oversubscription, Bolstering Financial Strength for Global Mining Growth - PR Newswire</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
         <v>17.88</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>27.9621983412582</v>
+        <v>27.96219834125584</v>
       </c>
       <c r="F97" s="2" t="n">
         <v>5</v>
@@ -7577,7 +7577,7 @@
         <v>63.69</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>24.98903891722411</v>
+        <v>27.10461202263113</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>0</v>
@@ -7586,11 +7586,11 @@
         <v>23</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>8</v>
+        <v>16.4</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>SLV Is Up 145% in One Year. Is the iShares Silver Trust Still Worth Buying? - The Motley Fool, Silver Slides As Stocks Stay Firm, Hedges Cool - Sahm, Silver is outperforming gold in 2026. Does SLV deserve a spot in your portfolio? - MSN</t>
+          <t>SLV Is Up 145% in One Year. Is the iShares Silver Trust Still Worth Buying? - The Motley Fool, 7 Best Silver ETFs to Buy in 2026 - U.S. News Money, Market Movers: iShares Silver Trust Up 12% - Yahoo Finance</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
         <v>56.53</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>33.91245993786859</v>
+        <v>34.15046552197702</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>10</v>
@@ -7657,7 +7657,7 @@
         <v>30</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>167.06</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>45.95979704055804</v>
+        <v>45.16720097046343</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>10</v>
@@ -7730,7 +7730,7 @@
         <v>30</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>516.2</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>31.28702889383209</v>
+        <v>30.58414726704795</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>0</v>
@@ -7803,7 +7803,7 @@
         <v>23</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>13.1</v>
+        <v>10.3</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>6834.26</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>57.70736001617205</v>
+        <v>57.70736001617377</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>10</v>
@@ -7940,7 +7940,7 @@
         <v>51.94</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45.16406353562228</v>
+        <v>45.1640635356184</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>10</v>
@@ -8013,7 +8013,7 @@
         <v>3421.3</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>14.16733566672025</v>
+        <v>13.46898022108397</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>0</v>
@@ -8022,11 +8022,11 @@
         <v>15</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Anglo American draws three bidders for coal sale - Mining.com, Anglo Advances Coal Business Sale After Setback With Peabody - Bloomberg.com, Anglo American has at least three potential buyers for Australian coal business - Bloomberg - Seeking Alpha</t>
+          <t>Anglo American draws three bidders for coal sale - Mining.com, Anglo Advances Coal Business Sale After Setback With Peabody - Bloomberg.com, Anglo American has at least three suitors for Australian coal business, Bloomberg News reports - Reuters</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
         <v>55.71</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>24.62162220379804</v>
+        <v>24.62162220385576</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>5</v>
@@ -8159,7 +8159,7 @@
         <v>3412.96</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>44.17203686386581</v>
+        <v>43.0644963234673</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>5</v>
@@ -8168,7 +8168,7 @@
         <v>23</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>34.44</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>47.92343790829618</v>
+        <v>47.92343790829339</v>
       </c>
       <c r="F107" s="2" t="n">
         <v>5</v>
@@ -8305,7 +8305,7 @@
         <v>10.85</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>12.02384606934956</v>
+        <v>12.02384606934857</v>
       </c>
       <c r="F108" s="2" t="n">
         <v>5</v>
@@ -8378,7 +8378,7 @@
         <v>76.27</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.21908269823107</v>
+        <v>29.21908269822954</v>
       </c>
       <c r="F109" s="2" t="n">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>174.38</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>31.13236002623803</v>
+        <v>30.37621163762637</v>
       </c>
       <c r="F110" s="2" t="n">
         <v>10</v>
@@ -8460,11 +8460,11 @@
         <v>30</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>-15.5</v>
+        <v>-18.5</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Albemarle teenager charged in 2024 drive-by shooting - WVIR, Waynesboro man arrested on charges from Madison, Charlottesville and Albemarle - cbs19news.com, Albemarle Fell 10% This Week. Here’s Where the Stock Could Go in 2026 - TIKR.com</t>
+          <t>Albemarle teenager charged in 2024 drive-by shooting - WVIR, Albemarle Fell 10% This Week. Here’s Where the Stock Could Go in 2026 - TIKR.com, Waynesboro man arrested on charges from Madison, Charlottesville and Albemarle - cbs19news.com</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
         <v>82.20999999999999</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>39.42140291259129</v>
+        <v>38.11132080667034</v>
       </c>
       <c r="F111" s="2" t="n">
         <v>5</v>
@@ -8531,11 +8531,11 @@
         <v>22</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>29.7</v>
+        <v>24.4</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>ALB vs. SQM: Which Lithium Stock Should You Bet on Now? - Zacks Investment Research, Sociedad Quimica Y Minera De Chile SA (SQM) Stock Up 3.9% but GF Value Says Overvalued -- GF Score: 84/100 - GuruFocus, SQM (NYSE: SQM) details Atacama lithium JV, price swings and $2.7B capex - Stock Titan</t>
+          <t>A Look At SQM’s Valuation After Rothschild Redburn’s Cautious Lithium Outlook - Yahoo Finance, ALB vs. SQM: Which Lithium Stock Should You Bet on Now? - Zacks Investment Research, SQM (NYSE: SQM) details Atacama lithium JV, price swings and $2.7B capex - Stock Titan</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
         <v>3.48</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>44.49786200187241</v>
+        <v>44.01691296136969</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>5</v>
@@ -8604,11 +8604,11 @@
         <v>30</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>18</v>
+        <v>16.1</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Standard Lithium reaches operational milestones at Arkansas demonstration plant - Magnolia Reporter, Standard Lithium Reaches Major Operational Milestones at Arkansas Demonstration Plant - Yahoo Finance, SW Arkansas' Standard Lithium to make billion dollar decision on moving forward - The Shreveport-Bossier City Advocate</t>
+          <t>Standard Lithium Reaches Major Operational Milestones at Arkansas Demonstration Plant - Yahoo Finance, Standard Lithium reaches operational milestones at Arkansas demonstration plant - Magnolia Reporter, SW Arkansas' Standard Lithium to make billion dollar decision on moving forward - The Shreveport-Bossier City Advocate</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
         <v>5.34</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>16.89152532256411</v>
+        <v>16.89152532255789</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>5</v>
@@ -8741,7 +8741,7 @@
         <v>2.07</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>14.29420918226551</v>
+        <v>14.29420918226452</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>5</v>
@@ -8814,7 +8814,7 @@
         <v>0.3</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>36.8188361562791</v>
+        <v>36.81883615627727</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>5</v>
@@ -8887,7 +8887,7 @@
         <v>18.23</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>34.9926072359133</v>
+        <v>34.99260723591604</v>
       </c>
       <c r="F116" s="2" t="n">
         <v>5</v>
@@ -8958,7 +8958,7 @@
         <v>5.42</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>31.43405641278974</v>
+        <v>31.43405641278975</v>
       </c>
       <c r="F117" s="2" t="n">
         <v>15</v>
@@ -9029,7 +9029,7 @@
         <v>23.23</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>28.77849039808022</v>
+        <v>28.77849039807985</v>
       </c>
       <c r="F118" s="2" t="n">
         <v>0</v>
@@ -9102,7 +9102,7 @@
         <v>77.58</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>4.464879073196001</v>
+        <v>4.464879073194393</v>
       </c>
       <c r="F119" s="2" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
         <v>15.31</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>29.21615448035514</v>
+        <v>29.20921235531596</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
         <v>23</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>214.8</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>7.059040046171329</v>
+        <v>5.811472642243599</v>
       </c>
       <c r="F121" s="2" t="n">
         <v>10</v>
@@ -9257,11 +9257,11 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>-31.8</v>
+        <v>-36.8</v>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Software stocks plunge on ServiceNow, IBM results as AI fears escalate - CNBC, Bank of America has a blunt message for investors on IBM stock - thestreet.com, IBM’s stock falls as software revenue underwhelms - MarketWatch</t>
+          <t>Software stocks plunge on ServiceNow, IBM results as AI fears escalate - CNBC, Bank of America has a blunt message for investors on IBM stock - thestreet.com, These Stocks Are Today’s Movers: Tesla, IBM, Oklo, ServiceNow, United Rentals, and More - Barron's</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
         <v>39.53</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>42.79402947238642</v>
+        <v>42.24461439252489</v>
       </c>
       <c r="F122" s="2" t="n">
         <v>10</v>
@@ -9330,7 +9330,7 @@
         <v>23</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>19.2</v>
+        <v>17</v>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>15.38</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>40.88922916910316</v>
+        <v>41.22557308058299</v>
       </c>
       <c r="F123" s="2" t="n">
         <v>5</v>
@@ -9403,7 +9403,7 @@
         <v>30</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>17.12</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>35.48607352840812</v>
+        <v>34.73449630383305</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>5</v>
@@ -9476,7 +9476,7 @@
         <v>23</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>47.67042839154995</v>
+        <v>45.91091571562072</v>
       </c>
       <c r="F125" s="2" t="n">
         <v>15</v>
@@ -9549,11 +9549,11 @@
         <v>23</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>18.7</v>
+        <v>11.6</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc. Announces Deployment-Ready NeuraWave, a Photonic Computing Platform for Real-time AI Inference at the Edge - PR Newswire, Quantum Computing Inc. Launches Photonic AI Platform - The Quantum Insider, Quantum Computing Inc. Launches NeuraWave Photonic Platform for Edge AI Inference - Quantum Computing Report</t>
+          <t>Quantum Computing Inc. Launches Photonic AI Platform - The Quantum Insider, Quantum Computing Inc. Announces Deployment-Ready NeuraWave, a Photonic Computing Platform for Real-time AI Inference at the Edge - PR Newswire, Quantum Computing Inc. Launches NeuraWave Photonic Platform for Edge AI Inference - Quantum Computing Report</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
         <v>393.17</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>11.27565662191312</v>
+        <v>11.22840033658935</v>
       </c>
       <c r="F126" s="2" t="n">
         <v>5</v>
@@ -9622,11 +9622,11 @@
         <v>7</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>-22.9</v>
+        <v>-23.1</v>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>20,000 job cuts at Meta, Microsoft raise concern that AI-driven labor crisis is here - CNBC, Meta to cut 8,000 jobs, Microsoft offers buyouts to staff as AI spending costs hit Big Tech workers - Yahoo Finance, Microsoft and Meta announce large staff reductions as they spend big on AI - The Guardian</t>
+          <t>20,000 job cuts at Meta, Microsoft raise concern that AI-driven labor crisis is here - CNBC, Microsoft and Meta announce large staff reductions as they spend big on AI - The Guardian, Meta and Microsoft have joined the tech layoff tsunami – but is AI really to blame? - The Conversation</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
         <v>318.89</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>11.55918370000408</v>
+        <v>11.94596708751747</v>
       </c>
       <c r="F127" s="2" t="n">
         <v>5</v>
@@ -9695,11 +9695,11 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Nvidia market cap back above $5T, Alphabet to invest $40B in Anthropic - Yahoo Finance, Alphabet Next: Google Cloud Says 75% of Customers Use AI as Pichai Targets $175B-$185B CapEx - Yahoo Finance, Going Into Earnings, Is Alphabet Stock a Buy, a Sell, or Fairly Valued? - Morningstar</t>
+          <t>Nvidia market cap back above $5T, Alphabet to invest $40B in Anthropic - Yahoo Finance, Going Into Earnings, Is Alphabet Stock a Buy, a Sell, or Fairly Valued? - Morningstar, Google to invest up to $40 billion in AI rival Anthropic - Reuters</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
         <v>197.38</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>14.95112826582013</v>
+        <v>15.10914148297219</v>
       </c>
       <c r="F128" s="2" t="n">
         <v>5</v>
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>192.84</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>29.86958673874961</v>
+        <v>30.33136985916175</v>
       </c>
       <c r="F129" s="2" t="n">
         <v>5</v>
@@ -9841,11 +9841,11 @@
         <v>8</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Nvidia stock closes at record, pushing market cap past $5 trillion - CNBC, Nvidia shareholders hit the jackpot. They're suing anyway. - Reuters, Oklo, NVIDIA, and Los Alamos National Laboratory Collaborate to Advance Nuclear Fuel Validation at Los Alamos in Support of Nuclear-Powered AI Factories - Oklo Inc.</t>
+          <t>Nvidia stock closes at record, pushing market cap past $5 trillion - CNBC, Meet the Biggest Threat to Nvidia in AI Chips. It's Not AMD, Intel, or Broadcom. - The Motley Fool, Meet the Biggest Threat to Nvidia in AI Chips. It's Not AMD, Intel, or Broadcom. - Yahoo Finance</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
@@ -9905,7 +9905,7 @@
         <v>322.05</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>14.75226622074103</v>
+        <v>14.83686220831007</v>
       </c>
       <c r="F130" s="2" t="n">
         <v>5</v>
@@ -9914,11 +9914,11 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>AMD Stock Is Up 13% Today – Is It Outperforming Other CPU Companies Like ARM? - Yahoo Finance, AMD’s Flagship Ryzen 9 9950X3D2 Outsells Every Intel CPU On Amazon As X3D Chips Dominate Top 10 - Wccftech, AMD Launches EXPO 1.2 for CUDIMM and Low-Latency DDR5 Memory - TechPowerUp</t>
+          <t>Why AMD Stock Surged Today - The Motley Fool, Meet the Biggest Threat to Nvidia in AI Chips. It's Not AMD, Intel, or Broadcom. - The Motley Fool, The Top-Tier iBuypower Gaming PC With AMD Ryzen 9 9950X3D CPU and 5090 GPU Drops Below $5,000 - IGN</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
         <v>76.43000000000001</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>14.48162811993968</v>
+        <v>14.54360363259357</v>
       </c>
       <c r="F131" s="2" t="n">
         <v>5</v>
@@ -9987,11 +9987,11 @@
         <v>8</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Intel stock soars on Q1 earnings beat, strong outlook - Yahoo Finance, AMD shares soar 12% on no company news. Here's what has investors so excited - CNBC, Anything Intel Can Do, Advanced Micro Devices Might Be Able to Do Better - Barron's</t>
+          <t>Intel stock soars on Q1 earnings beat, strong outlook - Yahoo Finance, AMD shares soar 12% on no company news. Here's what has investors so excited - CNBC, AMD stock jumps to record high on upgrade, Intel results - Yahoo Finance</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -10051,7 +10051,7 @@
         <v>372.65</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>29.93152728303761</v>
+        <v>30.57749224825815</v>
       </c>
       <c r="F132" s="2" t="n">
         <v>5</v>
@@ -10060,7 +10060,7 @@
         <v>15</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>19.7</v>
+        <v>22.3</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>1249.6</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>27.36837170088373</v>
+        <v>28.09153543786407</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>5</v>
@@ -10133,11 +10133,11 @@
         <v>15</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>9.5</v>
+        <v>12.4</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>ASML Loses Nearly $17 Billion of Value as TSMC Shuns Top-End Machines - WSJ, Taiwan Semiconductor (TSM) and ASML’s post-earnings Price Movements May be a Sign of What’s to Come from Chip Firms - Yahoo Finance, The MATCH Act Could Blow a Hole in ASML's Revenue. Here's What Investors Need to Know. - The Motley Fool</t>
+          <t>ASML Loses Nearly $17 Billion of Value as TSMC Shuns Top-End Machines - WSJ, ASML Ups Guidance As AI Partnership And €12b Buyback Shape Cash Returns - simplywall.st, The MATCH Act Could Blow a Hole in ASML's Revenue. Here's What Investors Need to Know. - The Motley Fool</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
         <v>386.15</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>20.45360354893186</v>
+        <v>21.8802192080785</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>5</v>
@@ -10206,11 +10206,11 @@
         <v>8</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Jim Cramer on Applied Materials: “It’s Not a Good Buy, It’s a Great Buy” - Yahoo Finance, Applied Materials (AMAT): Analyzing the Next Stock to Breach the Trillion Dollar Barrier - Yahoo Finance, Chart of the Day: All Indicators on Applied Materials Point Higher - TheStreet Pro</t>
+          <t>Applied Materials and Photronics Stocks Trade Up, What You Need To Know - StockStory, Advantest Partnership Puts Applied Materials’ EPIC R&amp;D And Valuation In Focus - simplywall.st, Applied Materials: The Next Correction Candidate (NASDAQ:AMAT) - Seeking Alpha</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
         <v>247.94</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>41.57576977087768</v>
+        <v>42.32389858736978</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>5</v>
@@ -10279,7 +10279,7 @@
         <v>22</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>38.3</v>
+        <v>41.3</v>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>1791.67</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>22.89076983649683</v>
+        <v>22.89076983649571</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>5</v>
@@ -10416,7 +10416,7 @@
         <v>152.14</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>14.9388114828525</v>
+        <v>14.93881148285323</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>5</v>
@@ -10487,7 +10487,7 @@
         <v>391.44</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>30.54847773163385</v>
+        <v>29.83056702650061</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>10</v>
@@ -10496,11 +10496,11 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>22.2</v>
+        <v>19.3</v>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Broadcom makes unexpected strategic move with Google - thestreet.com, Broadcom Inc. (AVGO): Safe Play Within Semiconductor Sector - Yahoo Finance, Is Broadcom Inc. (AVGO) Among the Best AI Stocks to Buy According to Billionaire Ken Griffin? - Yahoo Finance</t>
+          <t>Broadcom makes unexpected strategic move with Google - thestreet.com, Broadcom Inc. (AVGO): Safe Play Within Semiconductor Sector - Yahoo Finance, Meet the Biggest Threat to Nvidia in AI Chips. It's Not AMD, Intel, or Broadcom. - The Motley Fool</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -10560,7 +10560,7 @@
         <v>137.82</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>34.08733943664479</v>
+        <v>31.59397502615737</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>5</v>
@@ -10569,11 +10569,11 @@
         <v>8</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>24.3</v>
+        <v>14.4</v>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Why is April 29 Important for Qualcomm Investors? - Yahoo Finance, Is Qualcomm The Next AI Stock To Surge? - Trefis, The chip rally is getting so intense, even Qualcomm gets to surge - Sherwood News</t>
+          <t>Why is April 29 Important for Qualcomm Investors? - Yahoo Finance, Qualcomm Stock Hits Key Support – Buying Opportunity? - Trefis, Tested: Qualcomm’s Snapdragon X2 Elite is faster, but the battery life hit is real - PCWorld</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
         <v>46.73</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>14.98245142399759</v>
+        <v>14.29084131493407</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>0</v>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>39.9</v>
+        <v>37.2</v>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>54.15</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>17.27621910348542</v>
+        <v>17.99897189438654</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>10</v>
@@ -10715,7 +10715,7 @@
         <v>8</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>17.1</v>
+        <v>20</v>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>225.96</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>36.81790634803704</v>
+        <v>36.51307701878589</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>10</v>
@@ -10788,11 +10788,11 @@
         <v>7</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>19.3</v>
+        <v>18.1</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>New Buy Rating for NXP Semiconductors (NXPI), the Technology Giant - The Globe and Mail, BlackRock (NXPI) reports 20.7M shares, 8.2% stake in NXP Semiconductors (Amend. No.4) - Stock Titan, Wells Fargo resets NXP Semiconductors forecast ahead of earnings - MSN</t>
+          <t>New Buy Rating for NXP Semiconductors (NXPI), the Technology Giant - The Globe and Mail, BlackRock (NXPI) reports 20.7M shares, 8.2% stake in NXP Semiconductors (Amend. No.4) - Stock Titan, NXP Semiconductors surges as traders position ahead of earnings and margin-focused updates - Quiver Quantitative</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -10852,7 +10852,7 @@
         <v>91.11</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>18.00765384920539</v>
+        <v>18.00765384920368</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>5</v>
@@ -10923,7 +10923,7 @@
         <v>28.92</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>32.60082858614901</v>
+        <v>32.00037465431066</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>0</v>
@@ -10932,7 +10932,7 @@
         <v>15</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>30.4</v>
+        <v>28</v>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>427.41</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>5.032586003647057</v>
+        <v>5.03258600365561</v>
       </c>
       <c r="F145" s="2" t="n">
         <v>0</v>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Semiconductor Stocks Are on a Historic Winning Streak. Why It’s Time to Cash In. - Barron's, SOXX Has Never Had a Run Like This - ETF.com, “The Big Short” Bets Against Semiconductor ETF, Warns of Technical Correction - NAI500</t>
+          <t>SOXX Has Never Had a Run Like This - ETF.com, Semiconductor Stocks Are on a Historic Winning Streak. Why It’s Time to Cash In. - Barron's, “The Big Short” Bets Against Semiconductor ETF, Warns of Technical Correction - NAI500</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
@@ -11074,11 +11074,11 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>SOXX Has Never Had a Run Like This - ETF.com, Fears of an AI Bubble Are Growing. Should SMH Investors Be Worried? - The Motley Fool, Semiconductor ETF Nabs New High, Outpaces Broader Market - Schaeffer's Investment Research</t>
+          <t>$VanEck Semiconductor ETF (SMH.US)$ Quan Ge's US Stock Investment Review 25-4-2026: - Moomoo, SMH Returned Over 120% in One Year. Is the VanEck Semiconductor ETF Still a Buy? - AOL.com, SOXX Has Never Had a Run Like This - ETF.com</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
         <v>164.96</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>14.38222570065262</v>
+        <v>14.38222570064988</v>
       </c>
       <c r="F147" s="2" t="n">
         <v>5</v>
@@ -11211,7 +11211,7 @@
         <v>83.48999999999999</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>28.83615190163953</v>
+        <v>27.55349030718521</v>
       </c>
       <c r="F148" s="2" t="n">
         <v>5</v>
@@ -11220,11 +11220,11 @@
         <v>15</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>-24.7</v>
+        <v>-29.8</v>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Analysts reset ServiceNow stock price target after earnings - thestreet.com, These Stocks Are Today’s Movers: Tesla, IBM, Oklo, ServiceNow, United Rentals, and More - Barron's, ServiceNow and Google Cloud unite AI agents for autonomous enterprise operations - Business Wire</t>
+          <t>Analysts reset ServiceNow stock price target after earnings - thestreet.com, These Stocks Are Today’s Movers: Tesla, IBM, Oklo, ServiceNow, United Rentals, and More - Barron's, Stock Market Holds Near Highs As Intel Leads Chip Surge; Apple, Tesla, ServiceNow In Focus: Weekly Review - Investor's Business Daily</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
         <v>132.49</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>32.88549067638925</v>
+        <v>31.97528877482059</v>
       </c>
       <c r="F149" s="2" t="n">
         <v>5</v>
@@ -11293,11 +11293,11 @@
         <v>23</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>-0.5</v>
+        <v>-4.1</v>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Palantir under fire for X 'manifesto' from co-founder Alex Karp - BBC, Palantir Is Helping Trump’s IRS Conduct “Massive-Scale” Data Mining - The Intercept, Palantir inks $300 million deal with USDA to safeguard food supply - CNBC</t>
+          <t>Palantir under fire for X 'manifesto' from co-founder Alex Karp - BBC, Why Palantir Stock Is Slumping in 2026—and Why It Could Bounce Back - Barron's, Palantir inks $300 million deal with USDA to safeguard food supply - CNBC</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -11357,7 +11357,7 @@
         <v>8</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>24.74966351873523</v>
+        <v>21.84460661373938</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>5</v>
@@ -11366,11 +11366,11 @@
         <v>15</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>-1</v>
+        <v>-12.6</v>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>C3 AI CTO Nikhil Krishnan on Moving Government AI From Hype to Mission Impact - MeriTalk, The Wrap: AI Profile: C3 AI’s Nikhil Krishnan; Section 702 Scramble; DOD’s $350B Gamble - LinkedIn, C3.ai (AI) Valuation Check As Shares Outperform And Earnings Turnaround Hopes Build - simplywall.st</t>
+          <t>C3 AI CTO Nikhil Krishnan on Moving Government AI From Hype to Mission Impact - MeriTalk, The Wrap: AI Profile: C3 AI’s Nikhil Krishnan; Section 702 Scramble; DOD’s $350B Gamble - LinkedIn, C3.ai crashes as Wall Street gets the ick following guidance shortfall, mass layoffs - MSN</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
@@ -11430,7 +11430,7 @@
         <v>9.6</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>24.25539894028224</v>
+        <v>23.13441275618183</v>
       </c>
       <c r="F151" s="2" t="n">
         <v>5</v>
@@ -11439,11 +11439,11 @@
         <v>15</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>-3</v>
+        <v>-7.5</v>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>UiPath Brings its AI Document Processing Solution to Google Cloud Marketplace with Gemini-Powered Automation - UiPath, What is behind UiPath stock's recent gain in value today - Traders Union, Why UiPath Shares Are Slumping Despite Profit - TipRanks</t>
+          <t>UiPath Brings its AI Document Processing Solution to Google Cloud Marketplace with Gemini-Powered Automation - UiPath, UiPath CTO Raghu Malpani takes expanded role as chief product and technology officer - MSN, What is behind UiPath stock's recent gain in value today - Traders Union</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
         <v>129.93</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>6.328986112031243</v>
+        <v>6.328986112030954</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>5</v>
@@ -11576,7 +11576,7 @@
         <v>119.89</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>24.9017749447383</v>
+        <v>25.6159453652769</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>5</v>
@@ -11585,11 +11585,11 @@
         <v>15</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>-0.4</v>
+        <v>2.5</v>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Datadog Inc (DDOG) Stock Price, Trades &amp; News - GuruFocus, Costly GPU sprawl tackled by Datadog observability service - IT Europa, Datadog Tames AI GPU Spend - Enterprise Times</t>
+          <t>Datadog gets 90-day upside catalyst watch at Citi - MSN, Datadog Inc (DDOG) Stock Price, Trades &amp; News - GuruFocus, Costly GPU sprawl tackled by Datadog observability service - IT Europa</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -11649,7 +11649,7 @@
         <v>234.81</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>15.38582123816298</v>
+        <v>13.7144457642057</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>5</v>
@@ -11658,7 +11658,7 @@
         <v>15</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>1.5</v>
+        <v>-5.1</v>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>191.73</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>21.44633652828637</v>
+        <v>21.44633652828443</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>5</v>
@@ -11795,7 +11795,7 @@
         <v>110.89</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>24.40582565032285</v>
+        <v>24.40582565031848</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>5</v>
@@ -11868,7 +11868,7 @@
         <v>149.19</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>25.34200414085299</v>
+        <v>25.34200414084952</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>5</v>
@@ -11941,7 +11941,7 @@
         <v>34.59</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>14.84006970189454</v>
+        <v>14.84006970189436</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>0</v>
@@ -12014,7 +12014,7 @@
         <v>74.06</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>15.38132094778123</v>
+        <v>15.381320947785</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>0</v>
@@ -12087,7 +12087,7 @@
         <v>51.06</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>2.702495199629714</v>
+        <v>2.702495199635964</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>0</v>
@@ -12160,7 +12160,7 @@
         <v>47.79</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>56.09667890426756</v>
+        <v>56.09667890427048</v>
       </c>
       <c r="F161" s="3" t="n">
         <v>10</v>
@@ -12233,7 +12233,7 @@
         <v>13490.74</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>14.88442850299303</v>
+        <v>14.88442850299048</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>0</v>
@@ -12306,7 +12306,7 @@
         <v>111.3</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>18.69019542821202</v>
+        <v>19.35146821662823</v>
       </c>
       <c r="F163" s="2" t="n">
         <v>0</v>
@@ -12315,7 +12315,7 @@
         <v>15</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>-5.2</v>
+        <v>-2.6</v>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>359.24</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>24.26703653298735</v>
+        <v>24.74349408411058</v>
       </c>
       <c r="F164" s="2" t="n">
         <v>10</v>
@@ -12388,7 +12388,7 @@
         <v>15</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>99.09</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>27.05370385199809</v>
+        <v>27.05370385199585</v>
       </c>
       <c r="F165" s="2" t="n">
         <v>0</v>
@@ -12525,7 +12525,7 @@
         <v>207.11</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>28.41152950002905</v>
+        <v>29.36785417422016</v>
       </c>
       <c r="F166" s="2" t="n">
         <v>5</v>
@@ -12534,7 +12534,7 @@
         <v>7</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>45.6</v>
+        <v>49.5</v>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>172.22</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>38.53392278773893</v>
+        <v>38.73722361399523</v>
       </c>
       <c r="F167" s="2" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>30</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>1554.63</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>29.66406554915348</v>
+        <v>28.91152747907234</v>
       </c>
       <c r="F168" s="2" t="n">
         <v>5</v>
@@ -12680,7 +12680,7 @@
         <v>15</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>18.7</v>
+        <v>15.6</v>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>136.63</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>36.79811651072612</v>
+        <v>36.79811651074522</v>
       </c>
       <c r="F169" s="2" t="n">
         <v>5</v>
@@ -12817,7 +12817,7 @@
         <v>169.47</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>32.0483119878943</v>
+        <v>32.77506420388779</v>
       </c>
       <c r="F170" s="2" t="n">
         <v>10</v>
@@ -12826,7 +12826,7 @@
         <v>15</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>24.01</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>35.01657933462828</v>
+        <v>36.44498858135491</v>
       </c>
       <c r="F171" s="2" t="n">
         <v>0</v>
@@ -12899,7 +12899,7 @@
         <v>30</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>22.44</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>31.10378978029157</v>
+        <v>31.10378978029024</v>
       </c>
       <c r="F172" s="2" t="n">
         <v>10</v>
@@ -13036,7 +13036,7 @@
         <v>65.11</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>42.26440941915101</v>
+        <v>42.50565679744106</v>
       </c>
       <c r="F173" s="2" t="n">
         <v>5</v>
@@ -13045,7 +13045,7 @@
         <v>30</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>285.44</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>44.13896662368802</v>
+        <v>44.79716534911742</v>
       </c>
       <c r="F174" s="2" t="n">
         <v>5</v>
@@ -13118,7 +13118,7 @@
         <v>23</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>89.01000000000001</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>39.49313828908117</v>
+        <v>39.60991990007717</v>
       </c>
       <c r="F175" s="2" t="n">
         <v>5</v>
@@ -13191,7 +13191,7 @@
         <v>23</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>27.06</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>36.33955059759762</v>
+        <v>36.3395505976026</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>5</v>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Bank Maintains Buy Rating on ServiceNow (NOW) - Yahoo Finance, Deutsche Bank's ex-Citi bankers are proliferating. Its ex-Numis people are wary - eFinancialCareers, Molina Healthcare price target raised to $129 from $109 at Deutsche Bank - TipRanks</t>
+          <t>Deutsche Bank's ex-Citi bankers are proliferating. Its ex-Numis people are wary - eFinancialCareers, Deutsche Bank Maintains Buy Rating on ServiceNow (NOW) - Yahoo Finance, Molina Healthcare price target raised to $129 from $109 at Deutsche Bank - TipRanks</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
@@ -13328,7 +13328,7 @@
         <v>33.94</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>44.34433186614392</v>
+        <v>43.66304663196589</v>
       </c>
       <c r="F177" s="2" t="n">
         <v>5</v>
@@ -13337,7 +13337,7 @@
         <v>23</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>23.84</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>39.84540382865637</v>
+        <v>39.64788656216028</v>
       </c>
       <c r="F178" s="2" t="n">
         <v>10</v>
@@ -13410,11 +13410,11 @@
         <v>15</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>ING Bank Śląski completes acquisition of Goldman Sachs TFI - Yahoo Finance Singapore, Japanese inflation quickened in March, complicating Bank of Japan outlook | snaps - ING THINK economic and financial analysis | ING THINK, ING Group (ING) Projected to Post Earnings on Thursday - MarketBeat</t>
+          <t>ING Bank Śląski completes acquisition of Goldman Sachs TFI - Yahoo Finance UK, Japanese inflation quickened in March, complicating Bank of Japan outlook | snaps - ING THINK economic and financial analysis | ING THINK, ING Group (ING) Projected to Post Earnings on Thursday - MarketBeat</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -13474,7 +13474,7 @@
         <v>64.01000000000001</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>66.54465530080412</v>
+        <v>65.82306368277497</v>
       </c>
       <c r="F179" s="3" t="n">
         <v>10</v>
@@ -13483,7 +13483,7 @@
         <v>30</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>10.2</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>39.18868970126586</v>
+        <v>39.64462718927382</v>
       </c>
       <c r="F180" s="2" t="n">
         <v>5</v>
@@ -13556,7 +13556,7 @@
         <v>30</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>-3.2</v>
+        <v>-1.4</v>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>18.58</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>61.37147594242799</v>
+        <v>61.98803164995827</v>
       </c>
       <c r="F181" s="3" t="n">
         <v>10</v>
@@ -13629,7 +13629,7 @@
         <v>30</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="I181" s="3" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>29.11</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>26.16728688869212</v>
+        <v>24.95010686385935</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>10</v>
@@ -13702,7 +13702,7 @@
         <v>7</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43.88</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>30.90030150487337</v>
+        <v>31.53273537754164</v>
       </c>
       <c r="F183" s="2" t="n">
         <v>5</v>
@@ -13775,7 +13775,7 @@
         <v>15</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>23.6</v>
+        <v>26.1</v>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>99.75</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>44.35563610123719</v>
+        <v>44.35563610122887</v>
       </c>
       <c r="F184" s="2" t="n">
         <v>10</v>
@@ -13912,7 +13912,7 @@
         <v>858.25</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>35.84181004390074</v>
+        <v>36.43913687392807</v>
       </c>
       <c r="F185" s="2" t="n">
         <v>5</v>
@@ -13921,7 +13921,7 @@
         <v>23</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>11.4</v>
+        <v>13.8</v>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>174.14</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>23.48495752365188</v>
+        <v>23.484957523648</v>
       </c>
       <c r="F186" s="2" t="n">
         <v>10</v>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Morgan Stanley resets gold price target for rest of 2026 - thestreet.com, Morgan Stanley BTC risk factors: you can’t say you weren’t warned - CoinGeek, AI is going to change the video game industry. Morgan Stanley says these 4 stocks will be winners - CNBC</t>
+          <t>Morgan Stanley resets gold price target for rest of 2026 - thestreet.com, Morgan Stanley BTC risk factors: you can’t say you weren’t warned - CoinGeek, Why Morgan Stanley's stablecoin bet could reshape finance - Yahoo Finance</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -14058,7 +14058,7 @@
         <v>967.5599999999999</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>19.12177356891292</v>
+        <v>19.83073049224989</v>
       </c>
       <c r="F187" s="2" t="n">
         <v>10</v>
@@ -14067,11 +14067,11 @@
         <v>15</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>-3.5</v>
+        <v>-0.7</v>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Meet the Unstoppable BlackRock ETF Obliterating the S&amp;P 500, the Nasdaq-100, and the Dow Jones Right Now - The Motley Fool, How To Build A $7,000/Mo Income Using BlackRock's 8% Yielding 32 CEFs (NYSEARCA:SPY) - Seeking Alpha, BlackRock says investors need to look beyond the 60/40. Here’s how it is diversifying portfolios right now - CNBC</t>
+          <t>BlackRock says investors need to look beyond the 60/40. Here’s how it is diversifying portfolios right now - CNBC, Meet the Unstoppable BlackRock ETF Obliterating the S&amp;P 500, the Nasdaq-100, and the Dow Jones Right Now - The Motley Fool, How To Build A $7,000/Mo Income Using BlackRock's 8% Yielding 32 CEFs (NYSEARCA:SPY) - Seeking Alpha</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
@@ -14131,7 +14131,7 @@
         <v>58.8</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>34.97339248843601</v>
+        <v>34.97339248843668</v>
       </c>
       <c r="F188" s="2" t="n">
         <v>0</v>
@@ -14204,7 +14204,7 @@
         <v>388</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>42.35639242455492</v>
+        <v>42.35639242455438</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>10</v>
@@ -14277,7 +14277,7 @@
         <v>551.8</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>56.53069179691724</v>
+        <v>56.5306917969171</v>
       </c>
       <c r="F190" s="3" t="n">
         <v>10</v>
@@ -14350,7 +14350,7 @@
         <v>272</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>59.55789496377471</v>
+        <v>59.12102109007984</v>
       </c>
       <c r="F191" s="3" t="n">
         <v>10</v>
@@ -14359,7 +14359,7 @@
         <v>23</v>
       </c>
       <c r="H191" s="3" t="n">
-        <v>26.2</v>
+        <v>24.5</v>
       </c>
       <c r="I191" s="3" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>118.89</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>57.12670764884718</v>
+        <v>57.12670764884795</v>
       </c>
       <c r="F192" s="3" t="n">
         <v>10</v>
@@ -14496,7 +14496,7 @@
         <v>507.22</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>53.76775742229438</v>
+        <v>54.50951687712794</v>
       </c>
       <c r="F193" s="3" t="n">
         <v>5</v>
@@ -14505,7 +14505,7 @@
         <v>23</v>
       </c>
       <c r="H193" s="3" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>41.03</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>41.93926817923855</v>
+        <v>41.9392681792397</v>
       </c>
       <c r="F194" s="2" t="n">
         <v>10</v>
@@ -14642,7 +14642,7 @@
         <v>37.89</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>27.88446892798517</v>
+        <v>27.88446892798407</v>
       </c>
       <c r="F195" s="2" t="n">
         <v>10</v>
@@ -14715,7 +14715,7 @@
         <v>434.56</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>17.73507714456839</v>
+        <v>17.73507714457097</v>
       </c>
       <c r="F196" s="2" t="n">
         <v>5</v>
@@ -14788,7 +14788,7 @@
         <v>301.96</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>35.71780591086956</v>
+        <v>35.3957418054523</v>
       </c>
       <c r="F197" s="2" t="n">
         <v>5</v>
@@ -14797,7 +14797,7 @@
         <v>22</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>14.9</v>
+        <v>13.6</v>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>1770.79</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>23.954329919071</v>
+        <v>23.55338144115958</v>
       </c>
       <c r="F198" s="2" t="n">
         <v>5</v>
@@ -14870,11 +14870,11 @@
         <v>15</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>-4.2</v>
+        <v>-5.8</v>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Markel Bell - ESPN, NFL Draft Results: Eagles pick Markel Bell at No. 68 - Bleeding Green Nation, 2026 NFL Draft: Miami Hurricanes OT Markel Bell Selected with the 68th Pick by the Philadelphia Eagles - State of The U</t>
+          <t>Markel Bell - ESPN, Eagles draft massive Miami offensive tackle Markel Bell in Round 3 - NBC Sports Philadelphia, 2026 NFL Draft: Miami Hurricanes OT Markel Bell Selected with the 68th Pick by the Philadelphia Eagles - State of The U</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -14934,7 +14934,7 @@
         <v>240.69</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>51.36307492387164</v>
+        <v>51.36307492386823</v>
       </c>
       <c r="F199" s="3" t="n">
         <v>10</v>
@@ -15005,7 +15005,7 @@
         <v>298.15</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>30.07211286108306</v>
+        <v>30.07211286107452</v>
       </c>
       <c r="F200" s="2" t="n">
         <v>10</v>
@@ -15078,7 +15078,7 @@
         <v>105.28</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>28.51496664993633</v>
+        <v>28.51496664993915</v>
       </c>
       <c r="F201" s="2" t="n">
         <v>10</v>
@@ -15151,7 +15151,7 @@
         <v>12922.22</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>31.1790780834744</v>
+        <v>38.16228967345743</v>
       </c>
       <c r="F202" s="2" t="n">
         <v>10</v>
@@ -15160,7 +15160,7 @@
         <v>8</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>12.7</v>
+        <v>40.6</v>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
@@ -15224,7 +15224,7 @@
         <v>80.08</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>33.71053422055269</v>
+        <v>32.97887174597766</v>
       </c>
       <c r="F203" s="2" t="n">
         <v>0</v>
@@ -15233,7 +15233,7 @@
         <v>23</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>42.8</v>
+        <v>39.9</v>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>38.5</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>19.41611196845663</v>
+        <v>19.41611196845807</v>
       </c>
       <c r="F204" s="2" t="n">
         <v>0</v>
@@ -15370,7 +15370,7 @@
         <v>111.9</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>28.61287442035608</v>
+        <v>28.61287442035269</v>
       </c>
       <c r="F205" s="2" t="n">
         <v>10</v>
@@ -15443,7 +15443,7 @@
         <v>434.92</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>8.601211767644914</v>
+        <v>4.302497060977638</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>5</v>
@@ -15452,7 +15452,7 @@
         <v>8</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>-17.6</v>
+        <v>-14.8</v>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>164.12</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>18.51603601592634</v>
+        <v>18.5160360159282</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>5</v>
@@ -15660,7 +15660,7 @@
         <v>444.26</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>24.96933776884389</v>
+        <v>24.9693377688475</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>10</v>
@@ -15733,7 +15733,7 @@
         <v>78.26000000000001</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>37.66583159565243</v>
+        <v>37.66583159565652</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>10</v>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Straumann Holding AG (OTCMKTS:SAUHY) Sees Significant Growth in Short Interest - MarketBeat, Assessing Straumann Holding (SWX:STMN) Valuation After Recent Weak Share Price Performance - Yahoo Finance, Janet Straumann Obituary and Online Memorial (2026) - Legacy obituary</t>
+          <t>Straumann Holding AG (OTCMKTS:SAUHY) Sees Significant Growth in Short Interest - MarketBeat, Assessing Straumann Holding (SWX:STMN) Valuation After Recent Weak Share Price Performance - Yahoo Finance, Straumann forecasts 2026 growth despite China procurement uncertainty, shares rise - Reuters</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
         <v>24.88</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>37.57946194614347</v>
+        <v>38.08214875403085</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>5</v>
@@ -15815,11 +15815,11 @@
         <v>15</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Genmab A/S (GMAB) Rating Lifted by Goldman Sachs on Strong 2026 Catalyst Outlook - Yahoo Finance, Genmab: Multiple Binaries Could Alter The Thesis (NASDAQ:GMAB) - Seeking Alpha, Genmab gains as Goldman upgrades stock to Buy on increased pipeline confidence - Investing.com</t>
+          <t>Genmab A/S (GMAB) Rating Lifted by Goldman Sachs on Strong 2026 Catalyst Outlook - Yahoo Finance, Genmab: Multiple Binaries Could Alter The Thesis (NASDAQ:GMAB) - Seeking Alpha, Genmab A/S (NASDAQ:GMAB) Raised to Strong-Buy at BNP Paribas Exane - MarketBeat</t>
         </is>
       </c>
       <c r="J211" s="2" t="inlineStr">
@@ -15879,7 +15879,7 @@
         <v>239</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>19.84445730224243</v>
+        <v>20.48206048086066</v>
       </c>
       <c r="F212" s="2" t="n">
         <v>5</v>
@@ -15888,7 +15888,7 @@
         <v>15</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>163</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>34.30088173783088</v>
+        <v>34.34834310039125</v>
       </c>
       <c r="F213" s="2" t="n">
         <v>5</v>
@@ -15961,7 +15961,7 @@
         <v>23</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>43.19</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>15.7423140574268</v>
+        <v>16.41906556673433</v>
       </c>
       <c r="F214" s="2" t="n">
         <v>0</v>
@@ -16034,7 +16034,7 @@
         <v>15</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>35.56</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>17.92937462219492</v>
+        <v>17.91240536608064</v>
       </c>
       <c r="F215" s="2" t="n">
         <v>5</v>
@@ -16107,11 +16107,11 @@
         <v>15</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Draw Reveal: Veolia Atlanta Pickleball Championships - PPA Tour, Veolia Environnement: Combined Shareholders’ General Meeting, April 23, 2026 - Business Wire, ‘More room for prices to move up’ - Plastics News</t>
+          <t>Out Now: Veolia’s 2025–2026 annual Integrated Report &amp; our new "Ask Veolia" chatbot - veolia.com, Draw Reveal: Veolia Atlanta Pickleball Championships - PPA Tour, Veolia Environnement: Combined Shareholders’ General Meeting, April 23, 2026 - Business Wire</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -16171,7 +16171,7 @@
         <v>112.46</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>16.75850537605361</v>
+        <v>16.75850537604284</v>
       </c>
       <c r="F216" s="2" t="n">
         <v>10</v>
@@ -16244,7 +16244,7 @@
         <v>84.95</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>28.7386459763989</v>
+        <v>30.02332441972929</v>
       </c>
       <c r="F217" s="2" t="n">
         <v>5</v>
@@ -16253,11 +16253,11 @@
         <v>15</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Pentair PLC stock outperforms competitors on strong trading day - MarketWatch, Zacks Research Has Positive Outlook for Pentair Q2 Earnings - MarketBeat, Pentair Completes $1.6B Ice Maker Acquisition - Modern Distribution Management</t>
+          <t>Pentair PLC stock outperforms competitors on strong trading day - MarketWatch, Pentair 42002-0024S Stack Flue Sensor Replacement Temperature Sensor For Pool And Spa Heater Electri - portalcantagalo.com.br, Zacks Research Has Positive Outlook for Pentair Q2 Earnings - MarketBeat</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -16317,7 +16317,7 @@
         <v>278.9</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>35.8152180369984</v>
+        <v>36.18240956403748</v>
       </c>
       <c r="F218" s="2" t="n">
         <v>5</v>
@@ -16326,7 +16326,7 @@
         <v>23</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>249.53</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>39.65036253251498</v>
+        <v>41.76534143089539</v>
       </c>
       <c r="F219" s="2" t="n">
         <v>10</v>
@@ -16399,7 +16399,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>10.6</v>
+        <v>19.1</v>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>19.49</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>28.67210525275933</v>
+        <v>28.15645932068331</v>
       </c>
       <c r="F220" s="2" t="n">
         <v>0</v>
@@ -16472,11 +16472,11 @@
         <v>23</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>22.7</v>
+        <v>20.6</v>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>GLUG Stock Fund Price and Chart — EURONEXT:GLUG - TradingView, Fund Overview: L&amp;G Clean Water UCITS ETF - ETF Stream, It's World Water Day - How Do I Invest? - Morningstar</t>
+          <t>GLUG Stock Fund Price and Chart — EURONEXT:GLUG - TradingView, It's World Water Day - How Do I Invest? - Morningstar, Fund Overview: L&amp;G Clean Water UCITS ETF - ETF Stream</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -16536,7 +16536,7 @@
         <v>64.2</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>24.57692674547556</v>
+        <v>24.57692674547444</v>
       </c>
       <c r="F221" s="2" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>497.22</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>55.29224984533903</v>
+        <v>55.21420366317685</v>
       </c>
       <c r="F222" s="3" t="n">
         <v>5</v>
@@ -16618,7 +16618,7 @@
         <v>23</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>29.2</v>
+        <v>28.9</v>
       </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>90.61</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>50.76538876444154</v>
+        <v>53.50637047365495</v>
       </c>
       <c r="F223" s="3" t="n">
         <v>10</v>
@@ -16691,11 +16691,11 @@
         <v>22</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>15.1</v>
+        <v>26</v>
       </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
-          <t>When the Final Buzzer Sounds: A WHL Journey into Agriculture and Nutrien - Nutrien, How Investors May Respond To Nutrien (TSX:NTR) Leveraging Tight Fertilizer Markets And Brazil Expansion - simplywall.st, Assessing Nutrien (TSX:NTR) Valuation After Recent Share Price Momentum - Yahoo Finance</t>
+          <t>How Investors May Respond To Nutrien (TSX:NTR) Leveraging Tight Fertilizer Markets And Brazil Expansion - simplywall.st, Assessing Nutrien (TSX:NTR) Valuation After Recent Share Price Momentum - Yahoo Finance, Is It Too Late To Consider Nutrien (TSX:NTR) After Its Strong One Year Rally? - Yahoo Finance</t>
         </is>
       </c>
       <c r="J223" s="3" t="inlineStr">
@@ -16755,7 +16755,7 @@
         <v>22.22</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>31.81345385499495</v>
+        <v>31.81345385499532</v>
       </c>
       <c r="F224" s="2" t="n">
         <v>10</v>
@@ -16828,7 +16828,7 @@
         <v>111.97</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>46.53739527057738</v>
+        <v>46.53739527055339</v>
       </c>
       <c r="F225" s="2" t="n">
         <v>5</v>
@@ -16901,7 +16901,7 @@
         <v>4.8</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>19.61470165476364</v>
+        <v>19.61470165476378</v>
       </c>
       <c r="F226" s="2" t="n">
         <v>0</v>
@@ -16974,7 +16974,7 @@
         <v>54.32</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>24.98887819704311</v>
+        <v>24.9888782436046</v>
       </c>
       <c r="F227" s="2" t="n">
         <v>0</v>
@@ -17047,7 +17047,7 @@
         <v>18.06</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>21.78711122833479</v>
+        <v>21.78711122832794</v>
       </c>
       <c r="F228" s="2" t="n">
         <v>5</v>
@@ -17120,7 +17120,7 @@
         <v>73.89</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>36.56862682663148</v>
+        <v>36.56862682663233</v>
       </c>
       <c r="F229" s="2" t="n">
         <v>10</v>
@@ -17193,7 +17193,7 @@
         <v>13.78</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>34.43422293290561</v>
+        <v>34.43422293290475</v>
       </c>
       <c r="F230" s="2" t="n">
         <v>0</v>
@@ -17266,7 +17266,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>39.56131105312524</v>
+        <v>39.56131105312044</v>
       </c>
       <c r="F231" s="2" t="n">
         <v>0</v>
@@ -17339,7 +17339,7 @@
         <v>115.65</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>31.05242817850478</v>
+        <v>31.57934497298069</v>
       </c>
       <c r="F232" s="2" t="n">
         <v>10</v>
@@ -17348,11 +17348,11 @@
         <v>23</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>12.2</v>
+        <v>14.3</v>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Bunge Global S.A. stock underperforms Friday when compared to competitors - MarketWatch, Is It Time To Reassess Bunge Global (BG) After The Viterra Merger Story? - simplywall.st, Bunge Global (BG) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance</t>
+          <t>Bunge Global S.A. stock underperforms Friday when compared to competitors - MarketWatch, A Look At Bunge Global (BG) Valuation As Analyst Optimism Builds Before Earnings - simplywall.st, Bunge Global (BG) Expected to Beat Earnings Estimates: Should You Buy? - Yahoo Finance</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -17412,7 +17412,7 @@
         <v>520.96</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>22.07473805360961</v>
+        <v>22.07473805360616</v>
       </c>
       <c r="F233" s="2" t="n">
         <v>10</v>
@@ -17485,7 +17485,7 @@
         <v>107.53</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>40.18093178793904</v>
+        <v>40.18474862724759</v>
       </c>
       <c r="F234" s="2" t="n">
         <v>5</v>
@@ -17558,7 +17558,7 @@
         <v>9.49</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>19.85645955614402</v>
+        <v>20.86560740321813</v>
       </c>
       <c r="F235" s="2" t="n">
         <v>10</v>
@@ -17567,11 +17567,11 @@
         <v>8</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>-12.6</v>
+        <v>-8.5</v>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>CNH Industrial (CNH) to Release Earnings on Thursday - MarketBeat, Pricing of CNH Industrial Capital LLC $500 million notes - CNH Newsroom, CNH Industrial N.V. Reports Fourth Quarter and Full Year 2025 Results - CNH Newsroom</t>
+          <t>Pricing of CNH Industrial Capital LLC $500 million notes - CNH Newsroom, CNH Industrial (CNH) to Release Earnings on Thursday - MarketBeat, Assessing CNH Industrial (CNH) Valuation As Barclays Backs Outlook In A Tough Machinery Market - Yahoo Finance</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -17631,7 +17631,7 @@
         <v>76.06</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>25.55337967351248</v>
+        <v>25.5533796735087</v>
       </c>
       <c r="F236" s="2" t="n">
         <v>0</v>
@@ -17704,7 +17704,7 @@
         <v>185.95</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>30.31822964548746</v>
+        <v>30.61374202370246</v>
       </c>
       <c r="F237" s="2" t="n">
         <v>5</v>
@@ -17713,7 +17713,7 @@
         <v>15</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>22.96</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>41.26886677742637</v>
+        <v>40.55444471353166</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>10</v>
@@ -17786,7 +17786,7 @@
         <v>22</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>17.1</v>
+        <v>14.2</v>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>60.25</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>45.29241337913751</v>
+        <v>45.29241337917382</v>
       </c>
       <c r="F239" s="2" t="n">
         <v>5</v>
@@ -17923,7 +17923,7 @@
         <v>15.04</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>25.76410966179014</v>
+        <v>27.00719663925982</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>5</v>
@@ -17932,7 +17932,7 @@
         <v>23</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>11.1</v>
+        <v>16</v>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>103.95</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>42.380832144991</v>
+        <v>41.64275569841602</v>
       </c>
       <c r="F241" s="2" t="n">
         <v>10</v>
@@ -18005,11 +18005,11 @@
         <v>15</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>UNIBAIL-RODAMCO-WESTFIELD Q1-2026 TRADING UPDATE - GlobeNewswire, Unibail-Rodamco-Westfield: No slowdown in consumption - marketscreener.com, Unibail-Rodamco-Westfield Proportionate Total Turnover Eur 908.2 Mln - TradingView</t>
+          <t>UNIBAIL-RODAMCO-WESTFIELD Q1-2026 TRADING UPDATE - GlobeNewswire, Unibail-Rodamco-Westfield: No slowdown in consumption - marketscreener.com, Unibail-Rodamco-Westfield (MEX:URWN) Stock Earnings Transcripts - GuruFocus</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -18069,7 +18069,7 @@
         <v>34.82</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>35.84060097299355</v>
+        <v>36.51624914444904</v>
       </c>
       <c r="F242" s="2" t="n">
         <v>10</v>
@@ -18078,7 +18078,7 @@
         <v>23</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>-8.6</v>
+        <v>-5.9</v>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>656.48</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>37.23970655538645</v>
+        <v>37.23970655537801</v>
       </c>
       <c r="F243" s="2" t="n">
         <v>5</v>
@@ -18215,7 +18215,7 @@
         <v>553.7</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>32.27793636918403</v>
+        <v>32.33879969642278</v>
       </c>
       <c r="F244" s="2" t="n">
         <v>0</v>
@@ -18224,7 +18224,7 @@
         <v>23</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>362.31</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>46.50078964140855</v>
+        <v>46.41106066946894</v>
       </c>
       <c r="F245" s="2" t="n">
         <v>10</v>
@@ -18297,7 +18297,7 @@
         <v>23</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>58.64</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>19.7229747027168</v>
+        <v>20.16443734243561</v>
       </c>
       <c r="F246" s="2" t="n">
         <v>0</v>
@@ -18370,7 +18370,7 @@
         <v>23</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>131.57</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>19.52671142295323</v>
+        <v>10</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>0</v>
@@ -18443,11 +18443,11 @@
         <v>15</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Prologis, Inc. $PLD Shares Sold by Calamos Advisors LLC - MarketBeat, Approval Deadline Set For Caltrain Railyards Mega-Project, San Francisco - San Francisco YIMBY, Truist raises Prologis stock price target on strong FFO outlook - Investing.com</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -18507,7 +18507,7 @@
         <v>185.19</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>13.6160477511638</v>
+        <v>13.0336774960259</v>
       </c>
       <c r="F248" s="2" t="n">
         <v>0</v>
@@ -18516,11 +18516,11 @@
         <v>7</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>46.5</v>
+        <v>44.1</v>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>B. Metzler seel. Sohn &amp; Co. AG Sells 18,745 Shares of Digital Realty Trust, Inc. $DLR - MarketBeat, Digital Realty Trust: Structural AI Demand Meets Excellent Execution - Potential Momentum Reversal - Seeking Alpha, Digital Realty jumps as Q1 results and raised 2026 outlook highlight strong AI-driven leasing momentum - Quiver Quantitative</t>
+          <t>Digital Realty Trust (DLR) Q1 2026 Revenue Sets Benchmark For Data Center REIT Narratives - simplywall.st, Digital Realty (DLR) Receives a Buy from RBC Capital - The Globe and Mail, B. Metzler seel. Sohn &amp; Co. AG Sells 18,745 Shares of Digital Realty Trust, Inc. $DLR - MarketBeat</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -18580,7 +18580,7 @@
         <v>1026.63</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>2.629849435768776</v>
+        <v>1.402913993226997</v>
       </c>
       <c r="F249" s="2" t="n">
         <v>0</v>
@@ -18589,11 +18589,11 @@
         <v>0</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>30.5</v>
+        <v>25.6</v>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Arizona State Retirement System Has $21.13 Million Stock Position in Equinix, Inc. $EQIX - MarketBeat, Satellite firm SpinLaunch selects Equinix to host ground station infrastructure - Data Center Dynamics, Equinix's AI Discovery Hub set to accelerate AI deployment in Hong Kong - Light Reading</t>
+          <t>Equinix Representative Clears Up Concerns About Minooka Data Center Campus Project - WCSJ News, Teacher Retirement System of Texas Sells 8,165 Shares of Equinix, Inc. $EQIX - MarketBeat, Equinix's AI Discovery Hub set to accelerate AI deployment in Hong Kong - Light Reading</t>
         </is>
       </c>
       <c r="J249" s="2" t="inlineStr">
@@ -18653,7 +18653,7 @@
         <v>165.01</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>33.79046457354146</v>
+        <v>35.73875985108623</v>
       </c>
       <c r="F250" s="2" t="n">
         <v>0</v>
@@ -18662,11 +18662,11 @@
         <v>30</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>-4.8</v>
+        <v>3</v>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>American Tower (AMT) Proxy filing Summary - Quartr, Is American Tower Stock a Smart Buy Before Q1 Earnings Release? - Yahoo Finance, Is It Time To Reconsider American Tower (AMT) After A 14% One-Year Share Price Decline - simplywall.st</t>
+          <t>American Tower (AMT) Valuation Check As Mixed EPS And Revenue Forecasts Shape Earnings Expectations - simplywall.st, How Will American Tower Stock React To Its Upcoming Earnings? - Trefis, Impax Asset Management Group plc Has $21.73 Million Stock Position in American Tower Corporation $AMT - MarketBeat</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
         <v>203.21</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>41.73441025428677</v>
+        <v>42.299122493716</v>
       </c>
       <c r="F251" s="2" t="n">
         <v>10</v>
@@ -18735,11 +18735,11 @@
         <v>30</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>26.9</v>
+        <v>29.2</v>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Is It Time To Reassess SBA Communications (SBAC) After Its Sharp 30 Day Share Price Jump - simplywall.st, SBA Communications sale rumor buoys tower stocks - Fierce Network, Is SBA Communications in play? Report says Boca Raton tower giant is exploring a sale after takeover interest - Wireless Estimator</t>
+          <t>SBA Communications stock soars on buyout interest. What it means for tower stocks. - MSN, SBA Communications sale rumor buoys tower stocks - Fierce Network, Is SBA Communications in play? Report says Boca Raton tower giant is exploring a sale after takeover interest - Wireless Estimator</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
         <v>43.48</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>38.17704752274012</v>
+        <v>38.89027465321388</v>
       </c>
       <c r="F252" s="2" t="n">
         <v>0</v>
@@ -18808,7 +18808,7 @@
         <v>23</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>20.7</v>
+        <v>23.6</v>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>How the Largest ETFs in the UK Performed - Morningstar, IWDA.L Stock Chart | ISHARES CORE MSCI WORLD (LON:IWDA) - ChartMill, How the Largest ETFs in Norway Performed - Morningstar</t>
+          <t>IWDA.AS Stock Price, Quote &amp; Chart | ISHARES CORE MSCI WORLD (AMS:IWDA) - ChartMill, How the Largest ETFs in the UK Performed - Morningstar, IWDA.L Stock Chart | ISHARES CORE MSCI WORLD (LON:IWDA) - ChartMill</t>
         </is>
       </c>
       <c r="J254" s="2" t="inlineStr">
@@ -19087,7 +19087,7 @@
         <v>48.11</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>21.3895697804038</v>
+        <v>21.38956978040055</v>
       </c>
       <c r="F256" s="2" t="n">
         <v>0</v>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF EIMI.L - eToro, How the Largest ETFs in the UK Performed - Morningstar, How the Largest ETFs in Norway Performed - Morningstar</t>
+          <t>How the Largest ETFs in the UK Performed - Morningstar, iShares Core MSCI EM IMI UCITS ETF EIMI.L - eToro, How the Largest ETFs in Norway Performed - Morningstar</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -19160,7 +19160,7 @@
         <v>710.62</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>7.962932873517563</v>
+        <v>7.962932873516642</v>
       </c>
       <c r="F257" s="2" t="n">
         <v>0</v>
@@ -19233,7 +19233,7 @@
         <v>607.8</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>4.987785516304822</v>
+        <v>6.060748890041575</v>
       </c>
       <c r="F258" s="2" t="n">
         <v>0</v>
@@ -19242,11 +19242,11 @@
         <v>7</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>-8</v>
+        <v>-3.8</v>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>VOO vs VTI vs SPY: Best S&amp;P 500 ETF for Your Core - Gotrade, Buy, Hold, or Sell VOO at $650? - 24/7 Wall St., Why Is Vanguard S&amp;P 500 ETF (VOO) Up Today, 4/23/2026? - TipRanks</t>
+          <t>Buy, Hold, or Sell VOO at $650? - 24/7 Wall St., VOO Stock Price, Quote &amp; Chart | VANGUARD S&amp;P 500 ETF (NYSEARCA:VOO) - ChartMill, VOO vs VTI vs SPY: Best S&amp;P 500 ETF for Your Core - Gotrade</t>
         </is>
       </c>
       <c r="J258" s="2" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Pre-market 19 Mar 2026: EXW1.DE iShares EURO STOXX 50 XETRA €57.76, most active - Meyka, ETFs Investing in Safran SA Stocks - TradingView, ETFs Investing in Siemens Energy AG Stocks - TradingView</t>
+          <t>Pre-market 19 Mar 2026: EXW1.DE iShares EURO STOXX 50 XETRA €57.76, most active - Meyka, ETFs Investing in Safran SA Stocks - TradingView, ETFs Investing in ASML Holding NV Stocks - TradingView</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -19452,7 +19452,7 @@
         <v>943.52</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>33.11183382011953</v>
+        <v>33.11183382012049</v>
       </c>
       <c r="F261" s="2" t="n">
         <v>0</v>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>ISF.MI Stock Chart | ISHARES CORE FTSE 100 (BIT:ISF) - ChartMill, FTSE 100’s flying, but fund investors aren’t buying - Interactive Investor, Steady Gains Place FTSE 100 in Focus Across UK Markets - Kalkine Media</t>
+          <t>5 of the Best FTSE 100 ETFs to Buy in April 2026 - InvestingReviews, ISF.MI Stock Chart | ISHARES CORE FTSE 100 (BIT:ISF) - ChartMill, FTSE 100’s flying, but fund investors aren’t buying - Interactive Investor</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -19525,7 +19525,7 @@
         <v>32.08</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>1.299272570759195</v>
+        <v>1.732536684721935</v>
       </c>
       <c r="F262" s="2" t="n">
         <v>0</v>
@@ -19534,7 +19534,7 @@
         <v>0</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>57.96</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>2.951438299250827</v>
+        <v>2.951438299248407</v>
       </c>
       <c r="F263" s="2" t="n">
         <v>0</v>
@@ -19667,7 +19667,7 @@
         <v>16.47</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>31.60023057833118</v>
+        <v>33.36083620785239</v>
       </c>
       <c r="F264" s="2" t="n">
         <v>0</v>
@@ -19676,11 +19676,11 @@
         <v>30</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>6.4</v>
+        <v>13.4</v>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>PDBC: Trump Has Just Spoiled The 2022-Style Commodities Boom (NASDAQ:PDBC) - Seeking Alpha, Kiker Wealth Sells $12 Million of Invesco Optimum Yield Diversified Commodity Strategy ETF - The Motley Fool, The One Commodity ETF Every Retirement Portfolio Needs as Inflation Insurance - 24/7 Wall St.</t>
+          <t>PDBC soared 35% this year, yet its December payout remains impossible to predict - 24/7 Wall St., PDBC: Trump Has Just Spoiled The 2022-Style Commodities Boom (NASDAQ:PDBC) - Seeking Alpha, Kiker Wealth Sells $12 Million of Invesco Optimum Yield Diversified Commodity Strategy ETF - The Motley Fool</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -19738,7 +19738,7 @@
         <v>80.29000000000001</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>28.33975278772508</v>
+        <v>28.97452842444324</v>
       </c>
       <c r="F265" s="2" t="n">
         <v>0</v>
@@ -19747,7 +19747,7 @@
         <v>15</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>13.4</v>
+        <v>15.9</v>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>177.72</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>13.33780676135095</v>
+        <v>13.33780676137328</v>
       </c>
       <c r="F267" s="2" t="n">
         <v>0</v>
@@ -20026,7 +20026,7 @@
         <v>87.11</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>30.11572497896985</v>
+        <v>29.43787641823361</v>
       </c>
       <c r="F269" s="2" t="n">
         <v>0</v>
@@ -20035,7 +20035,7 @@
         <v>30</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>0.5</v>
+        <v>-2.2</v>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>192.04</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>16.36255975811506</v>
+        <v>16.36255975811867</v>
       </c>
       <c r="F270" s="2" t="n">
         <v>0</v>
@@ -20172,7 +20172,7 @@
         <v>203240.74</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>30.78059730121437</v>
+        <v>31.33776294069041</v>
       </c>
       <c r="F271" s="2" t="n">
         <v>5</v>
@@ -20181,11 +20181,11 @@
         <v>15</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>-16.9</v>
+        <v>-14.6</v>
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Samsung's chip output drops overnight as workers protest over pay, union says - Reuters, Samsung Upgraded PDF Scanner Comes to Older Flagships With One UI 8.5 - Gadget Hacks, Samsung is selling refurbished Galaxy Z Fold 7 phones for more than new ones - Mashable</t>
+          <t>Samsung workers protest over huge pay gap with SK Hynix, threaten long strike - Reuters, Samsung's chip output drops overnight as workers protest over pay, union says - Reuters, Samsung Rally Draws 30,000 to Demand Greater Share of AI Profits - Bloomberg.com</t>
         </is>
       </c>
       <c r="J271" s="2" t="inlineStr">
@@ -20242,7 +20242,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
@@ -20301,11 +20301,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Scoring model indicates exit</t>
+          <t>Scoring model indicates exit | News: Ecolab Inc. (ECL): On the Cusp of Breakout Growth on CoolIT Systems Purchase - Yahoo Finance, Siemens and Ecolab Partner to Help Industry Reduce Greenhouse Gas Emissions, Improve Production - Siemens, Ecolab Unleashes Water Intelligence to Drive Growth in the AI Era - Business Wire</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>39.65036253251498</v>
+        <v>41.76534143089539</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>10</v>
@@ -20332,11 +20332,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Scoring model indicates exit</t>
+          <t>Scoring model indicates exit | News: Heidelberg Materials doubles stake in Turkish cement producer, gains majority control - S&amp;P Global, Heidelberg Materials Gains Majority Control of Akcansa in Turkey | 2026 - News and Statistics - IndexBox, Heidelberg Materials profit plunges 57% on raw material costs, steep competition - The Business Standard</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.31822964548746</v>
+        <v>30.61374202370246</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>5</v>
